--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY173"/>
+  <dimension ref="A1:AY185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8331,10 +8331,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129908881</v>
+        <v>129910600</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8342,46 +8342,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>516659</v>
+        <v>517181</v>
       </c>
       <c r="R75" t="n">
-        <v>6986705</v>
+        <v>6986168</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8416,11 +8404,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8429,31 +8412,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8470,7 +8428,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129910600</v>
+        <v>129910583</v>
       </c>
       <c r="B76" t="n">
         <v>80186</v>
@@ -8505,10 +8463,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>517181</v>
+        <v>517001</v>
       </c>
       <c r="R76" t="n">
-        <v>6986168</v>
+        <v>6986369</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8567,32 +8525,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129910583</v>
+        <v>129910670</v>
       </c>
       <c r="B77" t="n">
-        <v>80186</v>
+        <v>79337</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8602,10 +8560,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>517001</v>
+        <v>517175</v>
       </c>
       <c r="R77" t="n">
-        <v>6986369</v>
+        <v>6986169</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8664,10 +8622,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129910670</v>
+        <v>129910565</v>
       </c>
       <c r="B78" t="n">
-        <v>79337</v>
+        <v>79167</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8675,21 +8633,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6459</v>
+        <v>6450</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8699,10 +8657,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>517175</v>
+        <v>517235</v>
       </c>
       <c r="R78" t="n">
-        <v>6986169</v>
+        <v>6986250</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8761,32 +8719,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129910565</v>
+        <v>129910633</v>
       </c>
       <c r="B79" t="n">
-        <v>79167</v>
+        <v>80186</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8799,7 +8757,7 @@
         <v>517235</v>
       </c>
       <c r="R79" t="n">
-        <v>6986250</v>
+        <v>6986077</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,10 +8816,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129910633</v>
+        <v>129910541</v>
       </c>
       <c r="B80" t="n">
-        <v>80186</v>
+        <v>83052</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8869,21 +8827,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8893,10 +8851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>517235</v>
+        <v>517005</v>
       </c>
       <c r="R80" t="n">
-        <v>6986077</v>
+        <v>6986418</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8955,10 +8913,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129910541</v>
+        <v>129908881</v>
       </c>
       <c r="B81" t="n">
-        <v>83052</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8966,34 +8924,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>517005</v>
+        <v>516659</v>
       </c>
       <c r="R81" t="n">
-        <v>6986418</v>
+        <v>6986705</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9028,6 +8998,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9036,6 +9011,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -16124,57 +16124,61 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129908882</v>
+        <v>129910648</v>
       </c>
       <c r="B149" t="n">
-        <v>57736</v>
+        <v>98785</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>516646</v>
+        <v>517224</v>
       </c>
       <c r="R149" t="n">
-        <v>6986735</v>
+        <v>6986227</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16211,7 +16215,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
+          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16220,33 +16224,9 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -16263,10 +16243,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129908909</v>
+        <v>129910587</v>
       </c>
       <c r="B150" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16274,37 +16254,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>516915</v>
+        <v>517018</v>
       </c>
       <c r="R150" t="n">
-        <v>6986509</v>
+        <v>6986301</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16345,34 +16322,8 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -16389,10 +16340,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129908903</v>
+        <v>129910609</v>
       </c>
       <c r="B151" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16400,37 +16351,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>516956</v>
+        <v>517221</v>
       </c>
       <c r="R151" t="n">
-        <v>6986419</v>
+        <v>6986213</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16465,45 +16413,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>På bark av tall.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16520,10 +16437,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129908900</v>
+        <v>129910662</v>
       </c>
       <c r="B152" t="n">
-        <v>79081</v>
+        <v>88998</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16531,37 +16448,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>516960</v>
+        <v>517336</v>
       </c>
       <c r="R152" t="n">
-        <v>6986352</v>
+        <v>6986195</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16596,45 +16510,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal gran.</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16651,61 +16534,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129910648</v>
+        <v>129910607</v>
       </c>
       <c r="B153" t="n">
-        <v>98785</v>
+        <v>80186</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>517224</v>
+        <v>517246</v>
       </c>
       <c r="R153" t="n">
-        <v>6986227</v>
+        <v>6986091</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16740,18 +16607,12 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16770,7 +16631,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129910587</v>
+        <v>129910745</v>
       </c>
       <c r="B154" t="n">
         <v>80186</v>
@@ -16805,10 +16666,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>517018</v>
+        <v>516739</v>
       </c>
       <c r="R154" t="n">
-        <v>6986301</v>
+        <v>6986664</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16843,6 +16704,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>På stående död sälg</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -16855,22 +16721,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129910609</v>
+        <v>129908882</v>
       </c>
       <c r="B155" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16878,34 +16744,46 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>517221</v>
+        <v>516646</v>
       </c>
       <c r="R155" t="n">
-        <v>6986213</v>
+        <v>6986735</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16940,6 +16818,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
@@ -16948,6 +16831,31 @@
       </c>
       <c r="AG155" t="b">
         <v>0</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -16964,10 +16872,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129910662</v>
+        <v>129908909</v>
       </c>
       <c r="B156" t="n">
-        <v>88998</v>
+        <v>79081</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16975,34 +16883,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>517336</v>
+        <v>516915</v>
       </c>
       <c r="R156" t="n">
-        <v>6986195</v>
+        <v>6986509</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17043,8 +16954,34 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
@@ -17061,10 +16998,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129910607</v>
+        <v>129908903</v>
       </c>
       <c r="B157" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17072,34 +17009,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>517246</v>
+        <v>516956</v>
       </c>
       <c r="R157" t="n">
-        <v>6986091</v>
+        <v>6986419</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17134,14 +17074,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>På bark av tall.</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
@@ -17158,10 +17129,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129910745</v>
+        <v>129908900</v>
       </c>
       <c r="B158" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17169,34 +17140,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>516739</v>
+        <v>516960</v>
       </c>
       <c r="R158" t="n">
-        <v>6986664</v>
+        <v>6986352</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17233,7 +17207,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>På stående död sälg</t>
+          <t>På en grovbarkad gammal gran.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17242,18 +17216,44 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17643,7 +17643,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129910744</v>
+        <v>129910623</v>
       </c>
       <c r="B162" t="n">
         <v>80186</v>
@@ -17678,10 +17678,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>516858</v>
+        <v>517174</v>
       </c>
       <c r="R162" t="n">
-        <v>6986573</v>
+        <v>6986187</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17716,11 +17716,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>På både en lutande död sälg och en stående avbruten sälg.</t>
-        </is>
-      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
@@ -17733,22 +17728,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129910623</v>
+        <v>129910548</v>
       </c>
       <c r="B163" t="n">
-        <v>80186</v>
+        <v>97031</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17756,21 +17751,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17780,10 +17775,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>517174</v>
+        <v>517167</v>
       </c>
       <c r="R163" t="n">
-        <v>6986187</v>
+        <v>6986105</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17842,10 +17837,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129910548</v>
+        <v>129910628</v>
       </c>
       <c r="B164" t="n">
-        <v>97031</v>
+        <v>80186</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17853,21 +17848,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17877,10 +17872,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>517167</v>
+        <v>517207</v>
       </c>
       <c r="R164" t="n">
-        <v>6986105</v>
+        <v>6986088</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17939,7 +17934,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129910628</v>
+        <v>129910576</v>
       </c>
       <c r="B165" t="n">
         <v>80186</v>
@@ -17974,10 +17969,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>517207</v>
+        <v>516994</v>
       </c>
       <c r="R165" t="n">
-        <v>6986088</v>
+        <v>6986453</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18036,10 +18031,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129910576</v>
+        <v>129910550</v>
       </c>
       <c r="B166" t="n">
-        <v>80186</v>
+        <v>90631</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18047,21 +18042,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18071,10 +18066,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>516994</v>
+        <v>517343</v>
       </c>
       <c r="R166" t="n">
-        <v>6986453</v>
+        <v>6986165</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18133,10 +18128,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129910550</v>
+        <v>129910598</v>
       </c>
       <c r="B167" t="n">
-        <v>90631</v>
+        <v>80186</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18144,21 +18139,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18168,10 +18163,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>517343</v>
+        <v>517155</v>
       </c>
       <c r="R167" t="n">
-        <v>6986165</v>
+        <v>6986194</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18230,7 +18225,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129910598</v>
+        <v>129910616</v>
       </c>
       <c r="B168" t="n">
         <v>80186</v>
@@ -18265,10 +18260,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>517155</v>
+        <v>517030</v>
       </c>
       <c r="R168" t="n">
-        <v>6986194</v>
+        <v>6986400</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18327,10 +18322,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129910616</v>
+        <v>129910558</v>
       </c>
       <c r="B169" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18338,34 +18333,42 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>517030</v>
+        <v>517356</v>
       </c>
       <c r="R169" t="n">
-        <v>6986400</v>
+        <v>6986190</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18398,6 +18401,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18424,10 +18432,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129910558</v>
+        <v>129910586</v>
       </c>
       <c r="B170" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18435,42 +18443,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>517356</v>
+        <v>517006</v>
       </c>
       <c r="R170" t="n">
-        <v>6986190</v>
+        <v>6986354</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18503,11 +18503,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18534,7 +18529,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129910586</v>
+        <v>129910611</v>
       </c>
       <c r="B171" t="n">
         <v>80186</v>
@@ -18569,10 +18564,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>517006</v>
+        <v>517216</v>
       </c>
       <c r="R171" t="n">
-        <v>6986354</v>
+        <v>6986197</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18631,32 +18626,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129910611</v>
+        <v>129910669</v>
       </c>
       <c r="B172" t="n">
-        <v>80186</v>
+        <v>79337</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18666,10 +18661,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>517216</v>
+        <v>517113</v>
       </c>
       <c r="R172" t="n">
-        <v>6986197</v>
+        <v>6986244</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18728,32 +18723,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129910669</v>
+        <v>129910744</v>
       </c>
       <c r="B173" t="n">
-        <v>79337</v>
+        <v>80186</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18763,10 +18758,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>517113</v>
+        <v>516858</v>
       </c>
       <c r="R173" t="n">
-        <v>6986244</v>
+        <v>6986573</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18801,6 +18796,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>På både en lutande död sälg och en stående avbruten sälg.</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
@@ -18813,15 +18813,1204 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>129921270</v>
+      </c>
+      <c r="B174" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>516982</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6986407</v>
+      </c>
+      <c r="S174" t="n">
+        <v>10</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>129921278</v>
+      </c>
+      <c r="B175" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>516722</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6986685</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Sälg 30d</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>129921263</v>
+      </c>
+      <c r="B176" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>517036</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6986282</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>129921277</v>
+      </c>
+      <c r="B177" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>516723</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6986678</v>
+      </c>
+      <c r="S177" t="n">
+        <v>10</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>129921275</v>
+      </c>
+      <c r="B178" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>516836</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6986578</v>
+      </c>
+      <c r="S178" t="n">
+        <v>10</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>129921267</v>
+      </c>
+      <c r="B179" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>516991</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6986401</v>
+      </c>
+      <c r="S179" t="n">
+        <v>10</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>129921276</v>
+      </c>
+      <c r="B180" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>516767</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6986655</v>
+      </c>
+      <c r="S180" t="n">
+        <v>10</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>129921280</v>
+      </c>
+      <c r="B181" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>516855</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6986589</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>129921271</v>
+      </c>
+      <c r="B182" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>517013</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6986336</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>129921272</v>
+      </c>
+      <c r="B183" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>516904</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6986452</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>129921265</v>
+      </c>
+      <c r="B184" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>516957</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6986331</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>129921274</v>
+      </c>
+      <c r="B185" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Bergmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>516894</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6986522</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129910649</v>
+        <v>129910580</v>
       </c>
       <c r="B27" t="n">
-        <v>56917</v>
+        <v>80186</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,50 +3302,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517134</v>
+        <v>517047</v>
       </c>
       <c r="R27" t="n">
-        <v>6986204</v>
+        <v>6986415</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3404,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129910564</v>
+        <v>129910610</v>
       </c>
       <c r="B28" t="n">
-        <v>80052</v>
+        <v>80186</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,21 +3399,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3439,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517170</v>
+        <v>517211</v>
       </c>
       <c r="R28" t="n">
-        <v>6986124</v>
+        <v>6986211</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3483,7 +3467,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3502,7 +3485,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129910580</v>
+        <v>129910599</v>
       </c>
       <c r="B29" t="n">
         <v>80186</v>
@@ -3537,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517047</v>
+        <v>517177</v>
       </c>
       <c r="R29" t="n">
-        <v>6986415</v>
+        <v>6986167</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3599,7 +3582,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129910610</v>
+        <v>129910620</v>
       </c>
       <c r="B30" t="n">
         <v>80186</v>
@@ -3634,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>517211</v>
+        <v>517112</v>
       </c>
       <c r="R30" t="n">
-        <v>6986211</v>
+        <v>6986273</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3696,32 +3679,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129910599</v>
+        <v>129910668</v>
       </c>
       <c r="B31" t="n">
-        <v>80186</v>
+        <v>79337</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3731,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>517177</v>
+        <v>517042</v>
       </c>
       <c r="R31" t="n">
-        <v>6986167</v>
+        <v>6986262</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3793,7 +3776,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129910620</v>
+        <v>129910631</v>
       </c>
       <c r="B32" t="n">
         <v>80186</v>
@@ -3828,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517112</v>
+        <v>517287</v>
       </c>
       <c r="R32" t="n">
-        <v>6986273</v>
+        <v>6986080</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3890,32 +3873,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129910668</v>
+        <v>129910601</v>
       </c>
       <c r="B33" t="n">
-        <v>79337</v>
+        <v>80186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3925,10 +3908,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517042</v>
+        <v>517170</v>
       </c>
       <c r="R33" t="n">
-        <v>6986262</v>
+        <v>6986161</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3987,7 +3970,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129910631</v>
+        <v>129910592</v>
       </c>
       <c r="B34" t="n">
         <v>80186</v>
@@ -4022,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517287</v>
+        <v>517119</v>
       </c>
       <c r="R34" t="n">
-        <v>6986080</v>
+        <v>6986251</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4084,10 +4067,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129910601</v>
+        <v>129908880</v>
       </c>
       <c r="B35" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4095,34 +4078,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517170</v>
+        <v>516686</v>
       </c>
       <c r="R35" t="n">
-        <v>6986161</v>
+        <v>6986687</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4157,6 +4152,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4165,6 +4165,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4181,10 +4206,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129910592</v>
+        <v>129910649</v>
       </c>
       <c r="B36" t="n">
-        <v>80186</v>
+        <v>56917</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4192,34 +4217,50 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517119</v>
+        <v>517134</v>
       </c>
       <c r="R36" t="n">
-        <v>6986251</v>
+        <v>6986204</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4278,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129908880</v>
+        <v>129910564</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>80052</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4289,46 +4330,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>388</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>516686</v>
+        <v>517170</v>
       </c>
       <c r="R37" t="n">
-        <v>6986687</v>
+        <v>6986124</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4363,44 +4392,15 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5220,10 +5220,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129910547</v>
+        <v>129910632</v>
       </c>
       <c r="B46" t="n">
-        <v>97036</v>
+        <v>80186</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5231,21 +5231,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>517122</v>
+        <v>517285</v>
       </c>
       <c r="R46" t="n">
-        <v>6986191</v>
+        <v>6986090</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5317,10 +5317,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129910568</v>
+        <v>129910591</v>
       </c>
       <c r="B47" t="n">
-        <v>80187</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>517230</v>
+        <v>517068</v>
       </c>
       <c r="R47" t="n">
-        <v>6986059</v>
+        <v>6986257</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5414,52 +5414,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129910660</v>
+        <v>129910750</v>
       </c>
       <c r="B48" t="n">
-        <v>92194</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>517050</v>
+        <v>517017</v>
       </c>
       <c r="R48" t="n">
-        <v>6986414</v>
+        <v>6986332</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,50 +5487,39 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129910632</v>
+        <v>129910559</v>
       </c>
       <c r="B49" t="n">
-        <v>80186</v>
+        <v>57896</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,34 +5527,50 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>517285</v>
+        <v>517266</v>
       </c>
       <c r="R49" t="n">
-        <v>6986090</v>
+        <v>6986055</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,10 +5629,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129910591</v>
+        <v>129910547</v>
       </c>
       <c r="B50" t="n">
-        <v>80186</v>
+        <v>97036</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5642,21 +5640,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5664,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>517068</v>
+        <v>517122</v>
       </c>
       <c r="R50" t="n">
-        <v>6986257</v>
+        <v>6986191</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,10 +5726,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129910750</v>
+        <v>129910568</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5739,21 +5737,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5761,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>517017</v>
+        <v>517230</v>
       </c>
       <c r="R51" t="n">
-        <v>6986332</v>
+        <v>6986059</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5801,11 +5799,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5818,73 +5811,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129910559</v>
+        <v>129910660</v>
       </c>
       <c r="B52" t="n">
-        <v>57896</v>
+        <v>92194</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>760</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>517266</v>
+        <v>517050</v>
       </c>
       <c r="R52" t="n">
-        <v>6986055</v>
+        <v>6986414</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5925,8 +5909,24 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -10482,32 +10482,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129910625</v>
+        <v>129910748</v>
       </c>
       <c r="B96" t="n">
-        <v>80186</v>
+        <v>98790</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10517,10 +10517,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>517184</v>
+        <v>516692</v>
       </c>
       <c r="R96" t="n">
-        <v>6986149</v>
+        <v>6986711</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10555,6 +10555,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10567,19 +10572,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129910626</v>
+        <v>129910739</v>
       </c>
       <c r="B97" t="n">
         <v>80186</v>
@@ -10614,10 +10619,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>517169</v>
+        <v>517016</v>
       </c>
       <c r="R97" t="n">
-        <v>6986147</v>
+        <v>6986355</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10652,6 +10657,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>2 st sälgar, stående, oklart om levande</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10664,22 +10674,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129910542</v>
+        <v>129910625</v>
       </c>
       <c r="B98" t="n">
-        <v>83052</v>
+        <v>80186</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10687,21 +10697,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10711,10 +10721,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>517009</v>
+        <v>517184</v>
       </c>
       <c r="R98" t="n">
-        <v>6986437</v>
+        <v>6986149</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10773,32 +10783,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129910748</v>
+        <v>129910626</v>
       </c>
       <c r="B99" t="n">
-        <v>98790</v>
+        <v>80186</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10808,10 +10818,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>516692</v>
+        <v>517169</v>
       </c>
       <c r="R99" t="n">
-        <v>6986711</v>
+        <v>6986147</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10846,11 +10856,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -10863,22 +10868,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129910739</v>
+        <v>129910542</v>
       </c>
       <c r="B100" t="n">
-        <v>80186</v>
+        <v>83052</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10886,21 +10891,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10910,10 +10915,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>517016</v>
+        <v>517009</v>
       </c>
       <c r="R100" t="n">
-        <v>6986355</v>
+        <v>6986437</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10948,11 +10953,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>2 st sälgar, stående, oklart om levande</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -10965,12 +10965,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -14197,61 +14197,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129910560</v>
+        <v>129910624</v>
       </c>
       <c r="B131" t="n">
-        <v>58369</v>
+        <v>80186</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>517237</v>
+        <v>517195</v>
       </c>
       <c r="R131" t="n">
-        <v>6986082</v>
+        <v>6986175</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14310,32 +14294,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129910584</v>
+        <v>129910572</v>
       </c>
       <c r="B132" t="n">
-        <v>80186</v>
+        <v>80090</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14345,10 +14329,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>517004</v>
+        <v>517147</v>
       </c>
       <c r="R132" t="n">
-        <v>6986361</v>
+        <v>6986129</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14407,45 +14391,57 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129910594</v>
+        <v>129908893</v>
       </c>
       <c r="B133" t="n">
-        <v>80186</v>
+        <v>98790</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>517165</v>
+        <v>516958</v>
       </c>
       <c r="R133" t="n">
-        <v>6986222</v>
+        <v>6986409</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14480,14 +14476,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i barrblandskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
@@ -14504,45 +14511,61 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129910624</v>
+        <v>129908897</v>
       </c>
       <c r="B134" t="n">
-        <v>80186</v>
+        <v>98790</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>517195</v>
+        <v>516696</v>
       </c>
       <c r="R134" t="n">
-        <v>6986175</v>
+        <v>6986696</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14577,14 +14600,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Minst 20 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
@@ -14601,10 +14635,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129910747</v>
+        <v>129910551</v>
       </c>
       <c r="B135" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14612,34 +14646,41 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>516674</v>
+        <v>517014</v>
       </c>
       <c r="R135" t="n">
-        <v>6986695</v>
+        <v>6986339</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14674,74 +14715,106 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på liggande men levande sälg.</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129910634</v>
+        <v>129910560</v>
       </c>
       <c r="B136" t="n">
-        <v>80186</v>
+        <v>58369</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>102125</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>517233</v>
+        <v>517237</v>
       </c>
       <c r="R136" t="n">
-        <v>6986069</v>
+        <v>6986082</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14800,52 +14873,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129910659</v>
+        <v>129910584</v>
       </c>
       <c r="B137" t="n">
-        <v>92881</v>
+        <v>80186</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>517328</v>
+        <v>517004</v>
       </c>
       <c r="R137" t="n">
-        <v>6986156</v>
+        <v>6986361</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14886,7 +14952,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14905,32 +14970,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129910572</v>
+        <v>129910594</v>
       </c>
       <c r="B138" t="n">
-        <v>80090</v>
+        <v>80186</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14940,10 +15005,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>517147</v>
+        <v>517165</v>
       </c>
       <c r="R138" t="n">
-        <v>6986129</v>
+        <v>6986222</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15002,10 +15067,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129910551</v>
+        <v>129910747</v>
       </c>
       <c r="B139" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15013,41 +15078,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>517014</v>
+        <v>516674</v>
       </c>
       <c r="R139" t="n">
-        <v>6986339</v>
+        <v>6986695</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15082,102 +15140,74 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på liggande men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129908893</v>
+        <v>129910634</v>
       </c>
       <c r="B140" t="n">
-        <v>98790</v>
+        <v>80186</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>516958</v>
+        <v>517233</v>
       </c>
       <c r="R140" t="n">
-        <v>6986409</v>
+        <v>6986069</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15212,25 +15242,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i barrblandskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
@@ -15247,50 +15266,41 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129908897</v>
+        <v>129910659</v>
       </c>
       <c r="B141" t="n">
-        <v>98790</v>
+        <v>92881</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15298,10 +15308,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>516696</v>
+        <v>517328</v>
       </c>
       <c r="R141" t="n">
-        <v>6986696</v>
+        <v>6986156</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15336,11 +15346,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Minst 20 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15350,11 +15355,6 @@
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
@@ -16124,10 +16124,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129910745</v>
+        <v>129908882</v>
       </c>
       <c r="B149" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16135,34 +16135,46 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>516739</v>
+        <v>516646</v>
       </c>
       <c r="R149" t="n">
-        <v>6986664</v>
+        <v>6986735</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16199,7 +16211,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>På stående död sälg</t>
+          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16210,26 +16222,51 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129908882</v>
+        <v>129910662</v>
       </c>
       <c r="B150" t="n">
-        <v>57736</v>
+        <v>88998</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16237,46 +16274,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>516646</v>
+        <v>517336</v>
       </c>
       <c r="R150" t="n">
-        <v>6986735</v>
+        <v>6986195</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16311,11 +16336,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -16324,31 +16344,6 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -16365,61 +16360,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129910648</v>
+        <v>129910607</v>
       </c>
       <c r="B151" t="n">
-        <v>98790</v>
+        <v>80186</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>517224</v>
+        <v>517246</v>
       </c>
       <c r="R151" t="n">
-        <v>6986227</v>
+        <v>6986091</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16454,18 +16433,12 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16484,10 +16457,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129910662</v>
+        <v>129908900</v>
       </c>
       <c r="B152" t="n">
-        <v>88998</v>
+        <v>79081</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16495,34 +16468,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>517336</v>
+        <v>516960</v>
       </c>
       <c r="R152" t="n">
-        <v>6986195</v>
+        <v>6986352</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16557,14 +16533,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal gran.</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16581,10 +16588,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129910607</v>
+        <v>129908909</v>
       </c>
       <c r="B153" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16592,34 +16599,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>517246</v>
+        <v>516915</v>
       </c>
       <c r="R153" t="n">
-        <v>6986091</v>
+        <v>6986509</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16660,8 +16670,34 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
@@ -16678,7 +16714,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129908900</v>
+        <v>129908903</v>
       </c>
       <c r="B154" t="n">
         <v>79081</v>
@@ -16716,10 +16752,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>516960</v>
+        <v>516956</v>
       </c>
       <c r="R154" t="n">
-        <v>6986352</v>
+        <v>6986419</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16756,7 +16792,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>På en grovbarkad gammal gran.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16776,22 +16812,22 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -16809,10 +16845,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129908909</v>
+        <v>129910587</v>
       </c>
       <c r="B155" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16820,37 +16856,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>516915</v>
+        <v>517018</v>
       </c>
       <c r="R155" t="n">
-        <v>6986509</v>
+        <v>6986301</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16891,34 +16924,8 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -16935,10 +16942,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129908903</v>
+        <v>129910609</v>
       </c>
       <c r="B156" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16946,37 +16953,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>516956</v>
+        <v>517221</v>
       </c>
       <c r="R156" t="n">
-        <v>6986419</v>
+        <v>6986213</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17011,45 +17015,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>På bark av tall.</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
@@ -17066,7 +17039,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129910587</v>
+        <v>129910745</v>
       </c>
       <c r="B157" t="n">
         <v>80186</v>
@@ -17101,10 +17074,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>517018</v>
+        <v>516739</v>
       </c>
       <c r="R157" t="n">
-        <v>6986301</v>
+        <v>6986664</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17139,6 +17112,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>På stående död sälg</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -17151,57 +17129,73 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129910609</v>
+        <v>129910648</v>
       </c>
       <c r="B158" t="n">
-        <v>80186</v>
+        <v>98790</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>517221</v>
+        <v>517224</v>
       </c>
       <c r="R158" t="n">
-        <v>6986213</v>
+        <v>6986227</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17236,12 +17230,18 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910556</v>
+        <v>129910574</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>79108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517169</v>
+        <v>517340</v>
       </c>
       <c r="R2" t="n">
-        <v>6986201</v>
+        <v>6986164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910557</v>
+        <v>129910577</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517175</v>
+        <v>517035</v>
       </c>
       <c r="R3" t="n">
-        <v>6986155</v>
+        <v>6986429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,45 +869,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910574</v>
+        <v>129910654</v>
       </c>
       <c r="B4" t="n">
-        <v>79105</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517340</v>
+        <v>517262</v>
       </c>
       <c r="R4" t="n">
-        <v>6986164</v>
+        <v>6986119</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,14 +953,35 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt!!</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -992,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910577</v>
+        <v>129910752</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517035</v>
+        <v>516947</v>
       </c>
       <c r="R5" t="n">
-        <v>6986429</v>
+        <v>6986297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1071,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1077,22 +1088,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910654</v>
+        <v>129908891</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1111,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1135,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517262</v>
+        <v>516683</v>
       </c>
       <c r="R6" t="n">
-        <v>6986119</v>
+        <v>6986718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1182,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt!!</t>
+          <t>På asp i granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,19 +1195,29 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1218,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910752</v>
+        <v>129910667</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516947</v>
+        <v>517221</v>
       </c>
       <c r="R7" t="n">
-        <v>6986297</v>
+        <v>6986209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,11 +1308,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1308,22 +1320,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129908891</v>
+        <v>129910666</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>81147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,41 +1343,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>229558</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516683</v>
+        <v>517120</v>
       </c>
       <c r="R8" t="n">
-        <v>6986718</v>
+        <v>6986257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,45 +1405,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp i granskog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1455,45 +1429,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129910667</v>
+        <v>129910557</v>
       </c>
       <c r="B9" t="n">
-        <v>79337</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517221</v>
+        <v>517175</v>
       </c>
       <c r="R9" t="n">
-        <v>6986209</v>
+        <v>6986155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,6 +1508,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129910642</v>
+        <v>129910556</v>
       </c>
       <c r="B10" t="n">
-        <v>78094</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,34 +1550,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517251</v>
+        <v>517169</v>
       </c>
       <c r="R10" t="n">
-        <v>6986078</v>
+        <v>6986201</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,6 +1618,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129910666</v>
+        <v>129910642</v>
       </c>
       <c r="B11" t="n">
-        <v>81144</v>
+        <v>78097</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229558</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517120</v>
+        <v>517251</v>
       </c>
       <c r="R11" t="n">
-        <v>6986257</v>
+        <v>6986078</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,7 +1749,7 @@
         <v>129910555</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>129908878</v>
       </c>
       <c r="B13" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>129910643</v>
       </c>
       <c r="B14" t="n">
-        <v>80057</v>
+        <v>80060</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>129910549</v>
       </c>
       <c r="B15" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>129910614</v>
       </c>
       <c r="B16" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>129910597</v>
       </c>
       <c r="B17" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>129910585</v>
       </c>
       <c r="B18" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>129910596</v>
       </c>
       <c r="B19" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>129910544</v>
       </c>
       <c r="B20" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>129910579</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>129910615</v>
       </c>
       <c r="B22" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>129910742</v>
       </c>
       <c r="B23" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>129910613</v>
       </c>
       <c r="B24" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>129908906</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>129910751</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129910580</v>
+        <v>129908880</v>
       </c>
       <c r="B27" t="n">
-        <v>80186</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,34 +3302,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517047</v>
+        <v>516686</v>
       </c>
       <c r="R27" t="n">
-        <v>6986415</v>
+        <v>6986687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,6 +3376,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3372,6 +3389,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3388,10 +3430,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129910610</v>
+        <v>129910592</v>
       </c>
       <c r="B28" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3423,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517211</v>
+        <v>517119</v>
       </c>
       <c r="R28" t="n">
-        <v>6986211</v>
+        <v>6986251</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,10 +3527,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129910599</v>
+        <v>129910649</v>
       </c>
       <c r="B29" t="n">
-        <v>80186</v>
+        <v>56918</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3496,34 +3538,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517177</v>
+        <v>517134</v>
       </c>
       <c r="R29" t="n">
-        <v>6986167</v>
+        <v>6986204</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,10 +3640,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129910620</v>
+        <v>129910580</v>
       </c>
       <c r="B30" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3617,10 +3675,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>517112</v>
+        <v>517047</v>
       </c>
       <c r="R30" t="n">
-        <v>6986273</v>
+        <v>6986415</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,32 +3737,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129910668</v>
+        <v>129910610</v>
       </c>
       <c r="B31" t="n">
-        <v>79337</v>
+        <v>80189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3772,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>517042</v>
+        <v>517211</v>
       </c>
       <c r="R31" t="n">
-        <v>6986262</v>
+        <v>6986211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,10 +3834,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129910631</v>
+        <v>129910599</v>
       </c>
       <c r="B32" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3811,10 +3869,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517287</v>
+        <v>517177</v>
       </c>
       <c r="R32" t="n">
-        <v>6986080</v>
+        <v>6986167</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3873,10 +3931,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129910601</v>
+        <v>129910620</v>
       </c>
       <c r="B33" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3908,10 +3966,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517170</v>
+        <v>517112</v>
       </c>
       <c r="R33" t="n">
-        <v>6986161</v>
+        <v>6986273</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3970,32 +4028,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129910592</v>
+        <v>129910668</v>
       </c>
       <c r="B34" t="n">
-        <v>80186</v>
+        <v>79340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4063,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517119</v>
+        <v>517042</v>
       </c>
       <c r="R34" t="n">
-        <v>6986251</v>
+        <v>6986262</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,10 +4125,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129908880</v>
+        <v>129910631</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>80189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,46 +4136,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>516686</v>
+        <v>517287</v>
       </c>
       <c r="R35" t="n">
-        <v>6986687</v>
+        <v>6986080</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,11 +4198,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4165,31 +4206,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4206,10 +4222,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129910649</v>
+        <v>129910601</v>
       </c>
       <c r="B36" t="n">
-        <v>56917</v>
+        <v>80189</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4217,50 +4233,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517134</v>
+        <v>517170</v>
       </c>
       <c r="R36" t="n">
-        <v>6986204</v>
+        <v>6986161</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4322,7 +4322,7 @@
         <v>129910564</v>
       </c>
       <c r="B37" t="n">
-        <v>80052</v>
+        <v>80055</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4417,45 +4417,61 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129910655</v>
+        <v>129908896</v>
       </c>
       <c r="B38" t="n">
-        <v>82918</v>
+        <v>98794</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>516970</v>
+        <v>516925</v>
       </c>
       <c r="R38" t="n">
-        <v>6986375</v>
+        <v>6986509</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4490,14 +4506,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4514,32 +4541,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129910567</v>
+        <v>129910646</v>
       </c>
       <c r="B39" t="n">
-        <v>80187</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4549,10 +4576,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>517062</v>
+        <v>517237</v>
       </c>
       <c r="R39" t="n">
-        <v>6986268</v>
+        <v>6986059</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4611,10 +4638,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129910581</v>
+        <v>129910655</v>
       </c>
       <c r="B40" t="n">
-        <v>80186</v>
+        <v>82921</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4622,21 +4649,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4646,10 +4673,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>517011</v>
+        <v>516970</v>
       </c>
       <c r="R40" t="n">
-        <v>6986383</v>
+        <v>6986375</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,10 +4735,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129910589</v>
+        <v>129910567</v>
       </c>
       <c r="B41" t="n">
-        <v>80186</v>
+        <v>80190</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4719,21 +4746,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4743,10 +4770,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>517055</v>
+        <v>517062</v>
       </c>
       <c r="R41" t="n">
-        <v>6986272</v>
+        <v>6986268</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4805,10 +4832,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129910578</v>
+        <v>129910581</v>
       </c>
       <c r="B42" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4840,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>517037</v>
+        <v>517011</v>
       </c>
       <c r="R42" t="n">
-        <v>6986432</v>
+        <v>6986383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4902,10 +4929,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129910629</v>
+        <v>129910589</v>
       </c>
       <c r="B43" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4937,10 +4964,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>517270</v>
+        <v>517055</v>
       </c>
       <c r="R43" t="n">
-        <v>6986036</v>
+        <v>6986272</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,32 +5026,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129910646</v>
+        <v>129910578</v>
       </c>
       <c r="B44" t="n">
-        <v>80146</v>
+        <v>80189</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5034,10 +5061,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>517237</v>
+        <v>517037</v>
       </c>
       <c r="R44" t="n">
-        <v>6986059</v>
+        <v>6986432</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5096,61 +5123,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129908896</v>
+        <v>129910629</v>
       </c>
       <c r="B45" t="n">
-        <v>98790</v>
+        <v>80189</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>516925</v>
+        <v>517270</v>
       </c>
       <c r="R45" t="n">
-        <v>6986509</v>
+        <v>6986036</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5185,25 +5196,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5220,45 +5220,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129910632</v>
+        <v>129910660</v>
       </c>
       <c r="B46" t="n">
-        <v>80186</v>
+        <v>92197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>517285</v>
+        <v>517050</v>
       </c>
       <c r="R46" t="n">
-        <v>6986090</v>
+        <v>6986414</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5299,8 +5306,24 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5317,10 +5340,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129910591</v>
+        <v>129910547</v>
       </c>
       <c r="B47" t="n">
-        <v>80186</v>
+        <v>97040</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5328,21 +5351,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5352,10 +5375,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>517068</v>
+        <v>517122</v>
       </c>
       <c r="R47" t="n">
-        <v>6986257</v>
+        <v>6986191</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5414,10 +5437,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129910750</v>
+        <v>129910568</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>80190</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5425,21 +5448,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5449,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>517017</v>
+        <v>517230</v>
       </c>
       <c r="R48" t="n">
-        <v>6986332</v>
+        <v>6986059</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5487,11 +5510,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5504,22 +5522,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129910559</v>
+        <v>129910632</v>
       </c>
       <c r="B49" t="n">
-        <v>57896</v>
+        <v>80189</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5527,50 +5545,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>517266</v>
+        <v>517285</v>
       </c>
       <c r="R49" t="n">
-        <v>6986055</v>
+        <v>6986090</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5629,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129910547</v>
+        <v>129910591</v>
       </c>
       <c r="B50" t="n">
-        <v>97036</v>
+        <v>80189</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5640,21 +5642,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5664,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>517122</v>
+        <v>517068</v>
       </c>
       <c r="R50" t="n">
-        <v>6986191</v>
+        <v>6986257</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5726,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129910568</v>
+        <v>129910750</v>
       </c>
       <c r="B51" t="n">
-        <v>80187</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5737,21 +5739,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5761,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>517230</v>
+        <v>517017</v>
       </c>
       <c r="R51" t="n">
-        <v>6986059</v>
+        <v>6986332</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,6 +5801,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5811,64 +5818,73 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129910660</v>
+        <v>129910559</v>
       </c>
       <c r="B52" t="n">
-        <v>92194</v>
+        <v>57895</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>760</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>517050</v>
+        <v>517266</v>
       </c>
       <c r="R52" t="n">
-        <v>6986414</v>
+        <v>6986055</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5909,24 +5925,8 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -5943,10 +5943,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129910573</v>
+        <v>129910588</v>
       </c>
       <c r="B53" t="n">
-        <v>75177</v>
+        <v>80189</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5954,21 +5954,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>517112</v>
+        <v>517014</v>
       </c>
       <c r="R53" t="n">
-        <v>6986241</v>
+        <v>6986283</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6040,10 +6040,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129910588</v>
+        <v>129908905</v>
       </c>
       <c r="B54" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6051,34 +6051,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>517014</v>
+        <v>517020</v>
       </c>
       <c r="R54" t="n">
-        <v>6986283</v>
+        <v>6986358</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6113,14 +6116,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar i granskog.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6137,10 +6171,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129908905</v>
+        <v>129910630</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6148,37 +6182,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>517020</v>
+        <v>517275</v>
       </c>
       <c r="R55" t="n">
-        <v>6986358</v>
+        <v>6986074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6213,45 +6244,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6268,10 +6268,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129910630</v>
+        <v>129910606</v>
       </c>
       <c r="B56" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>517275</v>
+        <v>517237</v>
       </c>
       <c r="R56" t="n">
-        <v>6986074</v>
+        <v>6986073</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6365,10 +6365,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129910606</v>
+        <v>129910741</v>
       </c>
       <c r="B57" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>517237</v>
+        <v>517046</v>
       </c>
       <c r="R57" t="n">
-        <v>6986073</v>
+        <v>6986289</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6438,6 +6438,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6450,57 +6455,64 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129910741</v>
+        <v>129910663</v>
       </c>
       <c r="B58" t="n">
-        <v>80186</v>
+        <v>80224</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>517046</v>
+        <v>517007</v>
       </c>
       <c r="R58" t="n">
-        <v>6986289</v>
+        <v>6986367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6535,39 +6547,35 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129910653</v>
+        <v>129910573</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>75180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6575,37 +6583,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>516971</v>
+        <v>517112</v>
       </c>
       <c r="R59" t="n">
-        <v>6986287</v>
+        <v>6986241</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6640,35 +6645,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6685,27 +6669,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129910663</v>
+        <v>129910653</v>
       </c>
       <c r="B60" t="n">
-        <v>80221</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6715,11 +6699,7 @@
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6727,10 +6707,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>517007</v>
+        <v>516971</v>
       </c>
       <c r="R60" t="n">
-        <v>6986367</v>
+        <v>6986287</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6765,6 +6745,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6774,6 +6759,21 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6790,10 +6790,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129910604</v>
+        <v>129908901</v>
       </c>
       <c r="B61" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6801,34 +6801,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>517211</v>
+        <v>516936</v>
       </c>
       <c r="R61" t="n">
-        <v>6986077</v>
+        <v>6986463</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6869,8 +6872,34 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6887,10 +6916,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129908888</v>
+        <v>129910604</v>
       </c>
       <c r="B62" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6916,19 +6945,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>516854</v>
+        <v>517211</v>
       </c>
       <c r="R62" t="n">
-        <v>6986558</v>
+        <v>6986077</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6963,45 +6989,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7018,10 +7013,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129910617</v>
+        <v>129908888</v>
       </c>
       <c r="B63" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7047,16 +7042,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>517040</v>
+        <v>516854</v>
       </c>
       <c r="R63" t="n">
-        <v>6986263</v>
+        <v>6986558</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7091,14 +7089,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7115,10 +7144,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129910575</v>
+        <v>129910746</v>
       </c>
       <c r="B64" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,10 +7179,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>516969</v>
+        <v>516690</v>
       </c>
       <c r="R64" t="n">
-        <v>6986323</v>
+        <v>6986709</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7188,6 +7217,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7200,22 +7234,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129910641</v>
+        <v>129910595</v>
       </c>
       <c r="B65" t="n">
-        <v>78094</v>
+        <v>80189</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7223,21 +7257,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7247,10 +7281,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>517183</v>
+        <v>517169</v>
       </c>
       <c r="R65" t="n">
-        <v>6986150</v>
+        <v>6986203</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7309,10 +7343,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129910746</v>
+        <v>129910617</v>
       </c>
       <c r="B66" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7344,10 +7378,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>516690</v>
+        <v>517040</v>
       </c>
       <c r="R66" t="n">
-        <v>6986709</v>
+        <v>6986263</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7382,11 +7416,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7399,22 +7428,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129910595</v>
+        <v>129910575</v>
       </c>
       <c r="B67" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7446,10 +7475,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>517169</v>
+        <v>516969</v>
       </c>
       <c r="R67" t="n">
-        <v>6986203</v>
+        <v>6986323</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7508,10 +7537,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129908901</v>
+        <v>129910641</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>78097</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7519,37 +7548,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>516936</v>
+        <v>517183</v>
       </c>
       <c r="R68" t="n">
-        <v>6986463</v>
+        <v>6986150</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7590,34 +7616,8 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -7634,10 +7634,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129910754</v>
+        <v>129910563</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>80055</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>516688</v>
+        <v>517167</v>
       </c>
       <c r="R69" t="n">
-        <v>6986695</v>
+        <v>6986122</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7707,39 +7707,35 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129908890</v>
+        <v>129910754</v>
       </c>
       <c r="B70" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7747,37 +7743,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>516676</v>
+        <v>516688</v>
       </c>
       <c r="R70" t="n">
-        <v>6986711</v>
+        <v>6986695</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7814,7 +7807,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På grovbarkad asp i granskog.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7823,85 +7816,55 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129910664</v>
+        <v>129908890</v>
       </c>
       <c r="B71" t="n">
-        <v>80221</v>
+        <v>80189</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7909,10 +7872,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>517231</v>
+        <v>516676</v>
       </c>
       <c r="R71" t="n">
-        <v>6986060</v>
+        <v>6986711</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7947,6 +7910,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På grovbarkad asp i granskog.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7956,6 +7924,31 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -7972,27 +7965,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129908908</v>
+        <v>129910664</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>80224</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8002,7 +7995,11 @@
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8010,10 +8007,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>516927</v>
+        <v>517231</v>
       </c>
       <c r="R72" t="n">
-        <v>6986311</v>
+        <v>6986060</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8057,31 +8054,6 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8098,10 +8070,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129908887</v>
+        <v>129908908</v>
       </c>
       <c r="B73" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8109,30 +8081,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8140,10 +8108,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>516880</v>
+        <v>516927</v>
       </c>
       <c r="R73" t="n">
-        <v>6986531</v>
+        <v>6986311</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8178,11 +8146,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8200,22 +8163,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8233,10 +8196,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129910563</v>
+        <v>129908887</v>
       </c>
       <c r="B74" t="n">
-        <v>80052</v>
+        <v>80189</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8244,34 +8207,41 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>517167</v>
+        <v>516880</v>
       </c>
       <c r="R74" t="n">
-        <v>6986122</v>
+        <v>6986531</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8306,6 +8276,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8315,6 +8290,31 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8334,7 +8334,7 @@
         <v>129908881</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>129910565</v>
       </c>
       <c r="B76" t="n">
-        <v>79167</v>
+        <v>79170</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>129910670</v>
       </c>
       <c r="B77" t="n">
-        <v>79337</v>
+        <v>79340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>129910600</v>
       </c>
       <c r="B78" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>129910583</v>
       </c>
       <c r="B79" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>129910633</v>
       </c>
       <c r="B80" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>129910541</v>
       </c>
       <c r="B81" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9052,61 +9052,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129908912</v>
+        <v>129910740</v>
       </c>
       <c r="B82" t="n">
-        <v>98707</v>
+        <v>80189</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>516929</v>
+        <v>517033</v>
       </c>
       <c r="R82" t="n">
-        <v>6986305</v>
+        <v>6986309</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9143,7 +9127,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>1 vinterståndare.</t>
+          <t>På torraka och låga av sälg</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9152,85 +9136,63 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129908894</v>
+        <v>129910749</v>
       </c>
       <c r="B83" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>517028</v>
+        <v>516929</v>
       </c>
       <c r="R83" t="n">
-        <v>6986324</v>
+        <v>6986288</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9265,45 +9227,34 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129910740</v>
+        <v>129910543</v>
       </c>
       <c r="B84" t="n">
-        <v>80186</v>
+        <v>83055</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9311,21 +9262,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9335,10 +9286,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>517033</v>
+        <v>517077</v>
       </c>
       <c r="R84" t="n">
-        <v>6986309</v>
+        <v>6986242</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9373,11 +9324,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På torraka och låga av sälg</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9390,22 +9336,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129910749</v>
+        <v>129910546</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9413,21 +9359,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9437,10 +9383,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>516929</v>
+        <v>517241</v>
       </c>
       <c r="R85" t="n">
-        <v>6986288</v>
+        <v>6986104</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9487,22 +9433,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129910543</v>
+        <v>129910602</v>
       </c>
       <c r="B86" t="n">
-        <v>83052</v>
+        <v>80189</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9510,21 +9456,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9534,10 +9480,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>517077</v>
+        <v>517146</v>
       </c>
       <c r="R86" t="n">
-        <v>6986242</v>
+        <v>6986161</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9596,10 +9542,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129910546</v>
+        <v>129910619</v>
       </c>
       <c r="B87" t="n">
-        <v>83052</v>
+        <v>80189</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9607,21 +9553,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9631,10 +9577,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>517241</v>
+        <v>517108</v>
       </c>
       <c r="R87" t="n">
-        <v>6986104</v>
+        <v>6986255</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9693,10 +9639,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129910602</v>
+        <v>129910647</v>
       </c>
       <c r="B88" t="n">
-        <v>80186</v>
+        <v>78841</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9704,21 +9650,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9728,10 +9674,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>517146</v>
+        <v>517081</v>
       </c>
       <c r="R88" t="n">
-        <v>6986161</v>
+        <v>6986186</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9790,32 +9736,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129910619</v>
+        <v>129910571</v>
       </c>
       <c r="B89" t="n">
-        <v>80186</v>
+        <v>80093</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9825,10 +9771,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>517108</v>
+        <v>517109</v>
       </c>
       <c r="R89" t="n">
-        <v>6986255</v>
+        <v>6986168</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9887,10 +9833,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129910647</v>
+        <v>129910636</v>
       </c>
       <c r="B90" t="n">
-        <v>78838</v>
+        <v>80189</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9898,21 +9844,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9922,10 +9868,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>517081</v>
+        <v>517228</v>
       </c>
       <c r="R90" t="n">
-        <v>6986186</v>
+        <v>6986059</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9984,32 +9930,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129910571</v>
+        <v>129910545</v>
       </c>
       <c r="B91" t="n">
-        <v>80090</v>
+        <v>83055</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10019,10 +9965,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>517109</v>
+        <v>517251</v>
       </c>
       <c r="R91" t="n">
-        <v>6986168</v>
+        <v>6986081</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10081,45 +10027,61 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129910636</v>
+        <v>129908912</v>
       </c>
       <c r="B92" t="n">
-        <v>80186</v>
+        <v>98711</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>517228</v>
+        <v>516929</v>
       </c>
       <c r="R92" t="n">
-        <v>6986059</v>
+        <v>6986305</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10154,14 +10116,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>1 vinterståndare.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10178,45 +10151,61 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129910545</v>
+        <v>129908894</v>
       </c>
       <c r="B93" t="n">
-        <v>83052</v>
+        <v>98794</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>517251</v>
+        <v>517028</v>
       </c>
       <c r="R93" t="n">
-        <v>6986081</v>
+        <v>6986324</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10251,14 +10240,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -10278,7 +10278,7 @@
         <v>129910554</v>
       </c>
       <c r="B94" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10385,10 +10385,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129910665</v>
+        <v>129910739</v>
       </c>
       <c r="B95" t="n">
-        <v>83044</v>
+        <v>80189</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10396,21 +10396,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10420,10 +10420,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>517165</v>
+        <v>517016</v>
       </c>
       <c r="R95" t="n">
-        <v>6986212</v>
+        <v>6986355</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10458,6 +10458,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>2 st sälgar, stående, oklart om levande</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -10470,44 +10475,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129910748</v>
+        <v>129910625</v>
       </c>
       <c r="B96" t="n">
-        <v>98790</v>
+        <v>80189</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10517,10 +10522,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>516692</v>
+        <v>517184</v>
       </c>
       <c r="R96" t="n">
-        <v>6986711</v>
+        <v>6986149</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10555,11 +10560,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10572,22 +10572,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129910739</v>
+        <v>129910626</v>
       </c>
       <c r="B97" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>517016</v>
+        <v>517169</v>
       </c>
       <c r="R97" t="n">
-        <v>6986355</v>
+        <v>6986147</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10657,11 +10657,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>2 st sälgar, stående, oklart om levande</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10674,22 +10669,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129910625</v>
+        <v>129910542</v>
       </c>
       <c r="B98" t="n">
-        <v>80186</v>
+        <v>83055</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10697,21 +10692,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10721,10 +10716,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>517184</v>
+        <v>517009</v>
       </c>
       <c r="R98" t="n">
-        <v>6986149</v>
+        <v>6986437</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10783,10 +10778,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129910626</v>
+        <v>129910665</v>
       </c>
       <c r="B99" t="n">
-        <v>80186</v>
+        <v>83047</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10794,21 +10789,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10818,10 +10813,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>517169</v>
+        <v>517165</v>
       </c>
       <c r="R99" t="n">
-        <v>6986147</v>
+        <v>6986212</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10880,32 +10875,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129910542</v>
+        <v>129910748</v>
       </c>
       <c r="B100" t="n">
-        <v>83052</v>
+        <v>98794</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10915,10 +10910,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>517009</v>
+        <v>516692</v>
       </c>
       <c r="R100" t="n">
-        <v>6986437</v>
+        <v>6986711</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10953,6 +10948,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -10965,57 +10965,60 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129910645</v>
+        <v>129908902</v>
       </c>
       <c r="B101" t="n">
-        <v>80057</v>
+        <v>79084</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>517286</v>
+        <v>516926</v>
       </c>
       <c r="R101" t="n">
-        <v>6986091</v>
+        <v>6986445</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11050,14 +11053,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11077,7 +11111,7 @@
         <v>129910590</v>
       </c>
       <c r="B102" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11174,7 +11208,7 @@
         <v>129910618</v>
       </c>
       <c r="B103" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11271,7 +11305,7 @@
         <v>129910593</v>
       </c>
       <c r="B104" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11368,7 +11402,7 @@
         <v>129908899</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11494,7 +11528,7 @@
         <v>129910622</v>
       </c>
       <c r="B106" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11588,10 +11622,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129908902</v>
+        <v>129908886</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11599,26 +11633,30 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11626,10 +11664,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>516926</v>
+        <v>517038</v>
       </c>
       <c r="R107" t="n">
-        <v>6986445</v>
+        <v>6986289</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11666,7 +11704,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>På levande sälg.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11678,31 +11716,6 @@
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11719,52 +11732,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129908886</v>
+        <v>129910645</v>
       </c>
       <c r="B108" t="n">
-        <v>80186</v>
+        <v>80060</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>389</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>517038</v>
+        <v>517286</v>
       </c>
       <c r="R108" t="n">
-        <v>6986289</v>
+        <v>6986091</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11799,18 +11805,12 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På levande sälg.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11829,41 +11829,37 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129910661</v>
+        <v>129910652</v>
       </c>
       <c r="B109" t="n">
-        <v>92194</v>
+        <v>79084</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11871,10 +11867,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>517220</v>
+        <v>517345</v>
       </c>
       <c r="R109" t="n">
-        <v>6986131</v>
+        <v>6986186</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11921,17 +11917,17 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -11949,39 +11945,39 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129908911</v>
+        <v>129910661</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>92197</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -11991,10 +11987,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>516729</v>
+        <v>517220</v>
       </c>
       <c r="R110" t="n">
-        <v>6986683</v>
+        <v>6986131</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12029,11 +12025,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På gran med apothecier.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12044,29 +12035,19 @@
       <c r="AG110" t="b">
         <v>0</v>
       </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12084,10 +12065,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129910743</v>
+        <v>129908911</v>
       </c>
       <c r="B111" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12095,34 +12076,41 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>516874</v>
+        <v>516729</v>
       </c>
       <c r="R111" t="n">
-        <v>6986542</v>
+        <v>6986683</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12159,7 +12147,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Liggande död sälg</t>
+          <t>På gran med apothecier.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12168,28 +12156,54 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129910652</v>
+        <v>129910743</v>
       </c>
       <c r="B112" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12197,37 +12211,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>517345</v>
+        <v>516874</v>
       </c>
       <c r="R112" t="n">
-        <v>6986186</v>
+        <v>6986542</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12262,40 +12273,29 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Liggande död sälg</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12305,7 +12305,7 @@
         <v>129910627</v>
       </c>
       <c r="B113" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>129910603</v>
       </c>
       <c r="B114" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12496,45 +12496,53 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129910644</v>
+        <v>129910553</v>
       </c>
       <c r="B115" t="n">
-        <v>80057</v>
+        <v>57737</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>389</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>517289</v>
+        <v>516968</v>
       </c>
       <c r="R115" t="n">
-        <v>6986084</v>
+        <v>6986277</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12567,6 +12575,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12593,53 +12606,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129910553</v>
+        <v>129910644</v>
       </c>
       <c r="B116" t="n">
-        <v>57736</v>
+        <v>80060</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>389</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>516968</v>
+        <v>517289</v>
       </c>
       <c r="R116" t="n">
-        <v>6986277</v>
+        <v>6986084</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12672,11 +12677,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12706,7 +12706,7 @@
         <v>129910638</v>
       </c>
       <c r="B117" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>129910738</v>
       </c>
       <c r="B118" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>129908885</v>
       </c>
       <c r="B119" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>129908889</v>
       </c>
       <c r="B120" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13172,10 +13172,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129910640</v>
+        <v>129910569</v>
       </c>
       <c r="B121" t="n">
-        <v>80186</v>
+        <v>80190</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13183,21 +13183,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>517288</v>
+        <v>517277</v>
       </c>
       <c r="R121" t="n">
         <v>6986118</v>
@@ -13269,45 +13269,52 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129910621</v>
+        <v>129910562</v>
       </c>
       <c r="B122" t="n">
-        <v>80186</v>
+        <v>91613</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>517170</v>
+        <v>517126</v>
       </c>
       <c r="R122" t="n">
-        <v>6986215</v>
+        <v>6986211</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13348,8 +13355,24 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
@@ -13366,10 +13389,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129910753</v>
+        <v>129910640</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13377,21 +13400,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13401,10 +13424,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>516914</v>
+        <v>517288</v>
       </c>
       <c r="R123" t="n">
-        <v>6986518</v>
+        <v>6986118</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13439,11 +13462,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>På granar</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -13456,22 +13474,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129910635</v>
+        <v>129910621</v>
       </c>
       <c r="B124" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13503,10 +13521,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>517229</v>
+        <v>517170</v>
       </c>
       <c r="R124" t="n">
-        <v>6986063</v>
+        <v>6986215</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13565,10 +13583,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129910605</v>
+        <v>129910753</v>
       </c>
       <c r="B125" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13576,21 +13594,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13600,10 +13618,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>517273</v>
+        <v>516914</v>
       </c>
       <c r="R125" t="n">
-        <v>6986075</v>
+        <v>6986518</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13638,6 +13656,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>På granar</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -13650,44 +13673,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129910566</v>
+        <v>129910635</v>
       </c>
       <c r="B126" t="n">
-        <v>79167</v>
+        <v>80189</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13697,10 +13720,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>517128</v>
+        <v>517229</v>
       </c>
       <c r="R126" t="n">
-        <v>6986180</v>
+        <v>6986063</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13759,61 +13782,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129908895</v>
+        <v>129910605</v>
       </c>
       <c r="B127" t="n">
-        <v>98790</v>
+        <v>80189</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>516927</v>
+        <v>517273</v>
       </c>
       <c r="R127" t="n">
-        <v>6986523</v>
+        <v>6986075</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13848,25 +13855,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor och 3 vinterståndare inom ca 3 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
@@ -13883,32 +13879,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129910569</v>
+        <v>129910566</v>
       </c>
       <c r="B128" t="n">
-        <v>80187</v>
+        <v>79170</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>6450</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13918,10 +13914,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>517277</v>
+        <v>517128</v>
       </c>
       <c r="R128" t="n">
-        <v>6986118</v>
+        <v>6986180</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13980,52 +13976,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129910562</v>
+        <v>129910637</v>
       </c>
       <c r="B129" t="n">
-        <v>91610</v>
+        <v>80189</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>517126</v>
+        <v>517251</v>
       </c>
       <c r="R129" t="n">
-        <v>6986211</v>
+        <v>6986087</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14066,24 +14055,8 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
@@ -14100,45 +14073,61 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129910637</v>
+        <v>129908895</v>
       </c>
       <c r="B130" t="n">
-        <v>80186</v>
+        <v>98794</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>517251</v>
+        <v>516927</v>
       </c>
       <c r="R130" t="n">
-        <v>6986087</v>
+        <v>6986523</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14173,14 +14162,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor och 3 vinterståndare inom ca 3 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -14197,45 +14197,52 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129910624</v>
+        <v>129910659</v>
       </c>
       <c r="B131" t="n">
-        <v>80186</v>
+        <v>92884</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>517195</v>
+        <v>517328</v>
       </c>
       <c r="R131" t="n">
-        <v>6986175</v>
+        <v>6986156</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14276,6 +14283,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14294,45 +14302,57 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129910572</v>
+        <v>129908893</v>
       </c>
       <c r="B132" t="n">
-        <v>80090</v>
+        <v>98794</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>517147</v>
+        <v>516958</v>
       </c>
       <c r="R132" t="n">
-        <v>6986129</v>
+        <v>6986409</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14367,14 +14387,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i barrblandskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
@@ -14391,10 +14422,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129908893</v>
+        <v>129908897</v>
       </c>
       <c r="B133" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14421,7 +14452,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14429,7 +14460,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
@@ -14438,10 +14473,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>516958</v>
+        <v>516696</v>
       </c>
       <c r="R133" t="n">
-        <v>6986409</v>
+        <v>6986696</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14478,7 +14513,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i barrblandskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+          <t>Minst 20 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14493,7 +14528,7 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -14511,50 +14546,41 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129908897</v>
+        <v>129910551</v>
       </c>
       <c r="B134" t="n">
-        <v>98790</v>
+        <v>91602</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14562,10 +14588,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>516696</v>
+        <v>517014</v>
       </c>
       <c r="R134" t="n">
-        <v>6986696</v>
+        <v>6986339</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14600,11 +14626,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Minst 20 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14615,9 +14636,24 @@
       <c r="AG134" t="b">
         <v>0</v>
       </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -14635,52 +14671,61 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129910551</v>
+        <v>129910560</v>
       </c>
       <c r="B135" t="n">
-        <v>91599</v>
+        <v>58372</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>102125</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>517014</v>
+        <v>517237</v>
       </c>
       <c r="R135" t="n">
-        <v>6986339</v>
+        <v>6986082</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14721,29 +14766,8 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
@@ -14760,61 +14784,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129910560</v>
+        <v>129910584</v>
       </c>
       <c r="B136" t="n">
-        <v>58369</v>
+        <v>80189</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>517237</v>
+        <v>517004</v>
       </c>
       <c r="R136" t="n">
-        <v>6986082</v>
+        <v>6986361</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14873,10 +14881,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129910584</v>
+        <v>129910594</v>
       </c>
       <c r="B137" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14908,10 +14916,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>517004</v>
+        <v>517165</v>
       </c>
       <c r="R137" t="n">
-        <v>6986361</v>
+        <v>6986222</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14970,10 +14978,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129910594</v>
+        <v>129910624</v>
       </c>
       <c r="B138" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15005,10 +15013,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>517165</v>
+        <v>517195</v>
       </c>
       <c r="R138" t="n">
-        <v>6986222</v>
+        <v>6986175</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15070,7 +15078,7 @@
         <v>129910747</v>
       </c>
       <c r="B139" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15172,7 +15180,7 @@
         <v>129910634</v>
       </c>
       <c r="B140" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15266,10 +15274,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129910659</v>
+        <v>129910572</v>
       </c>
       <c r="B141" t="n">
-        <v>92881</v>
+        <v>80093</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15277,41 +15285,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>517328</v>
+        <v>517147</v>
       </c>
       <c r="R141" t="n">
-        <v>6986156</v>
+        <v>6986129</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15352,7 +15353,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15374,7 +15374,7 @@
         <v>129910656</v>
       </c>
       <c r="B142" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15468,45 +15468,57 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129910570</v>
+        <v>129908879</v>
       </c>
       <c r="B143" t="n">
-        <v>80090</v>
+        <v>57737</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>517172</v>
+        <v>516930</v>
       </c>
       <c r="R143" t="n">
-        <v>6986122</v>
+        <v>6986299</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15541,6 +15553,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
@@ -15549,6 +15566,31 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
@@ -15565,48 +15607,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129910651</v>
+        <v>129910570</v>
       </c>
       <c r="B144" t="n">
-        <v>79081</v>
+        <v>80093</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>517137</v>
+        <v>517172</v>
       </c>
       <c r="R144" t="n">
-        <v>6986150</v>
+        <v>6986122</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15647,24 +15686,8 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
@@ -15681,10 +15704,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129910639</v>
+        <v>129910651</v>
       </c>
       <c r="B145" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15692,30 +15715,26 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -15723,10 +15742,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>517276</v>
+        <v>517137</v>
       </c>
       <c r="R145" t="n">
-        <v>6986120</v>
+        <v>6986150</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15761,11 +15780,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apotechier.</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -15775,6 +15789,21 @@
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -15791,10 +15820,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129910608</v>
+        <v>129910639</v>
       </c>
       <c r="B146" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15820,16 +15849,23 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>517230</v>
+        <v>517276</v>
       </c>
       <c r="R146" t="n">
-        <v>6986231</v>
+        <v>6986120</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15864,12 +15900,18 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apotechier.</t>
+        </is>
+      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15888,10 +15930,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129910582</v>
+        <v>129910608</v>
       </c>
       <c r="B147" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15923,10 +15965,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>517009</v>
+        <v>517230</v>
       </c>
       <c r="R147" t="n">
-        <v>6986366</v>
+        <v>6986231</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15985,10 +16027,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129908879</v>
+        <v>129910582</v>
       </c>
       <c r="B148" t="n">
-        <v>57736</v>
+        <v>80189</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15996,46 +16038,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>516930</v>
+        <v>517009</v>
       </c>
       <c r="R148" t="n">
-        <v>6986299</v>
+        <v>6986366</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16070,11 +16100,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -16083,31 +16108,6 @@
       </c>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -16124,57 +16124,61 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129908882</v>
+        <v>129910648</v>
       </c>
       <c r="B149" t="n">
-        <v>57736</v>
+        <v>98794</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>516646</v>
+        <v>517224</v>
       </c>
       <c r="R149" t="n">
-        <v>6986735</v>
+        <v>6986227</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16211,7 +16215,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
+          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16220,33 +16224,9 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -16263,10 +16243,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129910662</v>
+        <v>129908882</v>
       </c>
       <c r="B150" t="n">
-        <v>88998</v>
+        <v>57737</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16274,34 +16254,46 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>517336</v>
+        <v>516646</v>
       </c>
       <c r="R150" t="n">
-        <v>6986195</v>
+        <v>6986735</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16336,6 +16328,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -16344,6 +16341,31 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -16360,10 +16382,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129910607</v>
+        <v>129908900</v>
       </c>
       <c r="B151" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16371,34 +16393,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>517246</v>
+        <v>516960</v>
       </c>
       <c r="R151" t="n">
-        <v>6986091</v>
+        <v>6986352</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16433,14 +16458,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal gran.</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16457,10 +16513,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129908900</v>
+        <v>129910662</v>
       </c>
       <c r="B152" t="n">
-        <v>79081</v>
+        <v>89001</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16468,37 +16524,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>516960</v>
+        <v>517336</v>
       </c>
       <c r="R152" t="n">
-        <v>6986352</v>
+        <v>6986195</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16533,45 +16586,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal gran.</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16588,10 +16610,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129908909</v>
+        <v>129910607</v>
       </c>
       <c r="B153" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16599,37 +16621,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>516915</v>
+        <v>517246</v>
       </c>
       <c r="R153" t="n">
-        <v>6986509</v>
+        <v>6986091</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16670,34 +16689,8 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
@@ -16714,10 +16707,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129908903</v>
+        <v>129908909</v>
       </c>
       <c r="B154" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16752,10 +16745,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>516956</v>
+        <v>516915</v>
       </c>
       <c r="R154" t="n">
-        <v>6986419</v>
+        <v>6986509</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16790,11 +16783,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>På bark av tall.</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -16807,27 +16795,27 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -16845,10 +16833,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129910587</v>
+        <v>129908903</v>
       </c>
       <c r="B155" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16856,34 +16844,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>517018</v>
+        <v>516956</v>
       </c>
       <c r="R155" t="n">
-        <v>6986301</v>
+        <v>6986419</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16918,14 +16909,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>På bark av tall.</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -16942,10 +16964,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129910609</v>
+        <v>129910587</v>
       </c>
       <c r="B156" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16977,10 +16999,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>517221</v>
+        <v>517018</v>
       </c>
       <c r="R156" t="n">
-        <v>6986213</v>
+        <v>6986301</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17039,10 +17061,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129910745</v>
+        <v>129910609</v>
       </c>
       <c r="B157" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17074,10 +17096,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>516739</v>
+        <v>517221</v>
       </c>
       <c r="R157" t="n">
-        <v>6986664</v>
+        <v>6986213</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17112,11 +17134,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>På stående död sälg</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -17129,73 +17146,57 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129910648</v>
+        <v>129910745</v>
       </c>
       <c r="B158" t="n">
-        <v>98790</v>
+        <v>80189</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>517224</v>
+        <v>516739</v>
       </c>
       <c r="R158" t="n">
-        <v>6986227</v>
+        <v>6986664</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17232,7 +17233,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
+          <t>På stående död sälg</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17241,29 +17242,28 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910558</v>
+        <v>129910548</v>
       </c>
       <c r="B159" t="n">
-        <v>57736</v>
+        <v>97040</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17271,42 +17271,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>517356</v>
+        <v>517167</v>
       </c>
       <c r="R159" t="n">
-        <v>6986190</v>
+        <v>6986105</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17339,11 +17331,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17370,10 +17357,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910550</v>
+        <v>129910558</v>
       </c>
       <c r="B160" t="n">
-        <v>90631</v>
+        <v>57737</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17381,34 +17368,42 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>517343</v>
+        <v>517356</v>
       </c>
       <c r="R160" t="n">
-        <v>6986165</v>
+        <v>6986190</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17441,6 +17436,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17467,10 +17467,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910548</v>
+        <v>129910550</v>
       </c>
       <c r="B161" t="n">
-        <v>97036</v>
+        <v>90634</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17478,21 +17478,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>53</v>
+        <v>1962</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17502,10 +17502,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>517167</v>
+        <v>517343</v>
       </c>
       <c r="R161" t="n">
-        <v>6986105</v>
+        <v>6986165</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17567,7 +17567,7 @@
         <v>129908910</v>
       </c>
       <c r="B162" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>129910744</v>
       </c>
       <c r="B163" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>129910611</v>
       </c>
       <c r="B164" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>129910598</v>
       </c>
       <c r="B165" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>129910628</v>
       </c>
       <c r="B166" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>129908904</v>
       </c>
       <c r="B167" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>129910669</v>
       </c>
       <c r="B168" t="n">
-        <v>79337</v>
+        <v>79340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>129910586</v>
       </c>
       <c r="B169" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>129910616</v>
       </c>
       <c r="B170" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>129910576</v>
       </c>
       <c r="B171" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>129910623</v>
       </c>
       <c r="B172" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>129908907</v>
       </c>
       <c r="B173" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>129921270</v>
       </c>
       <c r="B174" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>129921278</v>
       </c>
       <c r="B175" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>129921263</v>
       </c>
       <c r="B176" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>129921277</v>
       </c>
       <c r="B177" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>129921267</v>
       </c>
       <c r="B178" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>129921275</v>
       </c>
       <c r="B179" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>129921276</v>
       </c>
       <c r="B180" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>129921280</v>
       </c>
       <c r="B181" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>129921271</v>
       </c>
       <c r="B182" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>129921272</v>
       </c>
       <c r="B183" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>129921265</v>
       </c>
       <c r="B184" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>129921274</v>
       </c>
       <c r="B185" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129910666</v>
+        <v>129910557</v>
       </c>
       <c r="B8" t="n">
-        <v>81147</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,34 +1343,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229558</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517120</v>
+        <v>517175</v>
       </c>
       <c r="R8" t="n">
-        <v>6986257</v>
+        <v>6986155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,6 +1411,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129910557</v>
+        <v>129910556</v>
       </c>
       <c r="B9" t="n">
         <v>57737</v>
@@ -1472,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517175</v>
+        <v>517169</v>
       </c>
       <c r="R9" t="n">
-        <v>6986155</v>
+        <v>6986201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129910556</v>
+        <v>129910642</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>78097</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,42 +1563,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517169</v>
+        <v>517251</v>
       </c>
       <c r="R10" t="n">
-        <v>6986201</v>
+        <v>6986078</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,11 +1623,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129910642</v>
+        <v>129910666</v>
       </c>
       <c r="B11" t="n">
-        <v>78097</v>
+        <v>81147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>229558</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517251</v>
+        <v>517120</v>
       </c>
       <c r="R11" t="n">
-        <v>6986078</v>
+        <v>6986257</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129910555</v>
+        <v>129908878</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,29 +1757,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1789,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517025</v>
+        <v>516921</v>
       </c>
       <c r="R12" t="n">
-        <v>6986271</v>
+        <v>6986515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,7 +1828,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>I en granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,8 +1837,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1856,52 +1881,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129908878</v>
+        <v>129910643</v>
       </c>
       <c r="B13" t="n">
-        <v>91602</v>
+        <v>80060</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>389</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516921</v>
+        <v>517173</v>
       </c>
       <c r="R13" t="n">
-        <v>6986515</v>
+        <v>6986129</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,45 +1954,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I en granlåga i granskog.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1991,45 +1978,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129910643</v>
+        <v>129910555</v>
       </c>
       <c r="B14" t="n">
-        <v>80060</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>389</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517173</v>
+        <v>517025</v>
       </c>
       <c r="R14" t="n">
-        <v>6986129</v>
+        <v>6986271</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,6 +2057,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2670,10 +2670,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129910579</v>
+        <v>129908906</v>
       </c>
       <c r="B21" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2681,34 +2681,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517061</v>
+        <v>517038</v>
       </c>
       <c r="R21" t="n">
-        <v>6986424</v>
+        <v>6986336</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,8 +2752,34 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2767,7 +2796,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129910615</v>
+        <v>129910579</v>
       </c>
       <c r="B22" t="n">
         <v>80189</v>
@@ -2802,10 +2831,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517004</v>
+        <v>517061</v>
       </c>
       <c r="R22" t="n">
-        <v>6986426</v>
+        <v>6986424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2864,7 +2893,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129910742</v>
+        <v>129910615</v>
       </c>
       <c r="B23" t="n">
         <v>80189</v>
@@ -2899,10 +2928,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>516904</v>
+        <v>517004</v>
       </c>
       <c r="R23" t="n">
-        <v>6986470</v>
+        <v>6986426</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,11 +2966,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2954,19 +2978,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129910613</v>
+        <v>129910742</v>
       </c>
       <c r="B24" t="n">
         <v>80189</v>
@@ -3001,10 +3025,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517125</v>
+        <v>516904</v>
       </c>
       <c r="R24" t="n">
-        <v>6986172</v>
+        <v>6986470</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,6 +3063,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Lunglav på asp</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3051,22 +3080,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129908906</v>
+        <v>129910613</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,37 +3103,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517038</v>
+        <v>517125</v>
       </c>
       <c r="R25" t="n">
-        <v>6986336</v>
+        <v>6986172</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,34 +3171,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129908880</v>
+        <v>129910564</v>
       </c>
       <c r="B27" t="n">
-        <v>57737</v>
+        <v>80055</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,46 +3302,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>388</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>516686</v>
+        <v>517170</v>
       </c>
       <c r="R27" t="n">
-        <v>6986687</v>
+        <v>6986124</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3376,44 +3364,15 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3430,7 +3389,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129910592</v>
+        <v>129910580</v>
       </c>
       <c r="B28" t="n">
         <v>80189</v>
@@ -3465,10 +3424,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517119</v>
+        <v>517047</v>
       </c>
       <c r="R28" t="n">
-        <v>6986251</v>
+        <v>6986415</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,10 +3486,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129910649</v>
+        <v>129910610</v>
       </c>
       <c r="B29" t="n">
-        <v>56918</v>
+        <v>80189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3538,50 +3497,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517134</v>
+        <v>517211</v>
       </c>
       <c r="R29" t="n">
-        <v>6986204</v>
+        <v>6986211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3640,7 +3583,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129910580</v>
+        <v>129910599</v>
       </c>
       <c r="B30" t="n">
         <v>80189</v>
@@ -3675,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>517047</v>
+        <v>517177</v>
       </c>
       <c r="R30" t="n">
-        <v>6986415</v>
+        <v>6986167</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3737,7 +3680,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129910610</v>
+        <v>129910620</v>
       </c>
       <c r="B31" t="n">
         <v>80189</v>
@@ -3772,10 +3715,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>517211</v>
+        <v>517112</v>
       </c>
       <c r="R31" t="n">
-        <v>6986211</v>
+        <v>6986273</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,32 +3777,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129910599</v>
+        <v>129910668</v>
       </c>
       <c r="B32" t="n">
-        <v>80189</v>
+        <v>79340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3869,10 +3812,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517177</v>
+        <v>517042</v>
       </c>
       <c r="R32" t="n">
-        <v>6986167</v>
+        <v>6986262</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3931,7 +3874,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129910620</v>
+        <v>129910631</v>
       </c>
       <c r="B33" t="n">
         <v>80189</v>
@@ -3966,10 +3909,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517112</v>
+        <v>517287</v>
       </c>
       <c r="R33" t="n">
-        <v>6986273</v>
+        <v>6986080</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4028,32 +3971,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129910668</v>
+        <v>129910601</v>
       </c>
       <c r="B34" t="n">
-        <v>79340</v>
+        <v>80189</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4063,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517042</v>
+        <v>517170</v>
       </c>
       <c r="R34" t="n">
-        <v>6986262</v>
+        <v>6986161</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4125,7 +4068,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129910631</v>
+        <v>129910592</v>
       </c>
       <c r="B35" t="n">
         <v>80189</v>
@@ -4160,10 +4103,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517287</v>
+        <v>517119</v>
       </c>
       <c r="R35" t="n">
-        <v>6986080</v>
+        <v>6986251</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4222,10 +4165,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129910601</v>
+        <v>129908880</v>
       </c>
       <c r="B36" t="n">
-        <v>80189</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4233,34 +4176,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517170</v>
+        <v>516686</v>
       </c>
       <c r="R36" t="n">
-        <v>6986161</v>
+        <v>6986687</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4295,6 +4250,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4303,6 +4263,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4319,10 +4304,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129910564</v>
+        <v>129910649</v>
       </c>
       <c r="B37" t="n">
-        <v>80055</v>
+        <v>56918</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4330,34 +4315,50 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>388</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>517170</v>
+        <v>517134</v>
       </c>
       <c r="R37" t="n">
-        <v>6986124</v>
+        <v>6986204</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4398,7 +4399,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5340,10 +5340,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129910547</v>
+        <v>129910559</v>
       </c>
       <c r="B47" t="n">
-        <v>97040</v>
+        <v>57895</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5351,34 +5351,50 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>517122</v>
+        <v>517266</v>
       </c>
       <c r="R47" t="n">
-        <v>6986191</v>
+        <v>6986055</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5437,10 +5453,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129910568</v>
+        <v>129910547</v>
       </c>
       <c r="B48" t="n">
-        <v>80190</v>
+        <v>97040</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5448,21 +5464,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5488,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>517230</v>
+        <v>517122</v>
       </c>
       <c r="R48" t="n">
-        <v>6986059</v>
+        <v>6986191</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5550,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129910632</v>
+        <v>129910568</v>
       </c>
       <c r="B49" t="n">
-        <v>80189</v>
+        <v>80190</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5561,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5585,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>517285</v>
+        <v>517230</v>
       </c>
       <c r="R49" t="n">
-        <v>6986090</v>
+        <v>6986059</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,7 +5647,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129910591</v>
+        <v>129910632</v>
       </c>
       <c r="B50" t="n">
         <v>80189</v>
@@ -5666,10 +5682,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>517068</v>
+        <v>517285</v>
       </c>
       <c r="R50" t="n">
-        <v>6986257</v>
+        <v>6986090</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,10 +5744,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129910750</v>
+        <v>129910591</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5739,21 +5755,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5779,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>517017</v>
+        <v>517068</v>
       </c>
       <c r="R51" t="n">
-        <v>6986332</v>
+        <v>6986257</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5801,11 +5817,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5818,22 +5829,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129910559</v>
+        <v>129910750</v>
       </c>
       <c r="B52" t="n">
-        <v>57895</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5841,50 +5852,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>517266</v>
+        <v>517017</v>
       </c>
       <c r="R52" t="n">
-        <v>6986055</v>
+        <v>6986332</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5919,6 +5914,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5931,12 +5931,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6467,27 +6467,27 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129910663</v>
+        <v>129910653</v>
       </c>
       <c r="B58" t="n">
-        <v>80224</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6497,11 +6497,7 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6509,10 +6505,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>517007</v>
+        <v>516971</v>
       </c>
       <c r="R58" t="n">
-        <v>6986367</v>
+        <v>6986287</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6547,6 +6543,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6556,6 +6557,21 @@
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -6572,45 +6588,52 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129910573</v>
+        <v>129910663</v>
       </c>
       <c r="B59" t="n">
-        <v>75180</v>
+        <v>80224</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1460</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>517112</v>
+        <v>517007</v>
       </c>
       <c r="R59" t="n">
-        <v>6986241</v>
+        <v>6986367</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6651,6 +6674,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6669,10 +6693,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129910653</v>
+        <v>129910573</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>75180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6680,37 +6704,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>516971</v>
+        <v>517112</v>
       </c>
       <c r="R60" t="n">
-        <v>6986287</v>
+        <v>6986241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6745,35 +6766,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6790,10 +6790,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129908901</v>
+        <v>129910604</v>
       </c>
       <c r="B61" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6801,37 +6801,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>516936</v>
+        <v>517211</v>
       </c>
       <c r="R61" t="n">
-        <v>6986463</v>
+        <v>6986077</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6872,34 +6869,8 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6916,7 +6887,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129910604</v>
+        <v>129908888</v>
       </c>
       <c r="B62" t="n">
         <v>80189</v>
@@ -6945,16 +6916,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>517211</v>
+        <v>516854</v>
       </c>
       <c r="R62" t="n">
-        <v>6986077</v>
+        <v>6986558</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6989,14 +6963,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7013,7 +7018,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129908888</v>
+        <v>129910746</v>
       </c>
       <c r="B63" t="n">
         <v>80189</v>
@@ -7042,19 +7047,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>516854</v>
+        <v>516690</v>
       </c>
       <c r="R63" t="n">
-        <v>6986558</v>
+        <v>6986709</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7091,7 +7093,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7100,51 +7102,25 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129910746</v>
+        <v>129910595</v>
       </c>
       <c r="B64" t="n">
         <v>80189</v>
@@ -7179,10 +7155,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>516690</v>
+        <v>517169</v>
       </c>
       <c r="R64" t="n">
-        <v>6986709</v>
+        <v>6986203</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7217,11 +7193,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7234,19 +7205,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129910595</v>
+        <v>129910617</v>
       </c>
       <c r="B65" t="n">
         <v>80189</v>
@@ -7281,10 +7252,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>517169</v>
+        <v>517040</v>
       </c>
       <c r="R65" t="n">
-        <v>6986203</v>
+        <v>6986263</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7343,7 +7314,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129910617</v>
+        <v>129910575</v>
       </c>
       <c r="B66" t="n">
         <v>80189</v>
@@ -7378,10 +7349,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>517040</v>
+        <v>516969</v>
       </c>
       <c r="R66" t="n">
-        <v>6986263</v>
+        <v>6986323</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7440,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129910575</v>
+        <v>129908901</v>
       </c>
       <c r="B67" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7451,34 +7422,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>516969</v>
+        <v>516936</v>
       </c>
       <c r="R67" t="n">
-        <v>6986323</v>
+        <v>6986463</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7519,8 +7493,34 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8331,57 +8331,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129908881</v>
+        <v>129910565</v>
       </c>
       <c r="B75" t="n">
-        <v>57737</v>
+        <v>79170</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>516659</v>
+        <v>517235</v>
       </c>
       <c r="R75" t="n">
-        <v>6986705</v>
+        <v>6986250</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8416,11 +8404,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8429,31 +8412,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8470,10 +8428,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129910565</v>
+        <v>129910670</v>
       </c>
       <c r="B76" t="n">
-        <v>79170</v>
+        <v>79340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8481,21 +8439,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6450</v>
+        <v>6459</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8505,10 +8463,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>517235</v>
+        <v>517175</v>
       </c>
       <c r="R76" t="n">
-        <v>6986250</v>
+        <v>6986169</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8567,32 +8525,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129910670</v>
+        <v>129910600</v>
       </c>
       <c r="B77" t="n">
-        <v>79340</v>
+        <v>80189</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8602,10 +8560,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>517175</v>
+        <v>517181</v>
       </c>
       <c r="R77" t="n">
-        <v>6986169</v>
+        <v>6986168</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8664,7 +8622,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129910600</v>
+        <v>129910583</v>
       </c>
       <c r="B78" t="n">
         <v>80189</v>
@@ -8699,10 +8657,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>517181</v>
+        <v>517001</v>
       </c>
       <c r="R78" t="n">
-        <v>6986168</v>
+        <v>6986369</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8761,7 +8719,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129910583</v>
+        <v>129910633</v>
       </c>
       <c r="B79" t="n">
         <v>80189</v>
@@ -8796,10 +8754,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>517001</v>
+        <v>517235</v>
       </c>
       <c r="R79" t="n">
-        <v>6986369</v>
+        <v>6986077</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,10 +8816,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129910633</v>
+        <v>129910541</v>
       </c>
       <c r="B80" t="n">
-        <v>80189</v>
+        <v>83055</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8869,21 +8827,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8893,10 +8851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>517235</v>
+        <v>517005</v>
       </c>
       <c r="R80" t="n">
-        <v>6986077</v>
+        <v>6986418</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8955,10 +8913,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129910541</v>
+        <v>129908881</v>
       </c>
       <c r="B81" t="n">
-        <v>83055</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8966,34 +8924,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>517005</v>
+        <v>516659</v>
       </c>
       <c r="R81" t="n">
-        <v>6986418</v>
+        <v>6986705</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9028,6 +8998,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9036,6 +9011,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9052,45 +9052,61 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129910740</v>
+        <v>129908912</v>
       </c>
       <c r="B82" t="n">
-        <v>80189</v>
+        <v>98711</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>517033</v>
+        <v>516929</v>
       </c>
       <c r="R82" t="n">
-        <v>6986309</v>
+        <v>6986305</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9127,7 +9143,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På torraka och låga av sälg</t>
+          <t>1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9136,28 +9152,34 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129910749</v>
+        <v>129910740</v>
       </c>
       <c r="B83" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9165,21 +9187,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9189,10 +9211,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>516929</v>
+        <v>517033</v>
       </c>
       <c r="R83" t="n">
-        <v>6986288</v>
+        <v>6986309</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9225,6 +9247,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På torraka och låga av sälg</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9251,10 +9278,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129910543</v>
+        <v>129910749</v>
       </c>
       <c r="B84" t="n">
-        <v>83055</v>
+        <v>79084</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9262,21 +9289,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9286,10 +9313,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>517077</v>
+        <v>516929</v>
       </c>
       <c r="R84" t="n">
-        <v>6986242</v>
+        <v>6986288</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9336,19 +9363,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129910546</v>
+        <v>129910543</v>
       </c>
       <c r="B85" t="n">
         <v>83055</v>
@@ -9383,10 +9410,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>517241</v>
+        <v>517077</v>
       </c>
       <c r="R85" t="n">
-        <v>6986104</v>
+        <v>6986242</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9445,10 +9472,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129910602</v>
+        <v>129910546</v>
       </c>
       <c r="B86" t="n">
-        <v>80189</v>
+        <v>83055</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9456,21 +9483,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9480,10 +9507,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>517146</v>
+        <v>517241</v>
       </c>
       <c r="R86" t="n">
-        <v>6986161</v>
+        <v>6986104</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9542,7 +9569,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129910619</v>
+        <v>129910602</v>
       </c>
       <c r="B87" t="n">
         <v>80189</v>
@@ -9577,10 +9604,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>517108</v>
+        <v>517146</v>
       </c>
       <c r="R87" t="n">
-        <v>6986255</v>
+        <v>6986161</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9639,10 +9666,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129910647</v>
+        <v>129910619</v>
       </c>
       <c r="B88" t="n">
-        <v>78841</v>
+        <v>80189</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9650,21 +9677,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9674,10 +9701,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>517081</v>
+        <v>517108</v>
       </c>
       <c r="R88" t="n">
-        <v>6986186</v>
+        <v>6986255</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9736,32 +9763,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129910571</v>
+        <v>129910647</v>
       </c>
       <c r="B89" t="n">
-        <v>80093</v>
+        <v>78841</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9771,10 +9798,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>517109</v>
+        <v>517081</v>
       </c>
       <c r="R89" t="n">
-        <v>6986168</v>
+        <v>6986186</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9833,32 +9860,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129910636</v>
+        <v>129910571</v>
       </c>
       <c r="B90" t="n">
-        <v>80189</v>
+        <v>80093</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9868,10 +9895,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>517228</v>
+        <v>517109</v>
       </c>
       <c r="R90" t="n">
-        <v>6986059</v>
+        <v>6986168</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9930,10 +9957,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129910545</v>
+        <v>129910636</v>
       </c>
       <c r="B91" t="n">
-        <v>83055</v>
+        <v>80189</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9941,21 +9968,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9965,10 +9992,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>517251</v>
+        <v>517228</v>
       </c>
       <c r="R91" t="n">
-        <v>6986081</v>
+        <v>6986059</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10027,61 +10054,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129908912</v>
+        <v>129910545</v>
       </c>
       <c r="B92" t="n">
-        <v>98711</v>
+        <v>83055</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219790</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>516929</v>
+        <v>517251</v>
       </c>
       <c r="R92" t="n">
-        <v>6986305</v>
+        <v>6986081</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10116,25 +10127,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>1 vinterståndare.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10275,10 +10275,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129910554</v>
+        <v>129910665</v>
       </c>
       <c r="B94" t="n">
-        <v>57737</v>
+        <v>83047</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10286,42 +10286,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>516949</v>
+        <v>517165</v>
       </c>
       <c r="R94" t="n">
-        <v>6986325</v>
+        <v>6986212</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10354,11 +10346,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10778,10 +10765,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129910665</v>
+        <v>129910554</v>
       </c>
       <c r="B99" t="n">
-        <v>83047</v>
+        <v>57737</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10789,34 +10776,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>517165</v>
+        <v>516949</v>
       </c>
       <c r="R99" t="n">
-        <v>6986212</v>
+        <v>6986325</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10849,6 +10844,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10977,48 +10977,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129908902</v>
+        <v>129910645</v>
       </c>
       <c r="B101" t="n">
-        <v>79084</v>
+        <v>80060</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>516926</v>
+        <v>517286</v>
       </c>
       <c r="R101" t="n">
-        <v>6986445</v>
+        <v>6986091</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11053,45 +11050,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11622,10 +11588,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129908886</v>
+        <v>129908902</v>
       </c>
       <c r="B107" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11633,30 +11599,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11664,10 +11626,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>517038</v>
+        <v>516926</v>
       </c>
       <c r="R107" t="n">
-        <v>6986289</v>
+        <v>6986445</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11704,7 +11666,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>På levande sälg.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11716,6 +11678,31 @@
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11732,45 +11719,52 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129910645</v>
+        <v>129908886</v>
       </c>
       <c r="B108" t="n">
-        <v>80060</v>
+        <v>80189</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>517286</v>
+        <v>517038</v>
       </c>
       <c r="R108" t="n">
-        <v>6986091</v>
+        <v>6986289</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11805,12 +11799,18 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På levande sälg.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11829,37 +11829,41 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129910652</v>
+        <v>129910661</v>
       </c>
       <c r="B109" t="n">
-        <v>79084</v>
+        <v>92197</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11867,10 +11871,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>517345</v>
+        <v>517220</v>
       </c>
       <c r="R109" t="n">
-        <v>6986186</v>
+        <v>6986131</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11917,17 +11921,17 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -11945,39 +11949,39 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129910661</v>
+        <v>129908911</v>
       </c>
       <c r="B110" t="n">
-        <v>92197</v>
+        <v>79084</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -11987,10 +11991,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>517220</v>
+        <v>516729</v>
       </c>
       <c r="R110" t="n">
-        <v>6986131</v>
+        <v>6986683</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12025,6 +12029,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På gran med apothecier.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12035,19 +12044,29 @@
       <c r="AG110" t="b">
         <v>0</v>
       </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12065,10 +12084,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129908911</v>
+        <v>129910743</v>
       </c>
       <c r="B111" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12076,41 +12095,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>516729</v>
+        <v>516874</v>
       </c>
       <c r="R111" t="n">
-        <v>6986683</v>
+        <v>6986542</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12147,7 +12159,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>På gran med apothecier.</t>
+          <t>Liggande död sälg</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12156,54 +12168,28 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129910743</v>
+        <v>129910652</v>
       </c>
       <c r="B112" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12211,34 +12197,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>516874</v>
+        <v>517345</v>
       </c>
       <c r="R112" t="n">
-        <v>6986542</v>
+        <v>6986186</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12273,29 +12262,40 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Liggande död sälg</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12496,53 +12496,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129910553</v>
+        <v>129910644</v>
       </c>
       <c r="B115" t="n">
-        <v>57737</v>
+        <v>80060</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>389</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>516968</v>
+        <v>517289</v>
       </c>
       <c r="R115" t="n">
-        <v>6986277</v>
+        <v>6986084</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12575,11 +12567,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12606,32 +12593,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129910644</v>
+        <v>129910638</v>
       </c>
       <c r="B116" t="n">
-        <v>80060</v>
+        <v>80189</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12641,10 +12628,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>517289</v>
+        <v>517253</v>
       </c>
       <c r="R116" t="n">
-        <v>6986084</v>
+        <v>6986103</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12703,7 +12690,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129910638</v>
+        <v>129910738</v>
       </c>
       <c r="B117" t="n">
         <v>80189</v>
@@ -12738,10 +12725,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>517253</v>
+        <v>516965</v>
       </c>
       <c r="R117" t="n">
-        <v>6986103</v>
+        <v>6986379</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12776,6 +12763,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12788,19 +12780,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129910738</v>
+        <v>129908885</v>
       </c>
       <c r="B118" t="n">
         <v>80189</v>
@@ -12829,16 +12821,23 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>516965</v>
+        <v>517022</v>
       </c>
       <c r="R118" t="n">
-        <v>6986379</v>
+        <v>6986309</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12875,7 +12874,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12884,25 +12883,51 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129908885</v>
+        <v>129908889</v>
       </c>
       <c r="B119" t="n">
         <v>80189</v>
@@ -12944,10 +12969,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>517022</v>
+        <v>516783</v>
       </c>
       <c r="R119" t="n">
-        <v>6986309</v>
+        <v>6986629</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13037,10 +13062,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129908889</v>
+        <v>129910553</v>
       </c>
       <c r="B120" t="n">
-        <v>80189</v>
+        <v>57737</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13048,28 +13073,29 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -13079,10 +13105,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>516783</v>
+        <v>516968</v>
       </c>
       <c r="R120" t="n">
-        <v>6986629</v>
+        <v>6986277</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13119,7 +13145,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13128,34 +13154,8 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
@@ -14197,32 +14197,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129910659</v>
+        <v>129910551</v>
       </c>
       <c r="B131" t="n">
-        <v>92884</v>
+        <v>91602</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>517328</v>
+        <v>517014</v>
       </c>
       <c r="R131" t="n">
-        <v>6986156</v>
+        <v>6986339</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14286,6 +14286,26 @@
       <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
@@ -14302,46 +14322,41 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129908893</v>
+        <v>129910659</v>
       </c>
       <c r="B132" t="n">
-        <v>98794</v>
+        <v>92884</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14349,10 +14364,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>516958</v>
+        <v>517328</v>
       </c>
       <c r="R132" t="n">
-        <v>6986409</v>
+        <v>6986156</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14387,11 +14402,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i barrblandskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -14401,11 +14411,6 @@
       <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
@@ -14422,61 +14427,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129908897</v>
+        <v>129910584</v>
       </c>
       <c r="B133" t="n">
-        <v>98794</v>
+        <v>80189</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>516696</v>
+        <v>517004</v>
       </c>
       <c r="R133" t="n">
-        <v>6986696</v>
+        <v>6986361</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14511,25 +14500,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Minst 20 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
@@ -14546,10 +14524,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129910551</v>
+        <v>129910594</v>
       </c>
       <c r="B134" t="n">
-        <v>91602</v>
+        <v>80189</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14557,41 +14535,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>517014</v>
+        <v>517165</v>
       </c>
       <c r="R134" t="n">
-        <v>6986339</v>
+        <v>6986222</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14632,29 +14603,8 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
@@ -14671,61 +14621,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129910560</v>
+        <v>129910624</v>
       </c>
       <c r="B135" t="n">
-        <v>58372</v>
+        <v>80189</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>517237</v>
+        <v>517195</v>
       </c>
       <c r="R135" t="n">
-        <v>6986082</v>
+        <v>6986175</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14784,7 +14718,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129910584</v>
+        <v>129910747</v>
       </c>
       <c r="B136" t="n">
         <v>80189</v>
@@ -14819,10 +14753,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>517004</v>
+        <v>516674</v>
       </c>
       <c r="R136" t="n">
-        <v>6986361</v>
+        <v>6986695</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14857,6 +14791,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på liggande men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14869,19 +14808,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129910594</v>
+        <v>129910634</v>
       </c>
       <c r="B137" t="n">
         <v>80189</v>
@@ -14916,10 +14855,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>517165</v>
+        <v>517233</v>
       </c>
       <c r="R137" t="n">
-        <v>6986222</v>
+        <v>6986069</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14978,32 +14917,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129910624</v>
+        <v>129910572</v>
       </c>
       <c r="B138" t="n">
-        <v>80189</v>
+        <v>80093</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15013,10 +14952,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>517195</v>
+        <v>517147</v>
       </c>
       <c r="R138" t="n">
-        <v>6986175</v>
+        <v>6986129</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15075,45 +15014,61 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129910747</v>
+        <v>129910560</v>
       </c>
       <c r="B139" t="n">
-        <v>80189</v>
+        <v>58372</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>102125</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>516674</v>
+        <v>517237</v>
       </c>
       <c r="R139" t="n">
-        <v>6986695</v>
+        <v>6986082</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15148,11 +15103,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på liggande men levande sälg.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15165,57 +15115,73 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129910634</v>
+        <v>129908897</v>
       </c>
       <c r="B140" t="n">
-        <v>80189</v>
+        <v>98794</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>517233</v>
+        <v>516696</v>
       </c>
       <c r="R140" t="n">
-        <v>6986069</v>
+        <v>6986696</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15250,14 +15216,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Minst 20 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
@@ -15274,45 +15251,57 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129910572</v>
+        <v>129908893</v>
       </c>
       <c r="B141" t="n">
-        <v>80093</v>
+        <v>98794</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>517147</v>
+        <v>516958</v>
       </c>
       <c r="R141" t="n">
-        <v>6986129</v>
+        <v>6986409</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15347,14 +15336,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i barrblandskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
@@ -15468,57 +15468,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129908879</v>
+        <v>129910570</v>
       </c>
       <c r="B143" t="n">
-        <v>57737</v>
+        <v>80093</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>516930</v>
+        <v>517172</v>
       </c>
       <c r="R143" t="n">
-        <v>6986299</v>
+        <v>6986122</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15553,11 +15541,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
@@ -15566,31 +15549,6 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
@@ -15607,45 +15565,48 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129910570</v>
+        <v>129910651</v>
       </c>
       <c r="B144" t="n">
-        <v>80093</v>
+        <v>79084</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>517172</v>
+        <v>517137</v>
       </c>
       <c r="R144" t="n">
-        <v>6986122</v>
+        <v>6986150</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15686,8 +15647,24 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
@@ -15704,10 +15681,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129910651</v>
+        <v>129910639</v>
       </c>
       <c r="B145" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15715,26 +15692,30 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -15742,10 +15723,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>517137</v>
+        <v>517276</v>
       </c>
       <c r="R145" t="n">
-        <v>6986150</v>
+        <v>6986120</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15780,6 +15761,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apotechier.</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -15789,21 +15775,6 @@
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -15820,7 +15791,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129910639</v>
+        <v>129910608</v>
       </c>
       <c r="B146" t="n">
         <v>80189</v>
@@ -15849,23 +15820,16 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>517276</v>
+        <v>517230</v>
       </c>
       <c r="R146" t="n">
-        <v>6986120</v>
+        <v>6986231</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15900,18 +15864,12 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apotechier.</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15930,7 +15888,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129910608</v>
+        <v>129910582</v>
       </c>
       <c r="B147" t="n">
         <v>80189</v>
@@ -15965,10 +15923,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>517230</v>
+        <v>517009</v>
       </c>
       <c r="R147" t="n">
-        <v>6986231</v>
+        <v>6986366</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16027,10 +15985,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129910582</v>
+        <v>129908879</v>
       </c>
       <c r="B148" t="n">
-        <v>80189</v>
+        <v>57737</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16038,34 +15996,46 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>517009</v>
+        <v>516930</v>
       </c>
       <c r="R148" t="n">
-        <v>6986366</v>
+        <v>6986299</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16100,6 +16070,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -16108,6 +16083,31 @@
       </c>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -16243,10 +16243,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129908882</v>
+        <v>129910662</v>
       </c>
       <c r="B150" t="n">
-        <v>57737</v>
+        <v>89001</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16254,46 +16254,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>516646</v>
+        <v>517336</v>
       </c>
       <c r="R150" t="n">
-        <v>6986735</v>
+        <v>6986195</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16328,11 +16316,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -16341,31 +16324,6 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -16382,10 +16340,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129908900</v>
+        <v>129910607</v>
       </c>
       <c r="B151" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16393,37 +16351,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>516960</v>
+        <v>517246</v>
       </c>
       <c r="R151" t="n">
-        <v>6986352</v>
+        <v>6986091</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16458,45 +16413,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal gran.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16513,10 +16437,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129910662</v>
+        <v>129908900</v>
       </c>
       <c r="B152" t="n">
-        <v>89001</v>
+        <v>79084</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16524,34 +16448,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>517336</v>
+        <v>516960</v>
       </c>
       <c r="R152" t="n">
-        <v>6986195</v>
+        <v>6986352</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16586,14 +16513,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal gran.</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16610,10 +16568,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129910607</v>
+        <v>129908909</v>
       </c>
       <c r="B153" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16621,34 +16579,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>517246</v>
+        <v>516915</v>
       </c>
       <c r="R153" t="n">
-        <v>6986091</v>
+        <v>6986509</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16689,8 +16650,34 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
@@ -16707,7 +16694,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129908909</v>
+        <v>129908903</v>
       </c>
       <c r="B154" t="n">
         <v>79084</v>
@@ -16745,10 +16732,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>516915</v>
+        <v>516956</v>
       </c>
       <c r="R154" t="n">
-        <v>6986509</v>
+        <v>6986419</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16783,6 +16770,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>På bark av tall.</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -16795,27 +16787,27 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -16833,10 +16825,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129908903</v>
+        <v>129910587</v>
       </c>
       <c r="B155" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16844,37 +16836,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>516956</v>
+        <v>517018</v>
       </c>
       <c r="R155" t="n">
-        <v>6986419</v>
+        <v>6986301</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16909,45 +16898,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>På bark av tall.</t>
-        </is>
-      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -16964,7 +16922,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129910587</v>
+        <v>129910609</v>
       </c>
       <c r="B156" t="n">
         <v>80189</v>
@@ -16999,10 +16957,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>517018</v>
+        <v>517221</v>
       </c>
       <c r="R156" t="n">
-        <v>6986301</v>
+        <v>6986213</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17061,7 +17019,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129910609</v>
+        <v>129910745</v>
       </c>
       <c r="B157" t="n">
         <v>80189</v>
@@ -17096,10 +17054,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>517221</v>
+        <v>516739</v>
       </c>
       <c r="R157" t="n">
-        <v>6986213</v>
+        <v>6986664</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17134,6 +17092,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>På stående död sälg</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -17146,22 +17109,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129910745</v>
+        <v>129908882</v>
       </c>
       <c r="B158" t="n">
-        <v>80189</v>
+        <v>57737</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17169,34 +17132,46 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>516739</v>
+        <v>516646</v>
       </c>
       <c r="R158" t="n">
-        <v>6986664</v>
+        <v>6986735</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17233,7 +17208,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>På stående död sälg</t>
+          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17244,16 +17219,41 @@
       </c>
       <c r="AG158" t="b">
         <v>0</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17357,10 +17357,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910558</v>
+        <v>129910550</v>
       </c>
       <c r="B160" t="n">
-        <v>57737</v>
+        <v>90634</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17368,42 +17368,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>517356</v>
+        <v>517343</v>
       </c>
       <c r="R160" t="n">
-        <v>6986190</v>
+        <v>6986165</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17436,11 +17428,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17467,10 +17454,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910550</v>
+        <v>129908904</v>
       </c>
       <c r="B161" t="n">
-        <v>90634</v>
+        <v>79084</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17478,34 +17465,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>517343</v>
+        <v>516981</v>
       </c>
       <c r="R161" t="n">
-        <v>6986165</v>
+        <v>6986356</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17546,8 +17536,34 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
@@ -18083,48 +18099,45 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129908904</v>
+        <v>129910669</v>
       </c>
       <c r="B167" t="n">
-        <v>79084</v>
+        <v>79340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>516981</v>
+        <v>517113</v>
       </c>
       <c r="R167" t="n">
-        <v>6986356</v>
+        <v>6986244</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18165,34 +18178,8 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
-      </c>
-      <c r="AH167" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
@@ -18209,32 +18196,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129910669</v>
+        <v>129910586</v>
       </c>
       <c r="B168" t="n">
-        <v>79340</v>
+        <v>80189</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18244,10 +18231,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>517113</v>
+        <v>517006</v>
       </c>
       <c r="R168" t="n">
-        <v>6986244</v>
+        <v>6986354</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18306,7 +18293,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129910586</v>
+        <v>129910616</v>
       </c>
       <c r="B169" t="n">
         <v>80189</v>
@@ -18341,10 +18328,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>517006</v>
+        <v>517030</v>
       </c>
       <c r="R169" t="n">
-        <v>6986354</v>
+        <v>6986400</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18403,7 +18390,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129910616</v>
+        <v>129910576</v>
       </c>
       <c r="B170" t="n">
         <v>80189</v>
@@ -18438,10 +18425,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>517030</v>
+        <v>516994</v>
       </c>
       <c r="R170" t="n">
-        <v>6986400</v>
+        <v>6986453</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18500,7 +18487,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129910576</v>
+        <v>129910623</v>
       </c>
       <c r="B171" t="n">
         <v>80189</v>
@@ -18535,10 +18522,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>516994</v>
+        <v>517174</v>
       </c>
       <c r="R171" t="n">
-        <v>6986453</v>
+        <v>6986187</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18597,10 +18584,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129910623</v>
+        <v>129908907</v>
       </c>
       <c r="B172" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18608,34 +18595,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>517174</v>
+        <v>517033</v>
       </c>
       <c r="R172" t="n">
-        <v>6986187</v>
+        <v>6986307</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18670,14 +18660,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>På en gammal gran i granskog.</t>
+        </is>
+      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
@@ -18694,10 +18715,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129908907</v>
+        <v>129910558</v>
       </c>
       <c r="B173" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18705,26 +18726,31 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
@@ -18732,10 +18758,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>517033</v>
+        <v>517356</v>
       </c>
       <c r="R173" t="n">
-        <v>6986307</v>
+        <v>6986190</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18772,7 +18798,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>På en gammal gran i granskog.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18781,34 +18807,8 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
-      </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK173" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910574</v>
+        <v>129910666</v>
       </c>
       <c r="B2" t="n">
-        <v>79108</v>
+        <v>81147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>229558</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517340</v>
+        <v>517120</v>
       </c>
       <c r="R2" t="n">
-        <v>6986164</v>
+        <v>6986257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910577</v>
+        <v>129910642</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>78097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517035</v>
+        <v>517251</v>
       </c>
       <c r="R3" t="n">
-        <v>6986429</v>
+        <v>6986078</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,56 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910654</v>
+        <v>129910574</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517262</v>
+        <v>517340</v>
       </c>
       <c r="R4" t="n">
-        <v>6986119</v>
+        <v>6986164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,35 +942,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt!!</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -998,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910752</v>
+        <v>129910654</v>
       </c>
       <c r="B5" t="n">
         <v>79084</v>
@@ -1026,17 +994,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516947</v>
+        <v>517262</v>
       </c>
       <c r="R5" t="n">
-        <v>6986297</v>
+        <v>6986119</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1052,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt!!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,28 +1061,44 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129908891</v>
+        <v>129910752</v>
       </c>
       <c r="B6" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,41 +1106,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516683</v>
+        <v>516947</v>
       </c>
       <c r="R6" t="n">
-        <v>6986718</v>
+        <v>6986297</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1170,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På asp i granskog.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,76 +1179,50 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910667</v>
+        <v>129910577</v>
       </c>
       <c r="B7" t="n">
-        <v>79340</v>
+        <v>80189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517221</v>
+        <v>517035</v>
       </c>
       <c r="R7" t="n">
-        <v>6986209</v>
+        <v>6986429</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129910557</v>
+        <v>129908891</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,29 +1305,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1375,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517175</v>
+        <v>516683</v>
       </c>
       <c r="R8" t="n">
-        <v>6986155</v>
+        <v>6986718</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1376,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>På asp i granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,8 +1385,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1442,53 +1429,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129910556</v>
+        <v>129910667</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>79340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517169</v>
+        <v>517221</v>
       </c>
       <c r="R9" t="n">
-        <v>6986201</v>
+        <v>6986209</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129910642</v>
+        <v>129910556</v>
       </c>
       <c r="B10" t="n">
-        <v>78097</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,34 +1537,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517251</v>
+        <v>517169</v>
       </c>
       <c r="R10" t="n">
-        <v>6986078</v>
+        <v>6986201</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,6 +1605,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129910666</v>
+        <v>129910557</v>
       </c>
       <c r="B11" t="n">
-        <v>81147</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,34 +1647,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229558</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517120</v>
+        <v>517175</v>
       </c>
       <c r="R11" t="n">
-        <v>6986257</v>
+        <v>6986155</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1978,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129910555</v>
+        <v>129910549</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>79703</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,42 +1989,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517025</v>
+        <v>517088</v>
       </c>
       <c r="R14" t="n">
-        <v>6986271</v>
+        <v>6986173</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,11 +2049,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129910549</v>
+        <v>129910544</v>
       </c>
       <c r="B15" t="n">
-        <v>79703</v>
+        <v>83055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,21 +2086,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2123,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517088</v>
+        <v>517187</v>
       </c>
       <c r="R15" t="n">
-        <v>6986173</v>
+        <v>6986154</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2573,10 +2560,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129910544</v>
+        <v>129910555</v>
       </c>
       <c r="B20" t="n">
-        <v>83055</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,34 +2571,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517187</v>
+        <v>517025</v>
       </c>
       <c r="R20" t="n">
-        <v>6986154</v>
+        <v>6986271</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2644,6 +2639,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,10 +2796,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129910579</v>
+        <v>129910751</v>
       </c>
       <c r="B22" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2807,21 +2807,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517061</v>
+        <v>516971</v>
       </c>
       <c r="R22" t="n">
-        <v>6986424</v>
+        <v>6986263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,6 +2869,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligare med garnlav på ca 10 granar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2881,19 +2886,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129910615</v>
+        <v>129910579</v>
       </c>
       <c r="B23" t="n">
         <v>80189</v>
@@ -2928,10 +2933,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517004</v>
+        <v>517061</v>
       </c>
       <c r="R23" t="n">
-        <v>6986426</v>
+        <v>6986424</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2995,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129910742</v>
+        <v>129910615</v>
       </c>
       <c r="B24" t="n">
         <v>80189</v>
@@ -3025,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516904</v>
+        <v>517004</v>
       </c>
       <c r="R24" t="n">
-        <v>6986470</v>
+        <v>6986426</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,11 +3068,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3080,19 +3080,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129910613</v>
+        <v>129910742</v>
       </c>
       <c r="B25" t="n">
         <v>80189</v>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517125</v>
+        <v>516904</v>
       </c>
       <c r="R25" t="n">
-        <v>6986172</v>
+        <v>6986470</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3165,6 +3165,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Lunglav på asp</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3177,22 +3182,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129910751</v>
+        <v>129910613</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3200,21 +3205,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3224,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516971</v>
+        <v>517125</v>
       </c>
       <c r="R26" t="n">
-        <v>6986263</v>
+        <v>6986172</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3262,11 +3267,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligare med garnlav på ca 10 granar.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3279,12 +3279,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4165,10 +4165,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129908880</v>
+        <v>129910649</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>56918</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,16 +4176,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4193,12 +4193,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4212,10 +4216,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>516686</v>
+        <v>517134</v>
       </c>
       <c r="R36" t="n">
-        <v>6986687</v>
+        <v>6986204</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,11 +4254,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4263,31 +4262,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4304,10 +4278,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129910649</v>
+        <v>129908880</v>
       </c>
       <c r="B37" t="n">
-        <v>56918</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4315,16 +4289,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4332,16 +4306,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4355,10 +4325,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>517134</v>
+        <v>516686</v>
       </c>
       <c r="R37" t="n">
-        <v>6986204</v>
+        <v>6986687</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4393,6 +4363,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4401,6 +4376,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5220,52 +5220,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129910660</v>
+        <v>129910547</v>
       </c>
       <c r="B46" t="n">
-        <v>92197</v>
+        <v>97040</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>760</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>517050</v>
+        <v>517122</v>
       </c>
       <c r="R46" t="n">
-        <v>6986414</v>
+        <v>6986191</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5306,24 +5299,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5340,10 +5317,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129910559</v>
+        <v>129910568</v>
       </c>
       <c r="B47" t="n">
-        <v>57895</v>
+        <v>80190</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5351,50 +5328,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>517266</v>
+        <v>517230</v>
       </c>
       <c r="R47" t="n">
-        <v>6986055</v>
+        <v>6986059</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5453,45 +5414,52 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129910547</v>
+        <v>129910660</v>
       </c>
       <c r="B48" t="n">
-        <v>97040</v>
+        <v>92197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>760</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>517122</v>
+        <v>517050</v>
       </c>
       <c r="R48" t="n">
-        <v>6986191</v>
+        <v>6986414</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5532,8 +5500,24 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5550,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129910568</v>
+        <v>129910591</v>
       </c>
       <c r="B49" t="n">
-        <v>80190</v>
+        <v>80189</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5561,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5585,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>517230</v>
+        <v>517068</v>
       </c>
       <c r="R49" t="n">
-        <v>6986059</v>
+        <v>6986257</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5647,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129910632</v>
+        <v>129910750</v>
       </c>
       <c r="B50" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5658,21 +5642,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5682,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>517285</v>
+        <v>517017</v>
       </c>
       <c r="R50" t="n">
-        <v>6986090</v>
+        <v>6986332</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,6 +5704,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5732,19 +5721,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129910591</v>
+        <v>129910632</v>
       </c>
       <c r="B51" t="n">
         <v>80189</v>
@@ -5779,10 +5768,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>517068</v>
+        <v>517285</v>
       </c>
       <c r="R51" t="n">
-        <v>6986257</v>
+        <v>6986090</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5841,10 +5830,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129910750</v>
+        <v>129910559</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>57895</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5852,34 +5841,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>517017</v>
+        <v>517266</v>
       </c>
       <c r="R52" t="n">
-        <v>6986332</v>
+        <v>6986055</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5914,11 +5919,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5931,22 +5931,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129910588</v>
+        <v>129910573</v>
       </c>
       <c r="B53" t="n">
-        <v>80189</v>
+        <v>75180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5954,21 +5954,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>517014</v>
+        <v>517112</v>
       </c>
       <c r="R53" t="n">
-        <v>6986283</v>
+        <v>6986241</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129910630</v>
+        <v>129910588</v>
       </c>
       <c r="B55" t="n">
         <v>80189</v>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>517275</v>
+        <v>517014</v>
       </c>
       <c r="R55" t="n">
-        <v>6986074</v>
+        <v>6986283</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129910606</v>
+        <v>129910630</v>
       </c>
       <c r="B56" t="n">
         <v>80189</v>
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>517237</v>
+        <v>517275</v>
       </c>
       <c r="R56" t="n">
-        <v>6986073</v>
+        <v>6986074</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6365,7 +6365,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129910741</v>
+        <v>129910606</v>
       </c>
       <c r="B57" t="n">
         <v>80189</v>
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>517046</v>
+        <v>517237</v>
       </c>
       <c r="R57" t="n">
-        <v>6986289</v>
+        <v>6986073</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6438,11 +6438,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6455,22 +6450,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129910653</v>
+        <v>129910741</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6478,37 +6473,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>516971</v>
+        <v>517046</v>
       </c>
       <c r="R58" t="n">
-        <v>6986287</v>
+        <v>6986289</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6545,7 +6537,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6554,34 +6546,18 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6693,10 +6669,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129910573</v>
+        <v>129910653</v>
       </c>
       <c r="B60" t="n">
-        <v>75180</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6704,34 +6680,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>517112</v>
+        <v>516971</v>
       </c>
       <c r="R60" t="n">
-        <v>6986241</v>
+        <v>6986287</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6766,14 +6745,35 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7634,10 +7634,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129910563</v>
+        <v>129908890</v>
       </c>
       <c r="B69" t="n">
-        <v>80055</v>
+        <v>80189</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7645,34 +7645,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>517167</v>
+        <v>516676</v>
       </c>
       <c r="R69" t="n">
-        <v>6986122</v>
+        <v>6986711</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7707,6 +7710,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På grovbarkad asp i granskog.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7716,6 +7724,31 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -7732,27 +7765,27 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129910754</v>
+        <v>129910664</v>
       </c>
       <c r="B70" t="n">
-        <v>79084</v>
+        <v>80224</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7761,16 +7794,23 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>516688</v>
+        <v>517231</v>
       </c>
       <c r="R70" t="n">
-        <v>6986695</v>
+        <v>6986060</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7805,36 +7845,32 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129908890</v>
+        <v>129908887</v>
       </c>
       <c r="B71" t="n">
         <v>80189</v>
@@ -7864,7 +7900,11 @@
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7872,10 +7912,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>516676</v>
+        <v>516880</v>
       </c>
       <c r="R71" t="n">
-        <v>6986711</v>
+        <v>6986531</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7912,7 +7952,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På grovbarkad asp i granskog.</t>
+          <t>Fertil lunglav med apothecier på en levande sälg.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7932,12 +7972,12 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -7947,7 +7987,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -7965,27 +8005,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129910664</v>
+        <v>129910754</v>
       </c>
       <c r="B72" t="n">
-        <v>80224</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7994,23 +8034,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>517231</v>
+        <v>516688</v>
       </c>
       <c r="R72" t="n">
-        <v>6986060</v>
+        <v>6986695</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8045,25 +8078,29 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8196,10 +8233,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129908887</v>
+        <v>129910563</v>
       </c>
       <c r="B74" t="n">
-        <v>80189</v>
+        <v>80055</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8207,41 +8244,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>516880</v>
+        <v>517167</v>
       </c>
       <c r="R74" t="n">
-        <v>6986531</v>
+        <v>6986122</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8276,11 +8306,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8290,31 +8315,6 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8428,32 +8428,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129910670</v>
+        <v>129910541</v>
       </c>
       <c r="B76" t="n">
-        <v>79340</v>
+        <v>83055</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8463,10 +8463,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>517175</v>
+        <v>517005</v>
       </c>
       <c r="R76" t="n">
-        <v>6986169</v>
+        <v>6986418</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8525,10 +8525,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129910600</v>
+        <v>129908881</v>
       </c>
       <c r="B77" t="n">
-        <v>80189</v>
+        <v>57737</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8536,34 +8536,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>517181</v>
+        <v>516659</v>
       </c>
       <c r="R77" t="n">
-        <v>6986168</v>
+        <v>6986705</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8598,6 +8610,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8606,6 +8623,31 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8622,32 +8664,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129910583</v>
+        <v>129910670</v>
       </c>
       <c r="B78" t="n">
-        <v>80189</v>
+        <v>79340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8657,10 +8699,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>517001</v>
+        <v>517175</v>
       </c>
       <c r="R78" t="n">
-        <v>6986369</v>
+        <v>6986169</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8719,7 +8761,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129910633</v>
+        <v>129910600</v>
       </c>
       <c r="B79" t="n">
         <v>80189</v>
@@ -8754,10 +8796,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>517235</v>
+        <v>517181</v>
       </c>
       <c r="R79" t="n">
-        <v>6986077</v>
+        <v>6986168</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8816,10 +8858,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129910541</v>
+        <v>129910583</v>
       </c>
       <c r="B80" t="n">
-        <v>83055</v>
+        <v>80189</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8827,21 +8869,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8851,10 +8893,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>517005</v>
+        <v>517001</v>
       </c>
       <c r="R80" t="n">
-        <v>6986418</v>
+        <v>6986369</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8913,10 +8955,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129908881</v>
+        <v>129910633</v>
       </c>
       <c r="B81" t="n">
-        <v>57737</v>
+        <v>80189</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8924,46 +8966,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>516659</v>
+        <v>517235</v>
       </c>
       <c r="R81" t="n">
-        <v>6986705</v>
+        <v>6986077</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8998,11 +9028,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9011,31 +9036,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9176,45 +9176,61 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129910740</v>
+        <v>129908894</v>
       </c>
       <c r="B83" t="n">
-        <v>80189</v>
+        <v>98794</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>517033</v>
+        <v>517028</v>
       </c>
       <c r="R83" t="n">
-        <v>6986309</v>
+        <v>6986324</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9251,7 +9267,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På torraka och låga av sälg</t>
+          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9260,18 +9276,24 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9569,10 +9591,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129910602</v>
+        <v>129910647</v>
       </c>
       <c r="B87" t="n">
-        <v>80189</v>
+        <v>78841</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9580,21 +9602,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9604,10 +9626,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>517146</v>
+        <v>517081</v>
       </c>
       <c r="R87" t="n">
-        <v>6986161</v>
+        <v>6986186</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9666,10 +9688,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129910619</v>
+        <v>129910545</v>
       </c>
       <c r="B88" t="n">
-        <v>80189</v>
+        <v>83055</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9677,21 +9699,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9701,10 +9723,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>517108</v>
+        <v>517251</v>
       </c>
       <c r="R88" t="n">
-        <v>6986255</v>
+        <v>6986081</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9763,10 +9785,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129910647</v>
+        <v>129910740</v>
       </c>
       <c r="B89" t="n">
-        <v>78841</v>
+        <v>80189</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9774,21 +9796,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9798,10 +9820,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>517081</v>
+        <v>517033</v>
       </c>
       <c r="R89" t="n">
-        <v>6986186</v>
+        <v>6986309</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9836,6 +9858,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På torraka och låga av sälg</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -9848,44 +9875,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129910571</v>
+        <v>129910602</v>
       </c>
       <c r="B90" t="n">
-        <v>80093</v>
+        <v>80189</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9895,10 +9922,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>517109</v>
+        <v>517146</v>
       </c>
       <c r="R90" t="n">
-        <v>6986168</v>
+        <v>6986161</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9957,7 +9984,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129910636</v>
+        <v>129910619</v>
       </c>
       <c r="B91" t="n">
         <v>80189</v>
@@ -9992,10 +10019,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>517228</v>
+        <v>517108</v>
       </c>
       <c r="R91" t="n">
-        <v>6986059</v>
+        <v>6986255</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10054,32 +10081,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129910545</v>
+        <v>129910571</v>
       </c>
       <c r="B92" t="n">
-        <v>83055</v>
+        <v>80093</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10089,10 +10116,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>517251</v>
+        <v>517109</v>
       </c>
       <c r="R92" t="n">
-        <v>6986081</v>
+        <v>6986168</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10151,61 +10178,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129908894</v>
+        <v>129910636</v>
       </c>
       <c r="B93" t="n">
-        <v>98794</v>
+        <v>80189</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>517028</v>
+        <v>517228</v>
       </c>
       <c r="R93" t="n">
-        <v>6986324</v>
+        <v>6986059</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10240,25 +10251,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -10275,10 +10275,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129910665</v>
+        <v>129910542</v>
       </c>
       <c r="B94" t="n">
-        <v>83047</v>
+        <v>83055</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10286,21 +10286,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10310,10 +10310,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>517165</v>
+        <v>517009</v>
       </c>
       <c r="R94" t="n">
-        <v>6986212</v>
+        <v>6986437</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10474,10 +10474,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129910625</v>
+        <v>129910665</v>
       </c>
       <c r="B96" t="n">
-        <v>80189</v>
+        <v>83047</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10485,21 +10485,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10509,10 +10509,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>517184</v>
+        <v>517165</v>
       </c>
       <c r="R96" t="n">
-        <v>6986149</v>
+        <v>6986212</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10571,7 +10571,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129910626</v>
+        <v>129910625</v>
       </c>
       <c r="B97" t="n">
         <v>80189</v>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>517169</v>
+        <v>517184</v>
       </c>
       <c r="R97" t="n">
-        <v>6986147</v>
+        <v>6986149</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10668,10 +10668,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129910542</v>
+        <v>129910626</v>
       </c>
       <c r="B98" t="n">
-        <v>83055</v>
+        <v>80189</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10679,21 +10679,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10703,10 +10703,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>517009</v>
+        <v>517169</v>
       </c>
       <c r="R98" t="n">
-        <v>6986437</v>
+        <v>6986147</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11365,10 +11365,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129908899</v>
+        <v>129910622</v>
       </c>
       <c r="B105" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11376,37 +11376,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>516951</v>
+        <v>517142</v>
       </c>
       <c r="R105" t="n">
-        <v>6986304</v>
+        <v>6986177</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11447,34 +11444,8 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11491,7 +11462,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129910622</v>
+        <v>129908886</v>
       </c>
       <c r="B106" t="n">
         <v>80189</v>
@@ -11520,16 +11491,23 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>517142</v>
+        <v>517038</v>
       </c>
       <c r="R106" t="n">
-        <v>6986177</v>
+        <v>6986289</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11564,12 +11542,18 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På levande sälg.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11588,7 +11572,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129908902</v>
+        <v>129908899</v>
       </c>
       <c r="B107" t="n">
         <v>79084</v>
@@ -11626,10 +11610,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>516926</v>
+        <v>516951</v>
       </c>
       <c r="R107" t="n">
-        <v>6986445</v>
+        <v>6986304</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11664,11 +11648,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11681,7 +11660,7 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -11719,10 +11698,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129908886</v>
+        <v>129908902</v>
       </c>
       <c r="B108" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11730,30 +11709,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11761,10 +11736,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>517038</v>
+        <v>516926</v>
       </c>
       <c r="R108" t="n">
-        <v>6986289</v>
+        <v>6986445</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11801,7 +11776,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>På levande sälg.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11813,6 +11788,31 @@
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12084,10 +12084,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129910743</v>
+        <v>129910652</v>
       </c>
       <c r="B111" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12095,34 +12095,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>516874</v>
+        <v>517345</v>
       </c>
       <c r="R111" t="n">
-        <v>6986542</v>
+        <v>6986186</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12157,39 +12160,50 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Liggande död sälg</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129910652</v>
+        <v>129910743</v>
       </c>
       <c r="B112" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12197,37 +12211,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>517345</v>
+        <v>516874</v>
       </c>
       <c r="R112" t="n">
-        <v>6986186</v>
+        <v>6986542</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12262,40 +12273,29 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Liggande död sälg</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -13389,10 +13389,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129910640</v>
+        <v>129910753</v>
       </c>
       <c r="B123" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13400,21 +13400,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13424,10 +13424,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>517288</v>
+        <v>516914</v>
       </c>
       <c r="R123" t="n">
-        <v>6986118</v>
+        <v>6986518</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13462,6 +13462,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>På granar</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -13474,44 +13479,44 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129910621</v>
+        <v>129910566</v>
       </c>
       <c r="B124" t="n">
-        <v>80189</v>
+        <v>79170</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13521,10 +13526,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>517170</v>
+        <v>517128</v>
       </c>
       <c r="R124" t="n">
-        <v>6986215</v>
+        <v>6986180</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13583,10 +13588,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129910753</v>
+        <v>129910640</v>
       </c>
       <c r="B125" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13594,21 +13599,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13618,10 +13623,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>516914</v>
+        <v>517288</v>
       </c>
       <c r="R125" t="n">
-        <v>6986518</v>
+        <v>6986118</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13656,11 +13661,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>På granar</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -13673,19 +13673,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129910635</v>
+        <v>129910621</v>
       </c>
       <c r="B126" t="n">
         <v>80189</v>
@@ -13720,10 +13720,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>517229</v>
+        <v>517170</v>
       </c>
       <c r="R126" t="n">
-        <v>6986063</v>
+        <v>6986215</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13782,7 +13782,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129910605</v>
+        <v>129910635</v>
       </c>
       <c r="B127" t="n">
         <v>80189</v>
@@ -13817,10 +13817,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>517273</v>
+        <v>517229</v>
       </c>
       <c r="R127" t="n">
-        <v>6986075</v>
+        <v>6986063</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13879,32 +13879,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129910566</v>
+        <v>129910605</v>
       </c>
       <c r="B128" t="n">
-        <v>79170</v>
+        <v>80189</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13914,10 +13914,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>517128</v>
+        <v>517273</v>
       </c>
       <c r="R128" t="n">
-        <v>6986180</v>
+        <v>6986075</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14197,10 +14197,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129910551</v>
+        <v>129910584</v>
       </c>
       <c r="B131" t="n">
-        <v>91602</v>
+        <v>80189</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14208,41 +14208,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>517014</v>
+        <v>517004</v>
       </c>
       <c r="R131" t="n">
-        <v>6986339</v>
+        <v>6986361</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14283,29 +14276,8 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
@@ -14322,52 +14294,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129910659</v>
+        <v>129910594</v>
       </c>
       <c r="B132" t="n">
-        <v>92884</v>
+        <v>80189</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>517328</v>
+        <v>517165</v>
       </c>
       <c r="R132" t="n">
-        <v>6986156</v>
+        <v>6986222</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14408,7 +14373,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14427,7 +14391,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129910584</v>
+        <v>129910624</v>
       </c>
       <c r="B133" t="n">
         <v>80189</v>
@@ -14462,10 +14426,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>517004</v>
+        <v>517195</v>
       </c>
       <c r="R133" t="n">
-        <v>6986361</v>
+        <v>6986175</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14524,7 +14488,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129910594</v>
+        <v>129910747</v>
       </c>
       <c r="B134" t="n">
         <v>80189</v>
@@ -14559,10 +14523,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>517165</v>
+        <v>516674</v>
       </c>
       <c r="R134" t="n">
-        <v>6986222</v>
+        <v>6986695</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14597,6 +14561,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på liggande men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14609,19 +14578,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129910624</v>
+        <v>129910634</v>
       </c>
       <c r="B135" t="n">
         <v>80189</v>
@@ -14656,10 +14625,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>517195</v>
+        <v>517233</v>
       </c>
       <c r="R135" t="n">
-        <v>6986175</v>
+        <v>6986069</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14718,32 +14687,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129910747</v>
+        <v>129910572</v>
       </c>
       <c r="B136" t="n">
-        <v>80189</v>
+        <v>80093</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14753,10 +14722,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>516674</v>
+        <v>517147</v>
       </c>
       <c r="R136" t="n">
-        <v>6986695</v>
+        <v>6986129</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14791,11 +14760,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på liggande men levande sälg.</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14808,22 +14772,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129910634</v>
+        <v>129910551</v>
       </c>
       <c r="B137" t="n">
-        <v>80189</v>
+        <v>91602</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14831,34 +14795,41 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>517233</v>
+        <v>517014</v>
       </c>
       <c r="R137" t="n">
-        <v>6986069</v>
+        <v>6986339</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14899,8 +14870,29 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
@@ -14917,10 +14909,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129910572</v>
+        <v>129910659</v>
       </c>
       <c r="B138" t="n">
-        <v>80093</v>
+        <v>92884</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14928,34 +14920,41 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>517147</v>
+        <v>517328</v>
       </c>
       <c r="R138" t="n">
-        <v>6986129</v>
+        <v>6986156</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14996,6 +14995,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15127,7 +15127,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129908897</v>
+        <v>129908893</v>
       </c>
       <c r="B140" t="n">
         <v>98794</v>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15165,11 +15165,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -15178,10 +15174,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>516696</v>
+        <v>516958</v>
       </c>
       <c r="R140" t="n">
-        <v>6986696</v>
+        <v>6986409</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15218,7 +15214,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Minst 20 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i barrblandskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15233,7 +15229,7 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -15251,7 +15247,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129908893</v>
+        <v>129908897</v>
       </c>
       <c r="B141" t="n">
         <v>98794</v>
@@ -15281,7 +15277,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15289,7 +15285,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -15298,10 +15298,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>516958</v>
+        <v>516696</v>
       </c>
       <c r="R141" t="n">
-        <v>6986409</v>
+        <v>6986696</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i barrblandskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+          <t>Minst 20 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15353,7 +15353,7 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -15468,45 +15468,48 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129910570</v>
+        <v>129910651</v>
       </c>
       <c r="B143" t="n">
-        <v>80093</v>
+        <v>79084</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>517172</v>
+        <v>517137</v>
       </c>
       <c r="R143" t="n">
-        <v>6986122</v>
+        <v>6986150</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15547,8 +15550,24 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
@@ -15565,48 +15584,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129910651</v>
+        <v>129910570</v>
       </c>
       <c r="B144" t="n">
-        <v>79084</v>
+        <v>80093</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>517137</v>
+        <v>517172</v>
       </c>
       <c r="R144" t="n">
-        <v>6986150</v>
+        <v>6986122</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15647,24 +15663,8 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
@@ -16124,61 +16124,57 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129910648</v>
+        <v>129908882</v>
       </c>
       <c r="B149" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>517224</v>
+        <v>516646</v>
       </c>
       <c r="R149" t="n">
-        <v>6986227</v>
+        <v>6986735</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16215,7 +16211,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16224,9 +16220,33 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -16340,10 +16360,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129910607</v>
+        <v>129908900</v>
       </c>
       <c r="B151" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16351,34 +16371,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>517246</v>
+        <v>516960</v>
       </c>
       <c r="R151" t="n">
-        <v>6986091</v>
+        <v>6986352</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16413,14 +16436,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal gran.</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16437,7 +16491,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129908900</v>
+        <v>129908903</v>
       </c>
       <c r="B152" t="n">
         <v>79084</v>
@@ -16475,10 +16529,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>516960</v>
+        <v>516956</v>
       </c>
       <c r="R152" t="n">
-        <v>6986352</v>
+        <v>6986419</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16515,7 +16569,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>På en grovbarkad gammal gran.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16535,22 +16589,22 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -16568,10 +16622,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129908909</v>
+        <v>129910607</v>
       </c>
       <c r="B153" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16579,37 +16633,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>516915</v>
+        <v>517246</v>
       </c>
       <c r="R153" t="n">
-        <v>6986509</v>
+        <v>6986091</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16650,34 +16701,8 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
@@ -16694,10 +16719,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129908903</v>
+        <v>129910587</v>
       </c>
       <c r="B154" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16705,37 +16730,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>516956</v>
+        <v>517018</v>
       </c>
       <c r="R154" t="n">
-        <v>6986419</v>
+        <v>6986301</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16770,45 +16792,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>På bark av tall.</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
@@ -16825,7 +16816,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129910587</v>
+        <v>129910609</v>
       </c>
       <c r="B155" t="n">
         <v>80189</v>
@@ -16860,10 +16851,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>517018</v>
+        <v>517221</v>
       </c>
       <c r="R155" t="n">
-        <v>6986301</v>
+        <v>6986213</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16922,7 +16913,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129910609</v>
+        <v>129910745</v>
       </c>
       <c r="B156" t="n">
         <v>80189</v>
@@ -16957,10 +16948,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>517221</v>
+        <v>516739</v>
       </c>
       <c r="R156" t="n">
-        <v>6986213</v>
+        <v>6986664</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16995,6 +16986,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På stående död sälg</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -17007,22 +17003,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129910745</v>
+        <v>129908909</v>
       </c>
       <c r="B157" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17030,34 +17026,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>516739</v>
+        <v>516915</v>
       </c>
       <c r="R157" t="n">
-        <v>6986664</v>
+        <v>6986509</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17092,86 +17091,111 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>På stående död sälg</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129908882</v>
+        <v>129910648</v>
       </c>
       <c r="B158" t="n">
-        <v>57737</v>
+        <v>98794</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>516646</v>
+        <v>517224</v>
       </c>
       <c r="R158" t="n">
-        <v>6986735</v>
+        <v>6986227</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17208,7 +17232,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
+          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17217,33 +17241,9 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
@@ -17260,10 +17260,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910548</v>
+        <v>129910550</v>
       </c>
       <c r="B159" t="n">
-        <v>97040</v>
+        <v>90634</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17271,21 +17271,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>53</v>
+        <v>1962</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17295,10 +17295,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>517167</v>
+        <v>517343</v>
       </c>
       <c r="R159" t="n">
-        <v>6986105</v>
+        <v>6986165</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17357,10 +17357,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910550</v>
+        <v>129910548</v>
       </c>
       <c r="B160" t="n">
-        <v>90634</v>
+        <v>97040</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17368,21 +17368,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1962</v>
+        <v>53</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17392,10 +17392,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>517343</v>
+        <v>517167</v>
       </c>
       <c r="R160" t="n">
-        <v>6986165</v>
+        <v>6986105</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17454,7 +17454,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129908904</v>
+        <v>129908910</v>
       </c>
       <c r="B161" t="n">
         <v>79084</v>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>516981</v>
+        <v>516902</v>
       </c>
       <c r="R161" t="n">
-        <v>6986356</v>
+        <v>6986521</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ161" t="inlineStr">
@@ -17580,7 +17580,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129908910</v>
+        <v>129908904</v>
       </c>
       <c r="B162" t="n">
         <v>79084</v>
@@ -17618,10 +17618,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>516902</v>
+        <v>516981</v>
       </c>
       <c r="R162" t="n">
-        <v>6986521</v>
+        <v>6986356</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -17706,10 +17706,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129910744</v>
+        <v>129908907</v>
       </c>
       <c r="B163" t="n">
-        <v>80189</v>
+        <v>79084</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17717,34 +17717,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>516858</v>
+        <v>517033</v>
       </c>
       <c r="R163" t="n">
-        <v>6986573</v>
+        <v>6986307</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17781,7 +17784,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>På både en lutande död sälg och en stående avbruten sälg.</t>
+          <t>På en gammal gran i granskog.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17790,25 +17793,51 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129910611</v>
+        <v>129910744</v>
       </c>
       <c r="B164" t="n">
         <v>80189</v>
@@ -17843,10 +17872,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>517216</v>
+        <v>516858</v>
       </c>
       <c r="R164" t="n">
-        <v>6986197</v>
+        <v>6986573</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17881,6 +17910,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>På både en lutande död sälg och en stående avbruten sälg.</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -17893,19 +17927,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129910598</v>
+        <v>129910611</v>
       </c>
       <c r="B165" t="n">
         <v>80189</v>
@@ -17940,10 +17974,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>517155</v>
+        <v>517216</v>
       </c>
       <c r="R165" t="n">
-        <v>6986194</v>
+        <v>6986197</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18002,7 +18036,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129910628</v>
+        <v>129910598</v>
       </c>
       <c r="B166" t="n">
         <v>80189</v>
@@ -18037,10 +18071,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>517207</v>
+        <v>517155</v>
       </c>
       <c r="R166" t="n">
-        <v>6986088</v>
+        <v>6986194</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18099,32 +18133,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129910669</v>
+        <v>129910628</v>
       </c>
       <c r="B167" t="n">
-        <v>79340</v>
+        <v>80189</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18134,10 +18168,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>517113</v>
+        <v>517207</v>
       </c>
       <c r="R167" t="n">
-        <v>6986244</v>
+        <v>6986088</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18196,32 +18230,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129910586</v>
+        <v>129910669</v>
       </c>
       <c r="B168" t="n">
-        <v>80189</v>
+        <v>79340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18231,10 +18265,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>517006</v>
+        <v>517113</v>
       </c>
       <c r="R168" t="n">
-        <v>6986354</v>
+        <v>6986244</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18293,7 +18327,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129910616</v>
+        <v>129910586</v>
       </c>
       <c r="B169" t="n">
         <v>80189</v>
@@ -18328,10 +18362,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>517030</v>
+        <v>517006</v>
       </c>
       <c r="R169" t="n">
-        <v>6986400</v>
+        <v>6986354</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18390,7 +18424,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129910576</v>
+        <v>129910616</v>
       </c>
       <c r="B170" t="n">
         <v>80189</v>
@@ -18425,10 +18459,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>516994</v>
+        <v>517030</v>
       </c>
       <c r="R170" t="n">
-        <v>6986453</v>
+        <v>6986400</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18487,7 +18521,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129910623</v>
+        <v>129910576</v>
       </c>
       <c r="B171" t="n">
         <v>80189</v>
@@ -18522,10 +18556,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>517174</v>
+        <v>516994</v>
       </c>
       <c r="R171" t="n">
-        <v>6986187</v>
+        <v>6986453</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18584,10 +18618,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129908907</v>
+        <v>129910623</v>
       </c>
       <c r="B172" t="n">
-        <v>79084</v>
+        <v>80189</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18595,37 +18629,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>517033</v>
+        <v>517174</v>
       </c>
       <c r="R172" t="n">
-        <v>6986307</v>
+        <v>6986187</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18660,45 +18691,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>På en gammal gran i granskog.</t>
-        </is>
-      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910654</v>
+        <v>129910557</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517262</v>
+        <v>517175</v>
       </c>
       <c r="R2" t="n">
-        <v>6986119</v>
+        <v>6986155</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt!!</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,24 +767,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -804,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910752</v>
+        <v>129910556</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,34 +796,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516947</v>
+        <v>517169</v>
       </c>
       <c r="R3" t="n">
-        <v>6986297</v>
+        <v>6986201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +868,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,22 +883,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910557</v>
+        <v>129910642</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>78100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,42 +906,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517175</v>
+        <v>517251</v>
       </c>
       <c r="R4" t="n">
-        <v>6986155</v>
+        <v>6986078</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910556</v>
+        <v>129910666</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>81150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,42 +1003,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>229558</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517169</v>
+        <v>517120</v>
       </c>
       <c r="R5" t="n">
-        <v>6986201</v>
+        <v>6986257</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,32 +1089,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910642</v>
+        <v>129910574</v>
       </c>
       <c r="B6" t="n">
-        <v>78100</v>
+        <v>79111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517251</v>
+        <v>517340</v>
       </c>
       <c r="R6" t="n">
-        <v>6986078</v>
+        <v>6986164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910666</v>
+        <v>129910654</v>
       </c>
       <c r="B7" t="n">
-        <v>81150</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,34 +1197,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229558</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517120</v>
+        <v>517262</v>
       </c>
       <c r="R7" t="n">
-        <v>6986257</v>
+        <v>6986119</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,14 +1270,35 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt!!</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1320,32 +1315,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129910574</v>
+        <v>129910752</v>
       </c>
       <c r="B8" t="n">
-        <v>79111</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517340</v>
+        <v>516947</v>
       </c>
       <c r="R8" t="n">
-        <v>6986164</v>
+        <v>6986297</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1388,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1405,12 +1405,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129910751</v>
+        <v>129908906</v>
       </c>
       <c r="B21" t="n">
         <v>79087</v>
@@ -2699,16 +2699,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516971</v>
+        <v>517038</v>
       </c>
       <c r="R21" t="n">
-        <v>6986263</v>
+        <v>6986336</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2743,36 +2746,57 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligare med garnlav på ca 10 granar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129908906</v>
+        <v>129910751</v>
       </c>
       <c r="B22" t="n">
         <v>79087</v>
@@ -2801,19 +2825,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517038</v>
+        <v>516971</v>
       </c>
       <c r="R22" t="n">
-        <v>6986336</v>
+        <v>6986263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2848,50 +2869,29 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligare med garnlav på ca 10 granar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -5943,10 +5943,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129910606</v>
+        <v>129910573</v>
       </c>
       <c r="B53" t="n">
-        <v>80192</v>
+        <v>75183</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5954,21 +5954,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>517237</v>
+        <v>517112</v>
       </c>
       <c r="R53" t="n">
-        <v>6986073</v>
+        <v>6986241</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6040,10 +6040,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129910588</v>
+        <v>129908905</v>
       </c>
       <c r="B54" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6051,34 +6051,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>517014</v>
+        <v>517020</v>
       </c>
       <c r="R54" t="n">
-        <v>6986283</v>
+        <v>6986358</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6113,14 +6116,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar i granskog.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6137,27 +6171,27 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129910663</v>
+        <v>129910653</v>
       </c>
       <c r="B55" t="n">
-        <v>80227</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6167,11 +6201,7 @@
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6179,10 +6209,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>517007</v>
+        <v>516971</v>
       </c>
       <c r="R55" t="n">
-        <v>6986367</v>
+        <v>6986287</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6217,6 +6247,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6226,6 +6261,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6242,7 +6292,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129910741</v>
+        <v>129910606</v>
       </c>
       <c r="B56" t="n">
         <v>80192</v>
@@ -6277,10 +6327,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>517046</v>
+        <v>517237</v>
       </c>
       <c r="R56" t="n">
-        <v>6986289</v>
+        <v>6986073</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6315,11 +6365,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6332,19 +6377,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129910630</v>
+        <v>129910588</v>
       </c>
       <c r="B57" t="n">
         <v>80192</v>
@@ -6379,10 +6424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>517275</v>
+        <v>517014</v>
       </c>
       <c r="R57" t="n">
-        <v>6986074</v>
+        <v>6986283</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6441,45 +6486,52 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129910573</v>
+        <v>129910663</v>
       </c>
       <c r="B58" t="n">
-        <v>75183</v>
+        <v>80227</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1460</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>517112</v>
+        <v>517007</v>
       </c>
       <c r="R58" t="n">
-        <v>6986241</v>
+        <v>6986367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6520,6 +6572,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6538,10 +6591,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129908905</v>
+        <v>129910741</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6549,37 +6602,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>517020</v>
+        <v>517046</v>
       </c>
       <c r="R59" t="n">
-        <v>6986358</v>
+        <v>6986289</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6616,7 +6666,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar i granskog.</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6625,54 +6675,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129910653</v>
+        <v>129910630</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6680,37 +6704,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>516971</v>
+        <v>517275</v>
       </c>
       <c r="R60" t="n">
-        <v>6986287</v>
+        <v>6986074</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6745,35 +6766,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -10275,32 +10275,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129910748</v>
+        <v>129910665</v>
       </c>
       <c r="B94" t="n">
-        <v>98797</v>
+        <v>83050</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10310,10 +10310,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>516692</v>
+        <v>517165</v>
       </c>
       <c r="R94" t="n">
-        <v>6986711</v>
+        <v>6986212</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10348,11 +10348,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10365,22 +10360,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129910665</v>
+        <v>129910542</v>
       </c>
       <c r="B95" t="n">
-        <v>83050</v>
+        <v>83058</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10388,21 +10383,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10412,10 +10407,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>517165</v>
+        <v>517009</v>
       </c>
       <c r="R95" t="n">
-        <v>6986212</v>
+        <v>6986437</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10474,10 +10469,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129910542</v>
+        <v>129910739</v>
       </c>
       <c r="B96" t="n">
-        <v>83058</v>
+        <v>80192</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10485,21 +10480,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10509,10 +10504,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>517009</v>
+        <v>517016</v>
       </c>
       <c r="R96" t="n">
-        <v>6986437</v>
+        <v>6986355</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10547,6 +10542,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>2 st sälgar, stående, oklart om levande</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10559,19 +10559,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129910739</v>
+        <v>129910626</v>
       </c>
       <c r="B97" t="n">
         <v>80192</v>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>517016</v>
+        <v>517169</v>
       </c>
       <c r="R97" t="n">
-        <v>6986355</v>
+        <v>6986147</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10644,11 +10644,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>2 st sälgar, stående, oklart om levande</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10661,19 +10656,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129910626</v>
+        <v>129910625</v>
       </c>
       <c r="B98" t="n">
         <v>80192</v>
@@ -10708,10 +10703,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>517169</v>
+        <v>517184</v>
       </c>
       <c r="R98" t="n">
-        <v>6986147</v>
+        <v>6986149</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10770,10 +10765,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129910625</v>
+        <v>129910554</v>
       </c>
       <c r="B99" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10781,34 +10776,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>517184</v>
+        <v>516949</v>
       </c>
       <c r="R99" t="n">
-        <v>6986149</v>
+        <v>6986325</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10841,6 +10844,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10867,53 +10875,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129910554</v>
+        <v>129910748</v>
       </c>
       <c r="B100" t="n">
-        <v>57740</v>
+        <v>98797</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>516949</v>
+        <v>516692</v>
       </c>
       <c r="R100" t="n">
-        <v>6986325</v>
+        <v>6986711</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10965,12 +10965,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11829,39 +11829,39 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129908911</v>
+        <v>129910661</v>
       </c>
       <c r="B109" t="n">
-        <v>79087</v>
+        <v>92200</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -11871,10 +11871,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>516729</v>
+        <v>517220</v>
       </c>
       <c r="R109" t="n">
-        <v>6986683</v>
+        <v>6986131</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11909,11 +11909,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På gran med apothecier.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -11924,29 +11919,19 @@
       <c r="AG109" t="b">
         <v>0</v>
       </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -11964,10 +11949,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129910652</v>
+        <v>129910743</v>
       </c>
       <c r="B110" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11975,37 +11960,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>517345</v>
+        <v>516874</v>
       </c>
       <c r="R110" t="n">
-        <v>6986186</v>
+        <v>6986542</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12040,92 +12022,74 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Liggande död sälg</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129910661</v>
+        <v>129910627</v>
       </c>
       <c r="B111" t="n">
-        <v>92200</v>
+        <v>80192</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>517220</v>
+        <v>517139</v>
       </c>
       <c r="R111" t="n">
-        <v>6986131</v>
+        <v>6986155</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12166,24 +12130,8 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -12200,7 +12148,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129910743</v>
+        <v>129910603</v>
       </c>
       <c r="B112" t="n">
         <v>80192</v>
@@ -12235,10 +12183,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>516874</v>
+        <v>517199</v>
       </c>
       <c r="R112" t="n">
-        <v>6986542</v>
+        <v>6986098</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12273,11 +12221,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Liggande död sälg</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12290,22 +12233,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129910627</v>
+        <v>129908911</v>
       </c>
       <c r="B113" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12313,34 +12256,41 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>517139</v>
+        <v>516729</v>
       </c>
       <c r="R113" t="n">
-        <v>6986155</v>
+        <v>6986683</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12375,14 +12325,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>På gran med apothecier.</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -12399,10 +12380,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129910603</v>
+        <v>129910652</v>
       </c>
       <c r="B114" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12410,34 +12391,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>517199</v>
+        <v>517345</v>
       </c>
       <c r="R114" t="n">
-        <v>6986098</v>
+        <v>6986186</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12478,8 +12462,24 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13172,45 +13172,52 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129910569</v>
+        <v>129910562</v>
       </c>
       <c r="B121" t="n">
-        <v>80193</v>
+        <v>91616</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2081</v>
+        <v>1205</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>517277</v>
+        <v>517126</v>
       </c>
       <c r="R121" t="n">
-        <v>6986118</v>
+        <v>6986211</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13251,8 +13258,24 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -13269,10 +13292,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129910640</v>
+        <v>129910753</v>
       </c>
       <c r="B122" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13280,21 +13303,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13304,10 +13327,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>517288</v>
+        <v>516914</v>
       </c>
       <c r="R122" t="n">
-        <v>6986118</v>
+        <v>6986518</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13342,6 +13365,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>På granar</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -13354,44 +13382,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129910637</v>
+        <v>129910566</v>
       </c>
       <c r="B123" t="n">
-        <v>80192</v>
+        <v>79173</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13401,10 +13429,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>517251</v>
+        <v>517128</v>
       </c>
       <c r="R123" t="n">
-        <v>6986087</v>
+        <v>6986180</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13463,45 +13491,61 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129910605</v>
+        <v>129908895</v>
       </c>
       <c r="B124" t="n">
-        <v>80192</v>
+        <v>98797</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>517273</v>
+        <v>516927</v>
       </c>
       <c r="R124" t="n">
-        <v>6986075</v>
+        <v>6986523</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13536,14 +13580,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor och 3 vinterståndare inom ca 3 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
@@ -13560,10 +13615,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129910635</v>
+        <v>129910569</v>
       </c>
       <c r="B125" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13571,21 +13626,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13595,10 +13650,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>517229</v>
+        <v>517277</v>
       </c>
       <c r="R125" t="n">
-        <v>6986063</v>
+        <v>6986118</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13657,7 +13712,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129910621</v>
+        <v>129910640</v>
       </c>
       <c r="B126" t="n">
         <v>80192</v>
@@ -13692,10 +13747,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>517170</v>
+        <v>517288</v>
       </c>
       <c r="R126" t="n">
-        <v>6986215</v>
+        <v>6986118</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13754,52 +13809,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129910562</v>
+        <v>129910637</v>
       </c>
       <c r="B127" t="n">
-        <v>91616</v>
+        <v>80192</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>517126</v>
+        <v>517251</v>
       </c>
       <c r="R127" t="n">
-        <v>6986211</v>
+        <v>6986087</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13840,24 +13888,8 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
@@ -13874,10 +13906,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129910753</v>
+        <v>129910605</v>
       </c>
       <c r="B128" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13885,21 +13917,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13909,10 +13941,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>516914</v>
+        <v>517273</v>
       </c>
       <c r="R128" t="n">
-        <v>6986518</v>
+        <v>6986075</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13947,11 +13979,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>På granar</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13964,44 +13991,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129910566</v>
+        <v>129910635</v>
       </c>
       <c r="B129" t="n">
-        <v>79173</v>
+        <v>80192</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14011,10 +14038,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>517128</v>
+        <v>517229</v>
       </c>
       <c r="R129" t="n">
-        <v>6986180</v>
+        <v>6986063</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14073,61 +14100,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129908895</v>
+        <v>129910621</v>
       </c>
       <c r="B130" t="n">
-        <v>98797</v>
+        <v>80192</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>516927</v>
+        <v>517170</v>
       </c>
       <c r="R130" t="n">
-        <v>6986523</v>
+        <v>6986215</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14162,25 +14173,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor och 3 vinterståndare inom ca 3 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -14197,52 +14197,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129910659</v>
+        <v>129910624</v>
       </c>
       <c r="B131" t="n">
-        <v>92887</v>
+        <v>80192</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>517328</v>
+        <v>517195</v>
       </c>
       <c r="R131" t="n">
-        <v>6986156</v>
+        <v>6986175</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14283,7 +14276,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14302,61 +14294,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129910560</v>
+        <v>129910747</v>
       </c>
       <c r="B132" t="n">
-        <v>58375</v>
+        <v>80192</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>517237</v>
+        <v>516674</v>
       </c>
       <c r="R132" t="n">
-        <v>6986082</v>
+        <v>6986695</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14391,6 +14367,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på liggande men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -14403,22 +14384,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129910551</v>
+        <v>129910594</v>
       </c>
       <c r="B133" t="n">
-        <v>91605</v>
+        <v>80192</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14426,41 +14407,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>517014</v>
+        <v>517165</v>
       </c>
       <c r="R133" t="n">
-        <v>6986339</v>
+        <v>6986222</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14501,29 +14475,8 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
@@ -14540,7 +14493,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129910624</v>
+        <v>129910584</v>
       </c>
       <c r="B134" t="n">
         <v>80192</v>
@@ -14575,10 +14528,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>517195</v>
+        <v>517004</v>
       </c>
       <c r="R134" t="n">
-        <v>6986175</v>
+        <v>6986361</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14637,7 +14590,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129910747</v>
+        <v>129910634</v>
       </c>
       <c r="B135" t="n">
         <v>80192</v>
@@ -14672,10 +14625,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>516674</v>
+        <v>517233</v>
       </c>
       <c r="R135" t="n">
-        <v>6986695</v>
+        <v>6986069</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14710,11 +14663,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på liggande men levande sälg.</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14727,44 +14675,44 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129910594</v>
+        <v>129910572</v>
       </c>
       <c r="B136" t="n">
-        <v>80192</v>
+        <v>80096</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14774,10 +14722,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>517165</v>
+        <v>517147</v>
       </c>
       <c r="R136" t="n">
-        <v>6986222</v>
+        <v>6986129</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14836,45 +14784,52 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129910584</v>
+        <v>129910659</v>
       </c>
       <c r="B137" t="n">
-        <v>80192</v>
+        <v>92887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>517004</v>
+        <v>517328</v>
       </c>
       <c r="R137" t="n">
-        <v>6986361</v>
+        <v>6986156</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14915,6 +14870,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14933,45 +14889,61 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129910634</v>
+        <v>129910560</v>
       </c>
       <c r="B138" t="n">
-        <v>80192</v>
+        <v>58375</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>102125</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>517233</v>
+        <v>517237</v>
       </c>
       <c r="R138" t="n">
-        <v>6986069</v>
+        <v>6986082</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15030,45 +15002,52 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129910572</v>
+        <v>129910551</v>
       </c>
       <c r="B139" t="n">
-        <v>80096</v>
+        <v>91605</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>517147</v>
+        <v>517014</v>
       </c>
       <c r="R139" t="n">
-        <v>6986129</v>
+        <v>6986339</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15109,8 +15088,29 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
@@ -16221,10 +16221,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129908882</v>
+        <v>129908900</v>
       </c>
       <c r="B150" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16232,46 +16232,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>516646</v>
+        <v>516960</v>
       </c>
       <c r="R150" t="n">
-        <v>6986735</v>
+        <v>6986352</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16308,7 +16299,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
+          <t>På en grovbarkad gammal gran.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16317,12 +16308,13 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
@@ -16337,12 +16329,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -16360,50 +16352,37 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129910648</v>
+        <v>129908909</v>
       </c>
       <c r="B151" t="n">
-        <v>98797</v>
+        <v>79087</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -16411,10 +16390,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>517224</v>
+        <v>516915</v>
       </c>
       <c r="R151" t="n">
-        <v>6986227</v>
+        <v>6986509</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16449,11 +16428,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
@@ -16463,6 +16437,31 @@
       <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16479,7 +16478,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129908900</v>
+        <v>129908903</v>
       </c>
       <c r="B152" t="n">
         <v>79087</v>
@@ -16517,10 +16516,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>516960</v>
+        <v>516956</v>
       </c>
       <c r="R152" t="n">
-        <v>6986352</v>
+        <v>6986419</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16557,7 +16556,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>På en grovbarkad gammal gran.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16577,22 +16576,22 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -16610,10 +16609,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129908909</v>
+        <v>129910587</v>
       </c>
       <c r="B153" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16621,37 +16620,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>516915</v>
+        <v>517018</v>
       </c>
       <c r="R153" t="n">
-        <v>6986509</v>
+        <v>6986301</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16692,34 +16688,8 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
@@ -16736,10 +16706,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129908903</v>
+        <v>129910609</v>
       </c>
       <c r="B154" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16747,37 +16717,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>516956</v>
+        <v>517221</v>
       </c>
       <c r="R154" t="n">
-        <v>6986419</v>
+        <v>6986213</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16812,45 +16779,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>På bark av tall.</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
@@ -16867,7 +16803,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129910587</v>
+        <v>129910745</v>
       </c>
       <c r="B155" t="n">
         <v>80192</v>
@@ -16902,10 +16838,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>517018</v>
+        <v>516739</v>
       </c>
       <c r="R155" t="n">
-        <v>6986301</v>
+        <v>6986664</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16940,6 +16876,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>På stående död sälg</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
@@ -16952,19 +16893,19 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129910609</v>
+        <v>129910607</v>
       </c>
       <c r="B156" t="n">
         <v>80192</v>
@@ -16999,10 +16940,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>517221</v>
+        <v>517246</v>
       </c>
       <c r="R156" t="n">
-        <v>6986213</v>
+        <v>6986091</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17061,10 +17002,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129910745</v>
+        <v>129908882</v>
       </c>
       <c r="B157" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17072,34 +17013,46 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>516739</v>
+        <v>516646</v>
       </c>
       <c r="R157" t="n">
-        <v>6986664</v>
+        <v>6986735</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17136,7 +17089,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>På stående död sälg</t>
+          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17147,61 +17100,102 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129910607</v>
+        <v>129910648</v>
       </c>
       <c r="B158" t="n">
-        <v>80192</v>
+        <v>98797</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>517246</v>
+        <v>517224</v>
       </c>
       <c r="R158" t="n">
-        <v>6986091</v>
+        <v>6986227</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17236,12 +17230,18 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -2670,7 +2670,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129908906</v>
+        <v>129910751</v>
       </c>
       <c r="B21" t="n">
         <v>79087</v>
@@ -2699,19 +2699,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517038</v>
+        <v>516971</v>
       </c>
       <c r="R21" t="n">
-        <v>6986336</v>
+        <v>6986263</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2746,57 +2743,36 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligare med garnlav på ca 10 granar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129910751</v>
+        <v>129908906</v>
       </c>
       <c r="B22" t="n">
         <v>79087</v>
@@ -2825,16 +2801,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516971</v>
+        <v>517038</v>
       </c>
       <c r="R22" t="n">
-        <v>6986263</v>
+        <v>6986336</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,29 +2848,50 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligare med garnlav på ca 10 granar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -12496,32 +12496,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129910644</v>
+        <v>129910738</v>
       </c>
       <c r="B115" t="n">
-        <v>80063</v>
+        <v>80192</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12531,10 +12531,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>517289</v>
+        <v>516965</v>
       </c>
       <c r="R115" t="n">
-        <v>6986084</v>
+        <v>6986379</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12569,6 +12569,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -12581,19 +12586,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129910738</v>
+        <v>129908889</v>
       </c>
       <c r="B116" t="n">
         <v>80192</v>
@@ -12622,16 +12627,23 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>516965</v>
+        <v>516783</v>
       </c>
       <c r="R116" t="n">
-        <v>6986379</v>
+        <v>6986629</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12668,7 +12680,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12677,25 +12689,51 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129908889</v>
+        <v>129908885</v>
       </c>
       <c r="B117" t="n">
         <v>80192</v>
@@ -12737,10 +12775,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>516783</v>
+        <v>517022</v>
       </c>
       <c r="R117" t="n">
-        <v>6986629</v>
+        <v>6986309</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12830,7 +12868,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129908885</v>
+        <v>129910638</v>
       </c>
       <c r="B118" t="n">
         <v>80192</v>
@@ -12859,23 +12897,16 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>517022</v>
+        <v>517253</v>
       </c>
       <c r="R118" t="n">
-        <v>6986309</v>
+        <v>6986103</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12910,45 +12941,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -12965,32 +12965,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129910638</v>
+        <v>129910644</v>
       </c>
       <c r="B119" t="n">
-        <v>80192</v>
+        <v>80063</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>389</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13000,10 +13000,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>517253</v>
+        <v>517289</v>
       </c>
       <c r="R119" t="n">
-        <v>6986103</v>
+        <v>6986084</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13172,52 +13172,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129910562</v>
+        <v>129910569</v>
       </c>
       <c r="B121" t="n">
-        <v>91616</v>
+        <v>80193</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1205</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>517126</v>
+        <v>517277</v>
       </c>
       <c r="R121" t="n">
-        <v>6986211</v>
+        <v>6986118</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13258,24 +13251,8 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -13292,45 +13269,52 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129910753</v>
+        <v>129910562</v>
       </c>
       <c r="B122" t="n">
-        <v>79087</v>
+        <v>91616</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>516914</v>
+        <v>517126</v>
       </c>
       <c r="R122" t="n">
-        <v>6986518</v>
+        <v>6986211</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13365,61 +13349,72 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>På granar</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129910566</v>
+        <v>129910753</v>
       </c>
       <c r="B123" t="n">
-        <v>79173</v>
+        <v>79087</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13429,10 +13424,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>517128</v>
+        <v>516914</v>
       </c>
       <c r="R123" t="n">
-        <v>6986180</v>
+        <v>6986518</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13467,6 +13462,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>På granar</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -13479,73 +13479,57 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129908895</v>
+        <v>129910566</v>
       </c>
       <c r="B124" t="n">
-        <v>98797</v>
+        <v>79173</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>516927</v>
+        <v>517128</v>
       </c>
       <c r="R124" t="n">
-        <v>6986523</v>
+        <v>6986180</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13580,25 +13564,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor och 3 vinterståndare inom ca 3 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
@@ -13615,10 +13588,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129910569</v>
+        <v>129910640</v>
       </c>
       <c r="B125" t="n">
-        <v>80193</v>
+        <v>80192</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13626,21 +13599,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13650,7 +13623,7 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>517277</v>
+        <v>517288</v>
       </c>
       <c r="R125" t="n">
         <v>6986118</v>
@@ -13712,7 +13685,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129910640</v>
+        <v>129910637</v>
       </c>
       <c r="B126" t="n">
         <v>80192</v>
@@ -13747,10 +13720,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>517288</v>
+        <v>517251</v>
       </c>
       <c r="R126" t="n">
-        <v>6986118</v>
+        <v>6986087</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13809,7 +13782,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129910637</v>
+        <v>129910605</v>
       </c>
       <c r="B127" t="n">
         <v>80192</v>
@@ -13844,10 +13817,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>517251</v>
+        <v>517273</v>
       </c>
       <c r="R127" t="n">
-        <v>6986087</v>
+        <v>6986075</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13906,7 +13879,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129910605</v>
+        <v>129910635</v>
       </c>
       <c r="B128" t="n">
         <v>80192</v>
@@ -13941,10 +13914,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>517273</v>
+        <v>517229</v>
       </c>
       <c r="R128" t="n">
-        <v>6986075</v>
+        <v>6986063</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14003,7 +13976,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129910635</v>
+        <v>129910621</v>
       </c>
       <c r="B129" t="n">
         <v>80192</v>
@@ -14038,10 +14011,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>517229</v>
+        <v>517170</v>
       </c>
       <c r="R129" t="n">
-        <v>6986063</v>
+        <v>6986215</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14100,45 +14073,61 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129910621</v>
+        <v>129908895</v>
       </c>
       <c r="B130" t="n">
-        <v>80192</v>
+        <v>98797</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>517170</v>
+        <v>516927</v>
       </c>
       <c r="R130" t="n">
-        <v>6986215</v>
+        <v>6986523</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14173,14 +14162,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor och 3 vinterståndare inom ca 3 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -17260,10 +17260,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910548</v>
+        <v>129908904</v>
       </c>
       <c r="B159" t="n">
-        <v>97043</v>
+        <v>79087</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17271,34 +17271,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>517167</v>
+        <v>516981</v>
       </c>
       <c r="R159" t="n">
-        <v>6986105</v>
+        <v>6986356</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17339,8 +17342,34 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
@@ -18366,10 +18395,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129910550</v>
+        <v>129910558</v>
       </c>
       <c r="B170" t="n">
-        <v>90637</v>
+        <v>57740</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18377,34 +18406,42 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>517343</v>
+        <v>517356</v>
       </c>
       <c r="R170" t="n">
-        <v>6986165</v>
+        <v>6986190</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18437,6 +18474,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18463,10 +18505,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129908910</v>
+        <v>129910550</v>
       </c>
       <c r="B171" t="n">
-        <v>79087</v>
+        <v>90637</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18474,37 +18516,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>516902</v>
+        <v>517343</v>
       </c>
       <c r="R171" t="n">
-        <v>6986521</v>
+        <v>6986165</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18545,34 +18584,8 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
@@ -18589,10 +18602,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129908904</v>
+        <v>129910548</v>
       </c>
       <c r="B172" t="n">
-        <v>79087</v>
+        <v>97043</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18600,37 +18613,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>516981</v>
+        <v>517167</v>
       </c>
       <c r="R172" t="n">
-        <v>6986356</v>
+        <v>6986105</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18671,34 +18681,8 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
@@ -18715,10 +18699,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129910558</v>
+        <v>129908910</v>
       </c>
       <c r="B173" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18726,31 +18710,26 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
@@ -18758,10 +18737,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>517356</v>
+        <v>516902</v>
       </c>
       <c r="R173" t="n">
-        <v>6986190</v>
+        <v>6986521</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18796,19 +18775,40 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910752</v>
+        <v>129910654</v>
       </c>
       <c r="B2" t="n">
         <v>79088</v>
@@ -703,17 +703,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516947</v>
+        <v>517262</v>
       </c>
       <c r="R2" t="n">
-        <v>6986297</v>
+        <v>6986119</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +761,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt!!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,28 +770,44 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129908891</v>
+        <v>129910752</v>
       </c>
       <c r="B3" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,41 +815,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516683</v>
+        <v>516947</v>
       </c>
       <c r="R3" t="n">
-        <v>6986718</v>
+        <v>6986297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,7 +879,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På asp i granskog.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,76 +888,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910667</v>
+        <v>129910577</v>
       </c>
       <c r="B4" t="n">
-        <v>79344</v>
+        <v>80193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517221</v>
+        <v>517035</v>
       </c>
       <c r="R4" t="n">
-        <v>6986209</v>
+        <v>6986429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910557</v>
+        <v>129908891</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,29 +1014,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1052,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517175</v>
+        <v>516683</v>
       </c>
       <c r="R5" t="n">
-        <v>6986155</v>
+        <v>6986718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1085,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>På asp i granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,8 +1094,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1119,53 +1138,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910556</v>
+        <v>129910667</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>79344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517169</v>
+        <v>517221</v>
       </c>
       <c r="R6" t="n">
-        <v>6986201</v>
+        <v>6986209</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,11 +1209,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129910654</v>
+        <v>129910557</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,34 +1343,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1372,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517262</v>
+        <v>517175</v>
       </c>
       <c r="R8" t="n">
-        <v>6986119</v>
+        <v>6986155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt!!</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,24 +1424,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1455,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129910577</v>
+        <v>129910556</v>
       </c>
       <c r="B9" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,34 +1453,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517035</v>
+        <v>517169</v>
       </c>
       <c r="R9" t="n">
-        <v>6986429</v>
+        <v>6986201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,6 +1521,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129910649</v>
+        <v>129910564</v>
       </c>
       <c r="B27" t="n">
-        <v>56921</v>
+        <v>80059</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,50 +3302,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>388</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517134</v>
+        <v>517170</v>
       </c>
       <c r="R27" t="n">
-        <v>6986204</v>
+        <v>6986124</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,6 +3370,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3404,10 +3389,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129908880</v>
+        <v>129910580</v>
       </c>
       <c r="B28" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,46 +3400,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>516686</v>
+        <v>517047</v>
       </c>
       <c r="R28" t="n">
-        <v>6986687</v>
+        <v>6986415</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3489,11 +3462,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3502,31 +3470,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3543,10 +3486,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129910564</v>
+        <v>129910610</v>
       </c>
       <c r="B29" t="n">
-        <v>80059</v>
+        <v>80193</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,21 +3497,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3578,10 +3521,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517170</v>
+        <v>517211</v>
       </c>
       <c r="R29" t="n">
-        <v>6986124</v>
+        <v>6986211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,7 +3565,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3641,7 +3583,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129910580</v>
+        <v>129910599</v>
       </c>
       <c r="B30" t="n">
         <v>80193</v>
@@ -3676,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>517047</v>
+        <v>517177</v>
       </c>
       <c r="R30" t="n">
-        <v>6986415</v>
+        <v>6986167</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3738,7 +3680,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129910610</v>
+        <v>129910620</v>
       </c>
       <c r="B31" t="n">
         <v>80193</v>
@@ -3773,10 +3715,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>517211</v>
+        <v>517112</v>
       </c>
       <c r="R31" t="n">
-        <v>6986211</v>
+        <v>6986273</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3835,32 +3777,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129910599</v>
+        <v>129910668</v>
       </c>
       <c r="B32" t="n">
-        <v>80193</v>
+        <v>79344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3870,10 +3812,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517177</v>
+        <v>517042</v>
       </c>
       <c r="R32" t="n">
-        <v>6986167</v>
+        <v>6986262</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,7 +3874,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129910620</v>
+        <v>129910631</v>
       </c>
       <c r="B33" t="n">
         <v>80193</v>
@@ -3967,10 +3909,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517112</v>
+        <v>517287</v>
       </c>
       <c r="R33" t="n">
-        <v>6986273</v>
+        <v>6986080</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4029,32 +3971,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129910668</v>
+        <v>129910601</v>
       </c>
       <c r="B34" t="n">
-        <v>79344</v>
+        <v>80193</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4064,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517042</v>
+        <v>517170</v>
       </c>
       <c r="R34" t="n">
-        <v>6986262</v>
+        <v>6986161</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4126,7 +4068,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129910631</v>
+        <v>129910592</v>
       </c>
       <c r="B35" t="n">
         <v>80193</v>
@@ -4161,10 +4103,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517287</v>
+        <v>517119</v>
       </c>
       <c r="R35" t="n">
-        <v>6986080</v>
+        <v>6986251</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4223,10 +4165,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129910601</v>
+        <v>129908880</v>
       </c>
       <c r="B36" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4234,34 +4176,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517170</v>
+        <v>516686</v>
       </c>
       <c r="R36" t="n">
-        <v>6986161</v>
+        <v>6986687</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4296,6 +4250,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4304,6 +4263,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4320,10 +4304,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129910592</v>
+        <v>129910649</v>
       </c>
       <c r="B37" t="n">
-        <v>80193</v>
+        <v>56921</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4331,34 +4315,50 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>517119</v>
+        <v>517134</v>
       </c>
       <c r="R37" t="n">
-        <v>6986251</v>
+        <v>6986204</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -6040,10 +6040,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129910588</v>
+        <v>129908905</v>
       </c>
       <c r="B54" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6051,34 +6051,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>517014</v>
+        <v>517020</v>
       </c>
       <c r="R54" t="n">
-        <v>6986283</v>
+        <v>6986358</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6113,14 +6116,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar i granskog.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6137,10 +6171,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129910630</v>
+        <v>129910653</v>
       </c>
       <c r="B55" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6148,34 +6182,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>517275</v>
+        <v>516971</v>
       </c>
       <c r="R55" t="n">
-        <v>6986074</v>
+        <v>6986287</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6210,14 +6247,35 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6234,7 +6292,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129910606</v>
+        <v>129910588</v>
       </c>
       <c r="B56" t="n">
         <v>80193</v>
@@ -6269,10 +6327,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>517237</v>
+        <v>517014</v>
       </c>
       <c r="R56" t="n">
-        <v>6986073</v>
+        <v>6986283</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6331,7 +6389,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129910741</v>
+        <v>129910630</v>
       </c>
       <c r="B57" t="n">
         <v>80193</v>
@@ -6366,10 +6424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>517046</v>
+        <v>517275</v>
       </c>
       <c r="R57" t="n">
-        <v>6986289</v>
+        <v>6986074</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6404,11 +6462,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6421,64 +6474,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129910663</v>
+        <v>129910606</v>
       </c>
       <c r="B58" t="n">
-        <v>80228</v>
+        <v>80193</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>517007</v>
+        <v>517237</v>
       </c>
       <c r="R58" t="n">
-        <v>6986367</v>
+        <v>6986073</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,7 +6565,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6538,10 +6583,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129908905</v>
+        <v>129910741</v>
       </c>
       <c r="B59" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6549,37 +6594,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>517020</v>
+        <v>517046</v>
       </c>
       <c r="R59" t="n">
-        <v>6986358</v>
+        <v>6986289</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6616,7 +6658,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar i granskog.</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6625,71 +6667,45 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129910653</v>
+        <v>129910663</v>
       </c>
       <c r="B60" t="n">
-        <v>79088</v>
+        <v>80228</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6699,7 +6715,11 @@
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6707,10 +6727,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>516971</v>
+        <v>517007</v>
       </c>
       <c r="R60" t="n">
-        <v>6986287</v>
+        <v>6986367</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6745,11 +6765,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6759,21 +6774,6 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8719,57 +8719,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129908881</v>
+        <v>129910565</v>
       </c>
       <c r="B79" t="n">
-        <v>57740</v>
+        <v>79174</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>516659</v>
+        <v>517235</v>
       </c>
       <c r="R79" t="n">
-        <v>6986705</v>
+        <v>6986250</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8804,11 +8792,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8817,31 +8800,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8858,32 +8816,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129910565</v>
+        <v>129910541</v>
       </c>
       <c r="B80" t="n">
-        <v>79174</v>
+        <v>83059</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6450</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8893,10 +8851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>517235</v>
+        <v>517005</v>
       </c>
       <c r="R80" t="n">
-        <v>6986250</v>
+        <v>6986418</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8955,10 +8913,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129910541</v>
+        <v>129908881</v>
       </c>
       <c r="B81" t="n">
-        <v>83059</v>
+        <v>57740</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8966,34 +8924,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>517005</v>
+        <v>516659</v>
       </c>
       <c r="R81" t="n">
-        <v>6986418</v>
+        <v>6986705</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9028,6 +8998,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9036,6 +9011,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10275,32 +10275,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129910665</v>
+        <v>129910748</v>
       </c>
       <c r="B94" t="n">
-        <v>83051</v>
+        <v>98798</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10310,10 +10310,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>517165</v>
+        <v>516692</v>
       </c>
       <c r="R94" t="n">
-        <v>6986212</v>
+        <v>6986711</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10348,6 +10348,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10360,22 +10365,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129910554</v>
+        <v>129910739</v>
       </c>
       <c r="B95" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10383,42 +10388,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>516949</v>
+        <v>517016</v>
       </c>
       <c r="R95" t="n">
-        <v>6986325</v>
+        <v>6986355</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10455,7 +10452,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>2 st sälgar, stående, oklart om levande</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10470,19 +10467,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129910739</v>
+        <v>129910625</v>
       </c>
       <c r="B96" t="n">
         <v>80193</v>
@@ -10517,10 +10514,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>517016</v>
+        <v>517184</v>
       </c>
       <c r="R96" t="n">
-        <v>6986355</v>
+        <v>6986149</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10555,11 +10552,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>2 st sälgar, stående, oklart om levande</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10572,19 +10564,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129910625</v>
+        <v>129910626</v>
       </c>
       <c r="B97" t="n">
         <v>80193</v>
@@ -10619,10 +10611,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>517184</v>
+        <v>517169</v>
       </c>
       <c r="R97" t="n">
-        <v>6986149</v>
+        <v>6986147</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10681,10 +10673,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129910626</v>
+        <v>129910542</v>
       </c>
       <c r="B98" t="n">
-        <v>80193</v>
+        <v>83059</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10692,21 +10684,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10716,10 +10708,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>517169</v>
+        <v>517009</v>
       </c>
       <c r="R98" t="n">
-        <v>6986147</v>
+        <v>6986437</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10778,10 +10770,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129910542</v>
+        <v>129910665</v>
       </c>
       <c r="B99" t="n">
-        <v>83059</v>
+        <v>83051</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10789,21 +10781,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10813,10 +10805,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>517009</v>
+        <v>517165</v>
       </c>
       <c r="R99" t="n">
-        <v>6986437</v>
+        <v>6986212</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10875,45 +10867,53 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129910748</v>
+        <v>129910554</v>
       </c>
       <c r="B100" t="n">
-        <v>98798</v>
+        <v>57740</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>516692</v>
+        <v>516949</v>
       </c>
       <c r="R100" t="n">
-        <v>6986711</v>
+        <v>6986325</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10965,12 +10965,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12593,10 +12593,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129910638</v>
+        <v>129910553</v>
       </c>
       <c r="B116" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12604,34 +12604,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>517253</v>
+        <v>516968</v>
       </c>
       <c r="R116" t="n">
-        <v>6986103</v>
+        <v>6986277</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12664,6 +12672,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12690,7 +12703,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129910738</v>
+        <v>129910638</v>
       </c>
       <c r="B117" t="n">
         <v>80193</v>
@@ -12725,10 +12738,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>516965</v>
+        <v>517253</v>
       </c>
       <c r="R117" t="n">
-        <v>6986379</v>
+        <v>6986103</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12763,11 +12776,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12780,19 +12788,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129908885</v>
+        <v>129910738</v>
       </c>
       <c r="B118" t="n">
         <v>80193</v>
@@ -12821,23 +12829,16 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>517022</v>
+        <v>516965</v>
       </c>
       <c r="R118" t="n">
-        <v>6986309</v>
+        <v>6986379</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12874,7 +12875,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12883,51 +12884,25 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129908889</v>
+        <v>129908885</v>
       </c>
       <c r="B119" t="n">
         <v>80193</v>
@@ -12969,10 +12944,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>516783</v>
+        <v>517022</v>
       </c>
       <c r="R119" t="n">
-        <v>6986629</v>
+        <v>6986309</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13062,10 +13037,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129910553</v>
+        <v>129908889</v>
       </c>
       <c r="B120" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13073,29 +13048,28 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -13105,10 +13079,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>516968</v>
+        <v>516783</v>
       </c>
       <c r="R120" t="n">
-        <v>6986277</v>
+        <v>6986629</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13145,7 +13119,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13154,8 +13128,34 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
@@ -13389,10 +13389,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129910640</v>
+        <v>129910753</v>
       </c>
       <c r="B123" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13400,21 +13400,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13424,10 +13424,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>517288</v>
+        <v>516914</v>
       </c>
       <c r="R123" t="n">
-        <v>6986118</v>
+        <v>6986518</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13462,6 +13462,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>På granar</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -13474,19 +13479,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129910621</v>
+        <v>129910640</v>
       </c>
       <c r="B124" t="n">
         <v>80193</v>
@@ -13521,10 +13526,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>517170</v>
+        <v>517288</v>
       </c>
       <c r="R124" t="n">
-        <v>6986215</v>
+        <v>6986118</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13583,7 +13588,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129910635</v>
+        <v>129910621</v>
       </c>
       <c r="B125" t="n">
         <v>80193</v>
@@ -13618,10 +13623,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>517229</v>
+        <v>517170</v>
       </c>
       <c r="R125" t="n">
-        <v>6986063</v>
+        <v>6986215</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13680,7 +13685,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129910605</v>
+        <v>129910635</v>
       </c>
       <c r="B126" t="n">
         <v>80193</v>
@@ -13715,10 +13720,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>517273</v>
+        <v>517229</v>
       </c>
       <c r="R126" t="n">
-        <v>6986075</v>
+        <v>6986063</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13777,32 +13782,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129910566</v>
+        <v>129910605</v>
       </c>
       <c r="B127" t="n">
-        <v>79174</v>
+        <v>80193</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13812,10 +13817,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>517128</v>
+        <v>517273</v>
       </c>
       <c r="R127" t="n">
-        <v>6986180</v>
+        <v>6986075</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13874,10 +13879,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129910753</v>
+        <v>129910637</v>
       </c>
       <c r="B128" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13885,21 +13890,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13909,10 +13914,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>516914</v>
+        <v>517251</v>
       </c>
       <c r="R128" t="n">
-        <v>6986518</v>
+        <v>6986087</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13947,11 +13952,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>På granar</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13964,44 +13964,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129910637</v>
+        <v>129910566</v>
       </c>
       <c r="B129" t="n">
-        <v>80193</v>
+        <v>79174</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14011,10 +14011,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>517251</v>
+        <v>517128</v>
       </c>
       <c r="R129" t="n">
-        <v>6986087</v>
+        <v>6986180</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16221,10 +16221,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129910607</v>
+        <v>129908900</v>
       </c>
       <c r="B150" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16232,34 +16232,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>517246</v>
+        <v>516960</v>
       </c>
       <c r="R150" t="n">
-        <v>6986091</v>
+        <v>6986352</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16294,14 +16297,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal gran.</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -16318,10 +16352,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129910587</v>
+        <v>129908909</v>
       </c>
       <c r="B151" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16329,34 +16363,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>517018</v>
+        <v>516915</v>
       </c>
       <c r="R151" t="n">
-        <v>6986301</v>
+        <v>6986509</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16397,8 +16434,34 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16415,10 +16478,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129910609</v>
+        <v>129908903</v>
       </c>
       <c r="B152" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16426,34 +16489,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>517221</v>
+        <v>516956</v>
       </c>
       <c r="R152" t="n">
-        <v>6986213</v>
+        <v>6986419</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16488,14 +16554,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>På bark av tall.</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16512,7 +16609,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129910745</v>
+        <v>129910607</v>
       </c>
       <c r="B153" t="n">
         <v>80193</v>
@@ -16547,10 +16644,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>516739</v>
+        <v>517246</v>
       </c>
       <c r="R153" t="n">
-        <v>6986664</v>
+        <v>6986091</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16585,11 +16682,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>På stående död sälg</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -16602,22 +16694,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129908882</v>
+        <v>129910587</v>
       </c>
       <c r="B154" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16625,46 +16717,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>516646</v>
+        <v>517018</v>
       </c>
       <c r="R154" t="n">
-        <v>6986735</v>
+        <v>6986301</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16699,11 +16779,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -16712,31 +16787,6 @@
       </c>
       <c r="AG154" t="b">
         <v>0</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
@@ -16753,10 +16803,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129908900</v>
+        <v>129910609</v>
       </c>
       <c r="B155" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16764,37 +16814,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>516960</v>
+        <v>517221</v>
       </c>
       <c r="R155" t="n">
-        <v>6986352</v>
+        <v>6986213</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16829,45 +16876,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal gran.</t>
-        </is>
-      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -16884,10 +16900,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129908909</v>
+        <v>129910745</v>
       </c>
       <c r="B156" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16895,37 +16911,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>516915</v>
+        <v>516739</v>
       </c>
       <c r="R156" t="n">
-        <v>6986509</v>
+        <v>6986664</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16960,87 +16973,79 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På stående död sälg</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129908903</v>
+        <v>129910648</v>
       </c>
       <c r="B157" t="n">
-        <v>79088</v>
+        <v>98798</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -17048,10 +17053,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>516956</v>
+        <v>517224</v>
       </c>
       <c r="R157" t="n">
-        <v>6986419</v>
+        <v>6986227</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17088,7 +17093,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17100,31 +17105,6 @@
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
@@ -17141,61 +17121,57 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129910648</v>
+        <v>129908882</v>
       </c>
       <c r="B158" t="n">
-        <v>98798</v>
+        <v>57740</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>517224</v>
+        <v>516646</v>
       </c>
       <c r="R158" t="n">
-        <v>6986227</v>
+        <v>6986735</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17232,7 +17208,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17241,9 +17217,33 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
@@ -17260,10 +17260,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910548</v>
+        <v>129910558</v>
       </c>
       <c r="B159" t="n">
-        <v>97044</v>
+        <v>57740</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17271,34 +17271,42 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>517167</v>
+        <v>517356</v>
       </c>
       <c r="R159" t="n">
-        <v>6986105</v>
+        <v>6986190</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17331,6 +17339,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17357,10 +17370,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910550</v>
+        <v>129910548</v>
       </c>
       <c r="B160" t="n">
-        <v>90638</v>
+        <v>97044</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17368,21 +17381,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1962</v>
+        <v>53</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17392,10 +17405,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>517343</v>
+        <v>517167</v>
       </c>
       <c r="R160" t="n">
-        <v>6986165</v>
+        <v>6986105</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17454,10 +17467,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129908910</v>
+        <v>129910550</v>
       </c>
       <c r="B161" t="n">
-        <v>79088</v>
+        <v>90638</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17465,37 +17478,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>516902</v>
+        <v>517343</v>
       </c>
       <c r="R161" t="n">
-        <v>6986521</v>
+        <v>6986165</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17536,34 +17546,8 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
@@ -17580,7 +17564,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129908904</v>
+        <v>129908910</v>
       </c>
       <c r="B162" t="n">
         <v>79088</v>
@@ -17618,10 +17602,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>516981</v>
+        <v>516902</v>
       </c>
       <c r="R162" t="n">
-        <v>6986356</v>
+        <v>6986521</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17668,7 +17652,7 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -17706,7 +17690,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129908907</v>
+        <v>129908904</v>
       </c>
       <c r="B163" t="n">
         <v>79088</v>
@@ -17744,10 +17728,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>517033</v>
+        <v>516981</v>
       </c>
       <c r="R163" t="n">
-        <v>6986307</v>
+        <v>6986356</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17782,11 +17766,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>På en gammal gran i granskog.</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
@@ -17799,7 +17778,7 @@
       </c>
       <c r="AH163" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
@@ -17837,10 +17816,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129910744</v>
+        <v>129908907</v>
       </c>
       <c r="B164" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17848,34 +17827,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>516858</v>
+        <v>517033</v>
       </c>
       <c r="R164" t="n">
-        <v>6986573</v>
+        <v>6986307</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17912,7 +17894,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>På både en lutande död sälg och en stående avbruten sälg.</t>
+          <t>På en gammal gran i granskog.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17921,25 +17903,51 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129910611</v>
+        <v>129910744</v>
       </c>
       <c r="B165" t="n">
         <v>80193</v>
@@ -17974,10 +17982,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>517216</v>
+        <v>516858</v>
       </c>
       <c r="R165" t="n">
-        <v>6986197</v>
+        <v>6986573</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18012,6 +18020,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>På både en lutande död sälg och en stående avbruten sälg.</t>
+        </is>
+      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
@@ -18024,19 +18037,19 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129910598</v>
+        <v>129910611</v>
       </c>
       <c r="B166" t="n">
         <v>80193</v>
@@ -18071,10 +18084,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>517155</v>
+        <v>517216</v>
       </c>
       <c r="R166" t="n">
-        <v>6986194</v>
+        <v>6986197</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18133,7 +18146,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129910628</v>
+        <v>129910598</v>
       </c>
       <c r="B167" t="n">
         <v>80193</v>
@@ -18168,10 +18181,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>517207</v>
+        <v>517155</v>
       </c>
       <c r="R167" t="n">
-        <v>6986088</v>
+        <v>6986194</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18230,32 +18243,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129910669</v>
+        <v>129910628</v>
       </c>
       <c r="B168" t="n">
-        <v>79344</v>
+        <v>80193</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18265,10 +18278,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>517113</v>
+        <v>517207</v>
       </c>
       <c r="R168" t="n">
-        <v>6986244</v>
+        <v>6986088</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18327,32 +18340,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129910586</v>
+        <v>129910669</v>
       </c>
       <c r="B169" t="n">
-        <v>80193</v>
+        <v>79344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18362,10 +18375,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>517006</v>
+        <v>517113</v>
       </c>
       <c r="R169" t="n">
-        <v>6986354</v>
+        <v>6986244</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18424,7 +18437,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129910616</v>
+        <v>129910586</v>
       </c>
       <c r="B170" t="n">
         <v>80193</v>
@@ -18459,10 +18472,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>517030</v>
+        <v>517006</v>
       </c>
       <c r="R170" t="n">
-        <v>6986400</v>
+        <v>6986354</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18521,7 +18534,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129910576</v>
+        <v>129910616</v>
       </c>
       <c r="B171" t="n">
         <v>80193</v>
@@ -18556,10 +18569,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>516994</v>
+        <v>517030</v>
       </c>
       <c r="R171" t="n">
-        <v>6986453</v>
+        <v>6986400</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18618,7 +18631,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129910623</v>
+        <v>129910576</v>
       </c>
       <c r="B172" t="n">
         <v>80193</v>
@@ -18653,10 +18666,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>517174</v>
+        <v>516994</v>
       </c>
       <c r="R172" t="n">
-        <v>6986187</v>
+        <v>6986453</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18715,10 +18728,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129910558</v>
+        <v>129910623</v>
       </c>
       <c r="B173" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18726,42 +18739,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>517356</v>
+        <v>517174</v>
       </c>
       <c r="R173" t="n">
-        <v>6986190</v>
+        <v>6986187</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18794,11 +18799,6 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD173" t="b">

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -1746,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129910643</v>
+        <v>129910549</v>
       </c>
       <c r="B12" t="n">
-        <v>80064</v>
+        <v>79707</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>389</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517173</v>
+        <v>517088</v>
       </c>
       <c r="R12" t="n">
-        <v>6986129</v>
+        <v>6986173</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129908878</v>
+        <v>129910544</v>
       </c>
       <c r="B13" t="n">
-        <v>91606</v>
+        <v>83059</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,41 +1854,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516921</v>
+        <v>517187</v>
       </c>
       <c r="R13" t="n">
-        <v>6986515</v>
+        <v>6986154</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,45 +1916,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I en granlåga i granskog.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1978,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129910614</v>
+        <v>129908878</v>
       </c>
       <c r="B14" t="n">
-        <v>80193</v>
+        <v>91606</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,34 +1951,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517123</v>
+        <v>516921</v>
       </c>
       <c r="R14" t="n">
-        <v>6986159</v>
+        <v>6986515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,14 +2020,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I en granlåga i granskog.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2075,32 +2075,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129910597</v>
+        <v>129910643</v>
       </c>
       <c r="B15" t="n">
-        <v>80193</v>
+        <v>80064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>389</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517147</v>
+        <v>517173</v>
       </c>
       <c r="R15" t="n">
-        <v>6986201</v>
+        <v>6986129</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,7 +2172,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129910585</v>
+        <v>129910614</v>
       </c>
       <c r="B16" t="n">
         <v>80193</v>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517011</v>
+        <v>517123</v>
       </c>
       <c r="R16" t="n">
-        <v>6986357</v>
+        <v>6986159</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129910596</v>
+        <v>129910597</v>
       </c>
       <c r="B17" t="n">
         <v>80193</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517141</v>
+        <v>517147</v>
       </c>
       <c r="R17" t="n">
-        <v>6986196</v>
+        <v>6986201</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129910549</v>
+        <v>129910585</v>
       </c>
       <c r="B18" t="n">
-        <v>79707</v>
+        <v>80193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517088</v>
+        <v>517011</v>
       </c>
       <c r="R18" t="n">
-        <v>6986173</v>
+        <v>6986357</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129910544</v>
+        <v>129910596</v>
       </c>
       <c r="B19" t="n">
-        <v>83059</v>
+        <v>80193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,21 +2474,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517187</v>
+        <v>517141</v>
       </c>
       <c r="R19" t="n">
-        <v>6986154</v>
+        <v>6986196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129908906</v>
+        <v>129910579</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2681,37 +2681,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517038</v>
+        <v>517061</v>
       </c>
       <c r="R21" t="n">
-        <v>6986336</v>
+        <v>6986424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2752,34 +2749,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2796,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129910751</v>
+        <v>129910615</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2807,21 +2778,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2831,10 +2802,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516971</v>
+        <v>517004</v>
       </c>
       <c r="R22" t="n">
-        <v>6986263</v>
+        <v>6986426</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,11 +2840,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligare med garnlav på ca 10 granar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2886,19 +2852,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129910579</v>
+        <v>129910742</v>
       </c>
       <c r="B23" t="n">
         <v>80193</v>
@@ -2933,10 +2899,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517061</v>
+        <v>516904</v>
       </c>
       <c r="R23" t="n">
-        <v>6986424</v>
+        <v>6986470</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,6 +2937,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på asp</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2983,19 +2954,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129910615</v>
+        <v>129910613</v>
       </c>
       <c r="B24" t="n">
         <v>80193</v>
@@ -3030,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517004</v>
+        <v>517125</v>
       </c>
       <c r="R24" t="n">
-        <v>6986426</v>
+        <v>6986172</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,10 +3063,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129910742</v>
+        <v>129908906</v>
       </c>
       <c r="B25" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3103,34 +3074,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516904</v>
+        <v>517038</v>
       </c>
       <c r="R25" t="n">
-        <v>6986470</v>
+        <v>6986336</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3165,39 +3139,60 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129910613</v>
+        <v>129910751</v>
       </c>
       <c r="B26" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,21 +3200,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3229,10 +3224,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>517125</v>
+        <v>516971</v>
       </c>
       <c r="R26" t="n">
-        <v>6986172</v>
+        <v>6986263</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3267,6 +3262,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligare med garnlav på ca 10 granar.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3279,22 +3279,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129910564</v>
+        <v>129910649</v>
       </c>
       <c r="B27" t="n">
-        <v>80059</v>
+        <v>56921</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,34 +3302,50 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>388</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517170</v>
+        <v>517134</v>
       </c>
       <c r="R27" t="n">
-        <v>6986124</v>
+        <v>6986204</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3386,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3389,10 +3404,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129910580</v>
+        <v>129908880</v>
       </c>
       <c r="B28" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3400,34 +3415,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517047</v>
+        <v>516686</v>
       </c>
       <c r="R28" t="n">
-        <v>6986415</v>
+        <v>6986687</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3462,6 +3489,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3470,6 +3502,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3486,10 +3543,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129910610</v>
+        <v>129910564</v>
       </c>
       <c r="B29" t="n">
-        <v>80193</v>
+        <v>80059</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3497,21 +3554,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3521,10 +3578,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517211</v>
+        <v>517170</v>
       </c>
       <c r="R29" t="n">
-        <v>6986211</v>
+        <v>6986124</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3565,6 +3622,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3583,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129910599</v>
+        <v>129910580</v>
       </c>
       <c r="B30" t="n">
         <v>80193</v>
@@ -3618,10 +3676,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>517177</v>
+        <v>517047</v>
       </c>
       <c r="R30" t="n">
-        <v>6986167</v>
+        <v>6986415</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3738,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129910620</v>
+        <v>129910610</v>
       </c>
       <c r="B31" t="n">
         <v>80193</v>
@@ -3715,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>517112</v>
+        <v>517211</v>
       </c>
       <c r="R31" t="n">
-        <v>6986273</v>
+        <v>6986211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3777,32 +3835,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129910668</v>
+        <v>129910599</v>
       </c>
       <c r="B32" t="n">
-        <v>79344</v>
+        <v>80193</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3812,10 +3870,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517042</v>
+        <v>517177</v>
       </c>
       <c r="R32" t="n">
-        <v>6986262</v>
+        <v>6986167</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3874,7 +3932,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129910631</v>
+        <v>129910620</v>
       </c>
       <c r="B33" t="n">
         <v>80193</v>
@@ -3909,10 +3967,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517287</v>
+        <v>517112</v>
       </c>
       <c r="R33" t="n">
-        <v>6986080</v>
+        <v>6986273</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3971,32 +4029,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129910601</v>
+        <v>129910668</v>
       </c>
       <c r="B34" t="n">
-        <v>80193</v>
+        <v>79344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4006,10 +4064,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517170</v>
+        <v>517042</v>
       </c>
       <c r="R34" t="n">
-        <v>6986161</v>
+        <v>6986262</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4068,7 +4126,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129910592</v>
+        <v>129910631</v>
       </c>
       <c r="B35" t="n">
         <v>80193</v>
@@ -4103,10 +4161,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517119</v>
+        <v>517287</v>
       </c>
       <c r="R35" t="n">
-        <v>6986251</v>
+        <v>6986080</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4165,10 +4223,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129908880</v>
+        <v>129910601</v>
       </c>
       <c r="B36" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,46 +4234,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>516686</v>
+        <v>517170</v>
       </c>
       <c r="R36" t="n">
-        <v>6986687</v>
+        <v>6986161</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,11 +4296,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4263,31 +4304,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4304,10 +4320,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129910649</v>
+        <v>129910592</v>
       </c>
       <c r="B37" t="n">
-        <v>56921</v>
+        <v>80193</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4315,50 +4331,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>517134</v>
+        <v>517119</v>
       </c>
       <c r="R37" t="n">
-        <v>6986204</v>
+        <v>6986251</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4417,10 +4417,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129910655</v>
+        <v>129910581</v>
       </c>
       <c r="B38" t="n">
-        <v>82925</v>
+        <v>80193</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4428,21 +4428,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>516970</v>
+        <v>517011</v>
       </c>
       <c r="R38" t="n">
-        <v>6986375</v>
+        <v>6986383</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129910567</v>
+        <v>129910589</v>
       </c>
       <c r="B39" t="n">
-        <v>80194</v>
+        <v>80193</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4525,21 +4525,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>517062</v>
+        <v>517055</v>
       </c>
       <c r="R39" t="n">
-        <v>6986268</v>
+        <v>6986272</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129910581</v>
+        <v>129910578</v>
       </c>
       <c r="B40" t="n">
         <v>80193</v>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>517011</v>
+        <v>517037</v>
       </c>
       <c r="R40" t="n">
-        <v>6986383</v>
+        <v>6986432</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129910589</v>
+        <v>129910629</v>
       </c>
       <c r="B41" t="n">
         <v>80193</v>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>517055</v>
+        <v>517270</v>
       </c>
       <c r="R41" t="n">
-        <v>6986272</v>
+        <v>6986036</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4805,10 +4805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129910578</v>
+        <v>129910655</v>
       </c>
       <c r="B42" t="n">
-        <v>80193</v>
+        <v>82925</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4816,21 +4816,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>517037</v>
+        <v>516970</v>
       </c>
       <c r="R42" t="n">
-        <v>6986432</v>
+        <v>6986375</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4902,10 +4902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129910629</v>
+        <v>129910567</v>
       </c>
       <c r="B43" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4913,21 +4913,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>517270</v>
+        <v>517062</v>
       </c>
       <c r="R43" t="n">
-        <v>6986036</v>
+        <v>6986268</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,45 +4999,61 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129910646</v>
+        <v>129908896</v>
       </c>
       <c r="B44" t="n">
-        <v>80153</v>
+        <v>98798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>517237</v>
+        <v>516925</v>
       </c>
       <c r="R44" t="n">
-        <v>6986059</v>
+        <v>6986509</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5072,14 +5088,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5096,61 +5123,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129908896</v>
+        <v>129910646</v>
       </c>
       <c r="B45" t="n">
-        <v>98798</v>
+        <v>80153</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>516925</v>
+        <v>517237</v>
       </c>
       <c r="R45" t="n">
-        <v>6986509</v>
+        <v>6986059</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5185,25 +5196,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5220,10 +5220,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129910547</v>
+        <v>129910750</v>
       </c>
       <c r="B46" t="n">
-        <v>97044</v>
+        <v>79088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5231,21 +5231,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>517122</v>
+        <v>517017</v>
       </c>
       <c r="R46" t="n">
-        <v>6986191</v>
+        <v>6986332</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5293,6 +5293,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5305,57 +5310,64 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129910750</v>
+        <v>129910660</v>
       </c>
       <c r="B47" t="n">
-        <v>79088</v>
+        <v>92201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>517017</v>
+        <v>517050</v>
       </c>
       <c r="R47" t="n">
-        <v>6986332</v>
+        <v>6986414</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5390,39 +5402,50 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129910632</v>
+        <v>129910547</v>
       </c>
       <c r="B48" t="n">
-        <v>80193</v>
+        <v>97044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5430,21 +5453,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5454,10 +5477,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>517285</v>
+        <v>517122</v>
       </c>
       <c r="R48" t="n">
-        <v>6986090</v>
+        <v>6986191</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5516,10 +5539,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129910591</v>
+        <v>129910568</v>
       </c>
       <c r="B49" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5527,21 +5550,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5551,10 +5574,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>517068</v>
+        <v>517230</v>
       </c>
       <c r="R49" t="n">
-        <v>6986257</v>
+        <v>6986059</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5613,52 +5636,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129910660</v>
+        <v>129910632</v>
       </c>
       <c r="B50" t="n">
-        <v>92201</v>
+        <v>80193</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>517050</v>
+        <v>517285</v>
       </c>
       <c r="R50" t="n">
-        <v>6986414</v>
+        <v>6986090</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5699,24 +5715,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5733,10 +5733,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129910568</v>
+        <v>129910591</v>
       </c>
       <c r="B51" t="n">
-        <v>80194</v>
+        <v>80193</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5744,21 +5744,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5768,10 +5768,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>517230</v>
+        <v>517068</v>
       </c>
       <c r="R51" t="n">
-        <v>6986059</v>
+        <v>6986257</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6040,10 +6040,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129908905</v>
+        <v>129910588</v>
       </c>
       <c r="B54" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6051,37 +6051,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>517020</v>
+        <v>517014</v>
       </c>
       <c r="R54" t="n">
-        <v>6986358</v>
+        <v>6986283</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6116,45 +6113,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6171,10 +6137,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129910653</v>
+        <v>129910630</v>
       </c>
       <c r="B55" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6182,37 +6148,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>516971</v>
+        <v>517275</v>
       </c>
       <c r="R55" t="n">
-        <v>6986287</v>
+        <v>6986074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6247,35 +6210,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6292,7 +6234,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129910588</v>
+        <v>129910606</v>
       </c>
       <c r="B56" t="n">
         <v>80193</v>
@@ -6327,10 +6269,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>517014</v>
+        <v>517237</v>
       </c>
       <c r="R56" t="n">
-        <v>6986283</v>
+        <v>6986073</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6389,7 +6331,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129910630</v>
+        <v>129910741</v>
       </c>
       <c r="B57" t="n">
         <v>80193</v>
@@ -6424,10 +6366,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>517275</v>
+        <v>517046</v>
       </c>
       <c r="R57" t="n">
-        <v>6986074</v>
+        <v>6986289</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6462,6 +6404,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6474,57 +6421,64 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129910606</v>
+        <v>129910663</v>
       </c>
       <c r="B58" t="n">
-        <v>80193</v>
+        <v>80228</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>517237</v>
+        <v>517007</v>
       </c>
       <c r="R58" t="n">
-        <v>6986073</v>
+        <v>6986367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6565,6 +6519,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6583,10 +6538,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129910741</v>
+        <v>129908905</v>
       </c>
       <c r="B59" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6594,34 +6549,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>517046</v>
+        <v>517020</v>
       </c>
       <c r="R59" t="n">
-        <v>6986289</v>
+        <v>6986358</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6658,7 +6616,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Långväxta bålar på flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6667,45 +6625,71 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129910663</v>
+        <v>129910653</v>
       </c>
       <c r="B60" t="n">
-        <v>80228</v>
+        <v>79088</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6715,11 +6699,7 @@
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6727,10 +6707,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>517007</v>
+        <v>516971</v>
       </c>
       <c r="R60" t="n">
-        <v>6986367</v>
+        <v>6986287</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6765,6 +6745,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6774,6 +6759,21 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -10275,32 +10275,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129910748</v>
+        <v>129910665</v>
       </c>
       <c r="B94" t="n">
-        <v>98798</v>
+        <v>83051</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10310,10 +10310,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>516692</v>
+        <v>517165</v>
       </c>
       <c r="R94" t="n">
-        <v>6986711</v>
+        <v>6986212</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10348,11 +10348,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10365,22 +10360,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129910739</v>
+        <v>129910554</v>
       </c>
       <c r="B95" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10388,34 +10383,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>517016</v>
+        <v>516949</v>
       </c>
       <c r="R95" t="n">
-        <v>6986355</v>
+        <v>6986325</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10452,7 +10455,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>2 st sälgar, stående, oklart om levande</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10467,19 +10470,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129910625</v>
+        <v>129910739</v>
       </c>
       <c r="B96" t="n">
         <v>80193</v>
@@ -10514,10 +10517,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>517184</v>
+        <v>517016</v>
       </c>
       <c r="R96" t="n">
-        <v>6986149</v>
+        <v>6986355</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10552,6 +10555,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>2 st sälgar, stående, oklart om levande</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10564,19 +10572,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129910626</v>
+        <v>129910625</v>
       </c>
       <c r="B97" t="n">
         <v>80193</v>
@@ -10611,10 +10619,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>517169</v>
+        <v>517184</v>
       </c>
       <c r="R97" t="n">
-        <v>6986147</v>
+        <v>6986149</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10673,10 +10681,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129910542</v>
+        <v>129910626</v>
       </c>
       <c r="B98" t="n">
-        <v>83059</v>
+        <v>80193</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10684,21 +10692,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10708,10 +10716,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>517009</v>
+        <v>517169</v>
       </c>
       <c r="R98" t="n">
-        <v>6986437</v>
+        <v>6986147</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10770,10 +10778,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129910665</v>
+        <v>129910542</v>
       </c>
       <c r="B99" t="n">
-        <v>83051</v>
+        <v>83059</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10781,21 +10789,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10805,10 +10813,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>517165</v>
+        <v>517009</v>
       </c>
       <c r="R99" t="n">
-        <v>6986212</v>
+        <v>6986437</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10867,53 +10875,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129910554</v>
+        <v>129910748</v>
       </c>
       <c r="B100" t="n">
-        <v>57740</v>
+        <v>98798</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>516949</v>
+        <v>516692</v>
       </c>
       <c r="R100" t="n">
-        <v>6986325</v>
+        <v>6986711</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10965,12 +10965,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12593,10 +12593,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129910553</v>
+        <v>129910638</v>
       </c>
       <c r="B116" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12604,42 +12604,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>516968</v>
+        <v>517253</v>
       </c>
       <c r="R116" t="n">
-        <v>6986277</v>
+        <v>6986103</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12672,11 +12664,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12703,7 +12690,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129910638</v>
+        <v>129910738</v>
       </c>
       <c r="B117" t="n">
         <v>80193</v>
@@ -12738,10 +12725,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>517253</v>
+        <v>516965</v>
       </c>
       <c r="R117" t="n">
-        <v>6986103</v>
+        <v>6986379</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12776,6 +12763,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12788,19 +12780,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129910738</v>
+        <v>129908885</v>
       </c>
       <c r="B118" t="n">
         <v>80193</v>
@@ -12829,16 +12821,23 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>516965</v>
+        <v>517022</v>
       </c>
       <c r="R118" t="n">
-        <v>6986379</v>
+        <v>6986309</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12875,7 +12874,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12884,25 +12883,51 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129908885</v>
+        <v>129908889</v>
       </c>
       <c r="B119" t="n">
         <v>80193</v>
@@ -12944,10 +12969,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>517022</v>
+        <v>516783</v>
       </c>
       <c r="R119" t="n">
-        <v>6986309</v>
+        <v>6986629</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13037,10 +13062,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129908889</v>
+        <v>129910553</v>
       </c>
       <c r="B120" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13048,28 +13073,29 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -13079,10 +13105,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>516783</v>
+        <v>516968</v>
       </c>
       <c r="R120" t="n">
-        <v>6986629</v>
+        <v>6986277</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13119,7 +13145,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13128,34 +13154,8 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
@@ -13389,10 +13389,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129910753</v>
+        <v>129910640</v>
       </c>
       <c r="B123" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13400,21 +13400,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13424,10 +13424,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>516914</v>
+        <v>517288</v>
       </c>
       <c r="R123" t="n">
-        <v>6986518</v>
+        <v>6986118</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13462,11 +13462,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>På granar</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -13479,19 +13474,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129910640</v>
+        <v>129910621</v>
       </c>
       <c r="B124" t="n">
         <v>80193</v>
@@ -13526,10 +13521,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>517288</v>
+        <v>517170</v>
       </c>
       <c r="R124" t="n">
-        <v>6986118</v>
+        <v>6986215</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13588,7 +13583,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129910621</v>
+        <v>129910635</v>
       </c>
       <c r="B125" t="n">
         <v>80193</v>
@@ -13623,10 +13618,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>517170</v>
+        <v>517229</v>
       </c>
       <c r="R125" t="n">
-        <v>6986215</v>
+        <v>6986063</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13685,7 +13680,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129910635</v>
+        <v>129910605</v>
       </c>
       <c r="B126" t="n">
         <v>80193</v>
@@ -13720,10 +13715,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>517229</v>
+        <v>517273</v>
       </c>
       <c r="R126" t="n">
-        <v>6986063</v>
+        <v>6986075</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13782,32 +13777,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129910605</v>
+        <v>129910566</v>
       </c>
       <c r="B127" t="n">
-        <v>80193</v>
+        <v>79174</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13817,10 +13812,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>517273</v>
+        <v>517128</v>
       </c>
       <c r="R127" t="n">
-        <v>6986075</v>
+        <v>6986180</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13879,10 +13874,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129910637</v>
+        <v>129910753</v>
       </c>
       <c r="B128" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13890,21 +13885,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13914,10 +13909,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>517251</v>
+        <v>516914</v>
       </c>
       <c r="R128" t="n">
-        <v>6986087</v>
+        <v>6986518</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13952,6 +13947,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>På granar</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13964,44 +13964,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129910566</v>
+        <v>129910637</v>
       </c>
       <c r="B129" t="n">
-        <v>79174</v>
+        <v>80193</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14011,10 +14011,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>517128</v>
+        <v>517251</v>
       </c>
       <c r="R129" t="n">
-        <v>6986180</v>
+        <v>6986087</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16221,10 +16221,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129908900</v>
+        <v>129910607</v>
       </c>
       <c r="B150" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16232,37 +16232,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>516960</v>
+        <v>517246</v>
       </c>
       <c r="R150" t="n">
-        <v>6986352</v>
+        <v>6986091</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16297,45 +16294,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal gran.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -16352,10 +16318,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129908909</v>
+        <v>129910587</v>
       </c>
       <c r="B151" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16363,37 +16329,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>516915</v>
+        <v>517018</v>
       </c>
       <c r="R151" t="n">
-        <v>6986509</v>
+        <v>6986301</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16434,34 +16397,8 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16478,10 +16415,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129908903</v>
+        <v>129910609</v>
       </c>
       <c r="B152" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16489,37 +16426,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>516956</v>
+        <v>517221</v>
       </c>
       <c r="R152" t="n">
-        <v>6986419</v>
+        <v>6986213</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16554,45 +16488,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>På bark av tall.</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16609,7 +16512,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129910607</v>
+        <v>129910745</v>
       </c>
       <c r="B153" t="n">
         <v>80193</v>
@@ -16644,10 +16547,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>517246</v>
+        <v>516739</v>
       </c>
       <c r="R153" t="n">
-        <v>6986091</v>
+        <v>6986664</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16682,6 +16585,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>På stående död sälg</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -16694,22 +16602,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129910587</v>
+        <v>129908882</v>
       </c>
       <c r="B154" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16717,34 +16625,46 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>517018</v>
+        <v>516646</v>
       </c>
       <c r="R154" t="n">
-        <v>6986301</v>
+        <v>6986735</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16779,6 +16699,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -16787,6 +16712,31 @@
       </c>
       <c r="AG154" t="b">
         <v>0</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
@@ -16803,10 +16753,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129910609</v>
+        <v>129908900</v>
       </c>
       <c r="B155" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16814,34 +16764,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>517221</v>
+        <v>516960</v>
       </c>
       <c r="R155" t="n">
-        <v>6986213</v>
+        <v>6986352</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16876,14 +16829,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal gran.</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
@@ -16900,10 +16884,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129910745</v>
+        <v>129908909</v>
       </c>
       <c r="B156" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16911,34 +16895,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>516739</v>
+        <v>516915</v>
       </c>
       <c r="R156" t="n">
-        <v>6986664</v>
+        <v>6986509</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16973,79 +16960,87 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>På stående död sälg</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129910648</v>
+        <v>129908903</v>
       </c>
       <c r="B157" t="n">
-        <v>98798</v>
+        <v>79088</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -17053,10 +17048,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>517224</v>
+        <v>516956</v>
       </c>
       <c r="R157" t="n">
-        <v>6986227</v>
+        <v>6986419</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17093,7 +17088,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17105,6 +17100,31 @@
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
@@ -17121,57 +17141,61 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129908882</v>
+        <v>129910648</v>
       </c>
       <c r="B158" t="n">
-        <v>57740</v>
+        <v>98798</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>516646</v>
+        <v>517224</v>
       </c>
       <c r="R158" t="n">
-        <v>6986735</v>
+        <v>6986227</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17208,7 +17232,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
+          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17217,33 +17241,9 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
@@ -17260,10 +17260,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910558</v>
+        <v>129910548</v>
       </c>
       <c r="B159" t="n">
-        <v>57740</v>
+        <v>97044</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17271,42 +17271,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>517356</v>
+        <v>517167</v>
       </c>
       <c r="R159" t="n">
-        <v>6986190</v>
+        <v>6986105</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17339,11 +17331,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17370,10 +17357,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910548</v>
+        <v>129910550</v>
       </c>
       <c r="B160" t="n">
-        <v>97044</v>
+        <v>90638</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17381,21 +17368,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>53</v>
+        <v>1962</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17405,10 +17392,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>517167</v>
+        <v>517343</v>
       </c>
       <c r="R160" t="n">
-        <v>6986105</v>
+        <v>6986165</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17467,10 +17454,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910550</v>
+        <v>129908910</v>
       </c>
       <c r="B161" t="n">
-        <v>90638</v>
+        <v>79088</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17478,34 +17465,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>517343</v>
+        <v>516902</v>
       </c>
       <c r="R161" t="n">
-        <v>6986165</v>
+        <v>6986521</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17546,8 +17536,34 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
@@ -17564,7 +17580,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129908910</v>
+        <v>129908904</v>
       </c>
       <c r="B162" t="n">
         <v>79088</v>
@@ -17602,10 +17618,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>516902</v>
+        <v>516981</v>
       </c>
       <c r="R162" t="n">
-        <v>6986521</v>
+        <v>6986356</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17652,7 +17668,7 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -17690,7 +17706,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129908904</v>
+        <v>129908907</v>
       </c>
       <c r="B163" t="n">
         <v>79088</v>
@@ -17728,10 +17744,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>516981</v>
+        <v>517033</v>
       </c>
       <c r="R163" t="n">
-        <v>6986356</v>
+        <v>6986307</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17766,6 +17782,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>På en gammal gran i granskog.</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
@@ -17778,7 +17799,7 @@
       </c>
       <c r="AH163" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
@@ -17816,10 +17837,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129908907</v>
+        <v>129910744</v>
       </c>
       <c r="B164" t="n">
-        <v>79088</v>
+        <v>80193</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17827,37 +17848,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>517033</v>
+        <v>516858</v>
       </c>
       <c r="R164" t="n">
-        <v>6986307</v>
+        <v>6986573</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17894,7 +17912,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>På en gammal gran i granskog.</t>
+          <t>På både en lutande död sälg och en stående avbruten sälg.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17903,51 +17921,25 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129910744</v>
+        <v>129910611</v>
       </c>
       <c r="B165" t="n">
         <v>80193</v>
@@ -17982,10 +17974,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>516858</v>
+        <v>517216</v>
       </c>
       <c r="R165" t="n">
-        <v>6986573</v>
+        <v>6986197</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18020,11 +18012,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>På både en lutande död sälg och en stående avbruten sälg.</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
@@ -18037,19 +18024,19 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129910611</v>
+        <v>129910598</v>
       </c>
       <c r="B166" t="n">
         <v>80193</v>
@@ -18084,10 +18071,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>517216</v>
+        <v>517155</v>
       </c>
       <c r="R166" t="n">
-        <v>6986197</v>
+        <v>6986194</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18146,7 +18133,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129910598</v>
+        <v>129910628</v>
       </c>
       <c r="B167" t="n">
         <v>80193</v>
@@ -18181,10 +18168,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>517155</v>
+        <v>517207</v>
       </c>
       <c r="R167" t="n">
-        <v>6986194</v>
+        <v>6986088</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18243,32 +18230,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129910628</v>
+        <v>129910669</v>
       </c>
       <c r="B168" t="n">
-        <v>80193</v>
+        <v>79344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18278,10 +18265,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>517207</v>
+        <v>517113</v>
       </c>
       <c r="R168" t="n">
-        <v>6986088</v>
+        <v>6986244</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18340,32 +18327,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129910669</v>
+        <v>129910586</v>
       </c>
       <c r="B169" t="n">
-        <v>79344</v>
+        <v>80193</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18375,10 +18362,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>517113</v>
+        <v>517006</v>
       </c>
       <c r="R169" t="n">
-        <v>6986244</v>
+        <v>6986354</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18437,7 +18424,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129910586</v>
+        <v>129910616</v>
       </c>
       <c r="B170" t="n">
         <v>80193</v>
@@ -18472,10 +18459,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>517006</v>
+        <v>517030</v>
       </c>
       <c r="R170" t="n">
-        <v>6986354</v>
+        <v>6986400</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18534,7 +18521,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129910616</v>
+        <v>129910576</v>
       </c>
       <c r="B171" t="n">
         <v>80193</v>
@@ -18569,10 +18556,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>517030</v>
+        <v>516994</v>
       </c>
       <c r="R171" t="n">
-        <v>6986400</v>
+        <v>6986453</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18631,7 +18618,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129910576</v>
+        <v>129910623</v>
       </c>
       <c r="B172" t="n">
         <v>80193</v>
@@ -18666,10 +18653,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>516994</v>
+        <v>517174</v>
       </c>
       <c r="R172" t="n">
-        <v>6986453</v>
+        <v>6986187</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18728,10 +18715,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129910623</v>
+        <v>129910558</v>
       </c>
       <c r="B173" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18739,34 +18726,42 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>517174</v>
+        <v>517356</v>
       </c>
       <c r="R173" t="n">
-        <v>6986187</v>
+        <v>6986190</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18799,6 +18794,11 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD173" t="b">

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910557</v>
+        <v>129910574</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>79119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517175</v>
+        <v>517340</v>
       </c>
       <c r="R2" t="n">
-        <v>6986155</v>
+        <v>6986164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910556</v>
+        <v>129910577</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517169</v>
+        <v>517035</v>
       </c>
       <c r="R3" t="n">
-        <v>6986201</v>
+        <v>6986429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910642</v>
+        <v>129908891</v>
       </c>
       <c r="B4" t="n">
-        <v>78107</v>
+        <v>80200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,34 +880,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517251</v>
+        <v>516683</v>
       </c>
       <c r="R4" t="n">
-        <v>6986078</v>
+        <v>6986718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,14 +949,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På asp i granskog.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -992,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910666</v>
+        <v>129910667</v>
       </c>
       <c r="B5" t="n">
-        <v>81158</v>
+        <v>79351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229558</v>
+        <v>6459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517120</v>
+        <v>517221</v>
       </c>
       <c r="R5" t="n">
-        <v>6986257</v>
+        <v>6986209</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910654</v>
+        <v>129910557</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1112,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1135,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517262</v>
+        <v>517175</v>
       </c>
       <c r="R6" t="n">
-        <v>6986119</v>
+        <v>6986155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1184,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt!!</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,24 +1193,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1218,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910752</v>
+        <v>129910556</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,34 +1222,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516947</v>
+        <v>517169</v>
       </c>
       <c r="R7" t="n">
-        <v>6986297</v>
+        <v>6986201</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1294,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,44 +1309,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129910574</v>
+        <v>129910642</v>
       </c>
       <c r="B8" t="n">
-        <v>79119</v>
+        <v>78107</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517340</v>
+        <v>517251</v>
       </c>
       <c r="R8" t="n">
-        <v>6986164</v>
+        <v>6986078</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129910577</v>
+        <v>129910666</v>
       </c>
       <c r="B9" t="n">
-        <v>80200</v>
+        <v>81158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>229558</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517035</v>
+        <v>517120</v>
       </c>
       <c r="R9" t="n">
-        <v>6986429</v>
+        <v>6986257</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129908891</v>
+        <v>129910654</v>
       </c>
       <c r="B10" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,30 +1526,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516683</v>
+        <v>517262</v>
       </c>
       <c r="R10" t="n">
-        <v>6986718</v>
+        <v>6986119</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På asp i granskog.</t>
+          <t>Rikligt!!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,29 +1614,19 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1649,32 +1644,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129910667</v>
+        <v>129910752</v>
       </c>
       <c r="B11" t="n">
-        <v>79351</v>
+        <v>79095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517221</v>
+        <v>516947</v>
       </c>
       <c r="R11" t="n">
-        <v>6986209</v>
+        <v>6986297</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,6 +1717,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1734,12 +1734,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129910579</v>
+        <v>129908906</v>
       </c>
       <c r="B21" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2681,34 +2681,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517061</v>
+        <v>517038</v>
       </c>
       <c r="R21" t="n">
-        <v>6986424</v>
+        <v>6986336</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,8 +2752,34 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2767,10 +2796,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129910615</v>
+        <v>129910751</v>
       </c>
       <c r="B22" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2778,21 +2807,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2802,10 +2831,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517004</v>
+        <v>516971</v>
       </c>
       <c r="R22" t="n">
-        <v>6986426</v>
+        <v>6986263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2840,6 +2869,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligare med garnlav på ca 10 granar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2852,19 +2886,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129910742</v>
+        <v>129910579</v>
       </c>
       <c r="B23" t="n">
         <v>80200</v>
@@ -2899,10 +2933,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>516904</v>
+        <v>517061</v>
       </c>
       <c r="R23" t="n">
-        <v>6986470</v>
+        <v>6986424</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,11 +2971,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2954,19 +2983,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129910613</v>
+        <v>129910615</v>
       </c>
       <c r="B24" t="n">
         <v>80200</v>
@@ -3001,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517125</v>
+        <v>517004</v>
       </c>
       <c r="R24" t="n">
-        <v>6986172</v>
+        <v>6986426</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,10 +3092,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129908906</v>
+        <v>129910742</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,37 +3103,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517038</v>
+        <v>516904</v>
       </c>
       <c r="R25" t="n">
-        <v>6986336</v>
+        <v>6986470</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3139,60 +3165,39 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Lunglav på asp</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129910751</v>
+        <v>129910613</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3200,21 +3205,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3224,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516971</v>
+        <v>517125</v>
       </c>
       <c r="R26" t="n">
-        <v>6986263</v>
+        <v>6986172</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3262,11 +3267,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligare med garnlav på ca 10 granar.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3279,22 +3279,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129910580</v>
+        <v>129910649</v>
       </c>
       <c r="B27" t="n">
-        <v>80200</v>
+        <v>56922</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,34 +3302,50 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517047</v>
+        <v>517134</v>
       </c>
       <c r="R27" t="n">
-        <v>6986415</v>
+        <v>6986204</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3404,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129910610</v>
+        <v>129910580</v>
       </c>
       <c r="B28" t="n">
         <v>80200</v>
@@ -3423,10 +3439,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517211</v>
+        <v>517047</v>
       </c>
       <c r="R28" t="n">
-        <v>6986211</v>
+        <v>6986415</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,7 +3501,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129910599</v>
+        <v>129910610</v>
       </c>
       <c r="B29" t="n">
         <v>80200</v>
@@ -3520,10 +3536,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517177</v>
+        <v>517211</v>
       </c>
       <c r="R29" t="n">
-        <v>6986167</v>
+        <v>6986211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,7 +3598,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129910620</v>
+        <v>129910599</v>
       </c>
       <c r="B30" t="n">
         <v>80200</v>
@@ -3617,10 +3633,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>517112</v>
+        <v>517177</v>
       </c>
       <c r="R30" t="n">
-        <v>6986273</v>
+        <v>6986167</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3679,32 +3695,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129910668</v>
+        <v>129910620</v>
       </c>
       <c r="B31" t="n">
-        <v>79351</v>
+        <v>80200</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3730,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>517042</v>
+        <v>517112</v>
       </c>
       <c r="R31" t="n">
-        <v>6986262</v>
+        <v>6986273</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,32 +3792,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129910631</v>
+        <v>129910668</v>
       </c>
       <c r="B32" t="n">
-        <v>80200</v>
+        <v>79351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3811,10 +3827,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517287</v>
+        <v>517042</v>
       </c>
       <c r="R32" t="n">
-        <v>6986080</v>
+        <v>6986262</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3873,7 +3889,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129910601</v>
+        <v>129910631</v>
       </c>
       <c r="B33" t="n">
         <v>80200</v>
@@ -3908,10 +3924,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517170</v>
+        <v>517287</v>
       </c>
       <c r="R33" t="n">
-        <v>6986161</v>
+        <v>6986080</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3970,7 +3986,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129910592</v>
+        <v>129910601</v>
       </c>
       <c r="B34" t="n">
         <v>80200</v>
@@ -4005,10 +4021,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517119</v>
+        <v>517170</v>
       </c>
       <c r="R34" t="n">
-        <v>6986251</v>
+        <v>6986161</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129910564</v>
+        <v>129910592</v>
       </c>
       <c r="B35" t="n">
-        <v>80066</v>
+        <v>80200</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,21 +4094,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4118,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517170</v>
+        <v>517119</v>
       </c>
       <c r="R35" t="n">
-        <v>6986124</v>
+        <v>6986251</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4146,7 +4162,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4165,10 +4180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129908880</v>
+        <v>129910564</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>80066</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,46 +4191,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>388</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>516686</v>
+        <v>517170</v>
       </c>
       <c r="R36" t="n">
-        <v>6986687</v>
+        <v>6986124</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,44 +4253,15 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4304,10 +4278,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129910649</v>
+        <v>129908880</v>
       </c>
       <c r="B37" t="n">
-        <v>56922</v>
+        <v>57741</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4315,16 +4289,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4332,16 +4306,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4355,10 +4325,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>517134</v>
+        <v>516686</v>
       </c>
       <c r="R37" t="n">
-        <v>6986204</v>
+        <v>6986687</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4393,6 +4363,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4401,6 +4376,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -9052,51 +9052,35 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129908912</v>
+        <v>129910749</v>
       </c>
       <c r="B82" t="n">
-        <v>98748</v>
+        <v>79095</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
@@ -9106,7 +9090,7 @@
         <v>516929</v>
       </c>
       <c r="R82" t="n">
-        <v>6986305</v>
+        <v>6986288</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9141,96 +9125,69 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>1 vinterståndare.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129908894</v>
+        <v>129910740</v>
       </c>
       <c r="B83" t="n">
-        <v>98831</v>
+        <v>80200</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>517028</v>
+        <v>517033</v>
       </c>
       <c r="R83" t="n">
-        <v>6986324</v>
+        <v>6986309</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9267,7 +9224,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+          <t>På torraka och låga av sälg</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9276,34 +9233,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129910749</v>
+        <v>129910543</v>
       </c>
       <c r="B84" t="n">
-        <v>79095</v>
+        <v>83073</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9311,21 +9262,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9335,10 +9286,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>516929</v>
+        <v>517077</v>
       </c>
       <c r="R84" t="n">
-        <v>6986288</v>
+        <v>6986242</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9385,22 +9336,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129910740</v>
+        <v>129910546</v>
       </c>
       <c r="B85" t="n">
-        <v>80200</v>
+        <v>83073</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9408,21 +9359,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9432,10 +9383,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>517033</v>
+        <v>517241</v>
       </c>
       <c r="R85" t="n">
-        <v>6986309</v>
+        <v>6986104</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9470,11 +9421,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På torraka och låga av sälg</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9487,22 +9433,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129910543</v>
+        <v>129910602</v>
       </c>
       <c r="B86" t="n">
-        <v>83073</v>
+        <v>80200</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9510,21 +9456,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9534,10 +9480,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>517077</v>
+        <v>517146</v>
       </c>
       <c r="R86" t="n">
-        <v>6986242</v>
+        <v>6986161</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9596,10 +9542,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129910546</v>
+        <v>129910619</v>
       </c>
       <c r="B87" t="n">
-        <v>83073</v>
+        <v>80200</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9607,21 +9553,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9631,10 +9577,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>517241</v>
+        <v>517108</v>
       </c>
       <c r="R87" t="n">
-        <v>6986104</v>
+        <v>6986255</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9693,10 +9639,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129910602</v>
+        <v>129910647</v>
       </c>
       <c r="B88" t="n">
-        <v>80200</v>
+        <v>78852</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9704,21 +9650,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9728,10 +9674,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>517146</v>
+        <v>517081</v>
       </c>
       <c r="R88" t="n">
-        <v>6986161</v>
+        <v>6986186</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9790,32 +9736,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129910619</v>
+        <v>129910571</v>
       </c>
       <c r="B89" t="n">
-        <v>80200</v>
+        <v>80104</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9825,10 +9771,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>517108</v>
+        <v>517109</v>
       </c>
       <c r="R89" t="n">
-        <v>6986255</v>
+        <v>6986168</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9887,10 +9833,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129910647</v>
+        <v>129910636</v>
       </c>
       <c r="B90" t="n">
-        <v>78852</v>
+        <v>80200</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9898,21 +9844,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9922,10 +9868,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>517081</v>
+        <v>517228</v>
       </c>
       <c r="R90" t="n">
-        <v>6986186</v>
+        <v>6986059</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9984,32 +9930,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129910571</v>
+        <v>129910545</v>
       </c>
       <c r="B91" t="n">
-        <v>80104</v>
+        <v>83073</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10019,10 +9965,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>517109</v>
+        <v>517251</v>
       </c>
       <c r="R91" t="n">
-        <v>6986168</v>
+        <v>6986081</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10081,45 +10027,61 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129910636</v>
+        <v>129908912</v>
       </c>
       <c r="B92" t="n">
-        <v>80200</v>
+        <v>98748</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>517228</v>
+        <v>516929</v>
       </c>
       <c r="R92" t="n">
-        <v>6986059</v>
+        <v>6986305</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10154,14 +10116,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>1 vinterståndare.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10178,45 +10151,61 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129910545</v>
+        <v>129908894</v>
       </c>
       <c r="B93" t="n">
-        <v>83073</v>
+        <v>98831</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>517251</v>
+        <v>517028</v>
       </c>
       <c r="R93" t="n">
-        <v>6986081</v>
+        <v>6986324</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10251,14 +10240,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -10765,53 +10765,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129910554</v>
+        <v>129910748</v>
       </c>
       <c r="B99" t="n">
-        <v>57741</v>
+        <v>98831</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>516949</v>
+        <v>516692</v>
       </c>
       <c r="R99" t="n">
-        <v>6986325</v>
+        <v>6986711</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10848,7 +10840,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10863,57 +10855,65 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129910748</v>
+        <v>129910554</v>
       </c>
       <c r="B100" t="n">
-        <v>98831</v>
+        <v>57741</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>516692</v>
+        <v>516949</v>
       </c>
       <c r="R100" t="n">
-        <v>6986711</v>
+        <v>6986325</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10965,12 +10965,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -13389,45 +13389,61 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129910753</v>
+        <v>129908895</v>
       </c>
       <c r="B123" t="n">
-        <v>79095</v>
+        <v>98831</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>516914</v>
+        <v>516927</v>
       </c>
       <c r="R123" t="n">
-        <v>6986518</v>
+        <v>6986523</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13464,7 +13480,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>På granar</t>
+          <t>Minst 16 plantor och 3 vinterståndare inom ca 3 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13473,28 +13489,34 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129910640</v>
+        <v>129910753</v>
       </c>
       <c r="B124" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13502,21 +13524,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13526,10 +13548,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>517288</v>
+        <v>516914</v>
       </c>
       <c r="R124" t="n">
-        <v>6986118</v>
+        <v>6986518</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13564,6 +13586,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På granar</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -13576,19 +13603,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129910621</v>
+        <v>129910640</v>
       </c>
       <c r="B125" t="n">
         <v>80200</v>
@@ -13623,10 +13650,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>517170</v>
+        <v>517288</v>
       </c>
       <c r="R125" t="n">
-        <v>6986215</v>
+        <v>6986118</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13685,7 +13712,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129910635</v>
+        <v>129910621</v>
       </c>
       <c r="B126" t="n">
         <v>80200</v>
@@ -13720,10 +13747,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>517229</v>
+        <v>517170</v>
       </c>
       <c r="R126" t="n">
-        <v>6986063</v>
+        <v>6986215</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13782,7 +13809,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129910605</v>
+        <v>129910635</v>
       </c>
       <c r="B127" t="n">
         <v>80200</v>
@@ -13817,10 +13844,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>517273</v>
+        <v>517229</v>
       </c>
       <c r="R127" t="n">
-        <v>6986075</v>
+        <v>6986063</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13879,32 +13906,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129910566</v>
+        <v>129910605</v>
       </c>
       <c r="B128" t="n">
-        <v>79181</v>
+        <v>80200</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13914,10 +13941,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>517128</v>
+        <v>517273</v>
       </c>
       <c r="R128" t="n">
-        <v>6986180</v>
+        <v>6986075</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13976,32 +14003,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129910637</v>
+        <v>129910566</v>
       </c>
       <c r="B129" t="n">
-        <v>80200</v>
+        <v>79181</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14011,10 +14038,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>517251</v>
+        <v>517128</v>
       </c>
       <c r="R129" t="n">
-        <v>6986087</v>
+        <v>6986180</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14073,61 +14100,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129908895</v>
+        <v>129910637</v>
       </c>
       <c r="B130" t="n">
-        <v>98831</v>
+        <v>80200</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>516927</v>
+        <v>517251</v>
       </c>
       <c r="R130" t="n">
-        <v>6986523</v>
+        <v>6986087</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14162,25 +14173,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor och 3 vinterståndare inom ca 3 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -15468,45 +15468,48 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129910570</v>
+        <v>129910651</v>
       </c>
       <c r="B143" t="n">
-        <v>80104</v>
+        <v>79095</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>517172</v>
+        <v>517137</v>
       </c>
       <c r="R143" t="n">
-        <v>6986122</v>
+        <v>6986150</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15547,8 +15550,24 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
@@ -15565,52 +15584,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129910639</v>
+        <v>129910570</v>
       </c>
       <c r="B144" t="n">
-        <v>80200</v>
+        <v>80104</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>517276</v>
+        <v>517172</v>
       </c>
       <c r="R144" t="n">
-        <v>6986120</v>
+        <v>6986122</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15645,18 +15657,12 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apotechier.</t>
-        </is>
-      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15675,7 +15681,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129910608</v>
+        <v>129910639</v>
       </c>
       <c r="B145" t="n">
         <v>80200</v>
@@ -15704,16 +15710,23 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>517230</v>
+        <v>517276</v>
       </c>
       <c r="R145" t="n">
-        <v>6986231</v>
+        <v>6986120</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15748,12 +15761,18 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apotechier.</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15772,7 +15791,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129910582</v>
+        <v>129910608</v>
       </c>
       <c r="B146" t="n">
         <v>80200</v>
@@ -15807,10 +15826,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>517009</v>
+        <v>517230</v>
       </c>
       <c r="R146" t="n">
-        <v>6986366</v>
+        <v>6986231</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15869,10 +15888,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129910651</v>
+        <v>129910582</v>
       </c>
       <c r="B147" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15880,37 +15899,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>517137</v>
+        <v>517009</v>
       </c>
       <c r="R147" t="n">
-        <v>6986150</v>
+        <v>6986366</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15951,24 +15967,8 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -2670,10 +2670,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129908906</v>
+        <v>129910579</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2681,37 +2681,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517038</v>
+        <v>517061</v>
       </c>
       <c r="R21" t="n">
-        <v>6986336</v>
+        <v>6986424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2752,34 +2749,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2796,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129910751</v>
+        <v>129910615</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2807,21 +2778,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2831,10 +2802,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516971</v>
+        <v>517004</v>
       </c>
       <c r="R22" t="n">
-        <v>6986263</v>
+        <v>6986426</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,11 +2840,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligare med garnlav på ca 10 granar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2886,19 +2852,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129910579</v>
+        <v>129910742</v>
       </c>
       <c r="B23" t="n">
         <v>80200</v>
@@ -2933,10 +2899,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517061</v>
+        <v>516904</v>
       </c>
       <c r="R23" t="n">
-        <v>6986424</v>
+        <v>6986470</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,6 +2937,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på asp</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2983,19 +2954,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129910615</v>
+        <v>129910613</v>
       </c>
       <c r="B24" t="n">
         <v>80200</v>
@@ -3030,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517004</v>
+        <v>517125</v>
       </c>
       <c r="R24" t="n">
-        <v>6986426</v>
+        <v>6986172</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,10 +3063,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129910742</v>
+        <v>129908906</v>
       </c>
       <c r="B25" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3103,34 +3074,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516904</v>
+        <v>517038</v>
       </c>
       <c r="R25" t="n">
-        <v>6986470</v>
+        <v>6986336</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3165,39 +3139,60 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129910613</v>
+        <v>129910751</v>
       </c>
       <c r="B26" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3205,21 +3200,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3229,10 +3224,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>517125</v>
+        <v>516971</v>
       </c>
       <c r="R26" t="n">
-        <v>6986172</v>
+        <v>6986263</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3267,6 +3262,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligare med garnlav på ca 10 granar.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3279,22 +3279,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129910649</v>
+        <v>129910580</v>
       </c>
       <c r="B27" t="n">
-        <v>56922</v>
+        <v>80200</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,50 +3302,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517134</v>
+        <v>517047</v>
       </c>
       <c r="R27" t="n">
-        <v>6986204</v>
+        <v>6986415</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3404,7 +3388,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129910580</v>
+        <v>129910610</v>
       </c>
       <c r="B28" t="n">
         <v>80200</v>
@@ -3439,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517047</v>
+        <v>517211</v>
       </c>
       <c r="R28" t="n">
-        <v>6986415</v>
+        <v>6986211</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,7 +3485,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129910610</v>
+        <v>129910599</v>
       </c>
       <c r="B29" t="n">
         <v>80200</v>
@@ -3536,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517211</v>
+        <v>517177</v>
       </c>
       <c r="R29" t="n">
-        <v>6986211</v>
+        <v>6986167</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,7 +3582,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129910599</v>
+        <v>129910620</v>
       </c>
       <c r="B30" t="n">
         <v>80200</v>
@@ -3633,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>517177</v>
+        <v>517112</v>
       </c>
       <c r="R30" t="n">
-        <v>6986167</v>
+        <v>6986273</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3695,32 +3679,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129910620</v>
+        <v>129910668</v>
       </c>
       <c r="B31" t="n">
-        <v>80200</v>
+        <v>79351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3730,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>517112</v>
+        <v>517042</v>
       </c>
       <c r="R31" t="n">
-        <v>6986273</v>
+        <v>6986262</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3792,32 +3776,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129910668</v>
+        <v>129910631</v>
       </c>
       <c r="B32" t="n">
-        <v>79351</v>
+        <v>80200</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3827,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517042</v>
+        <v>517287</v>
       </c>
       <c r="R32" t="n">
-        <v>6986262</v>
+        <v>6986080</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3889,7 +3873,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129910631</v>
+        <v>129910601</v>
       </c>
       <c r="B33" t="n">
         <v>80200</v>
@@ -3924,10 +3908,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517287</v>
+        <v>517170</v>
       </c>
       <c r="R33" t="n">
-        <v>6986080</v>
+        <v>6986161</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3986,7 +3970,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129910601</v>
+        <v>129910592</v>
       </c>
       <c r="B34" t="n">
         <v>80200</v>
@@ -4021,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517170</v>
+        <v>517119</v>
       </c>
       <c r="R34" t="n">
-        <v>6986161</v>
+        <v>6986251</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4083,10 +4067,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129910592</v>
+        <v>129910564</v>
       </c>
       <c r="B35" t="n">
-        <v>80200</v>
+        <v>80066</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4094,21 +4078,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4118,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517119</v>
+        <v>517170</v>
       </c>
       <c r="R35" t="n">
-        <v>6986251</v>
+        <v>6986124</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4162,6 +4146,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4180,10 +4165,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129910564</v>
+        <v>129908880</v>
       </c>
       <c r="B36" t="n">
-        <v>80066</v>
+        <v>57741</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4191,34 +4176,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>388</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517170</v>
+        <v>516686</v>
       </c>
       <c r="R36" t="n">
-        <v>6986124</v>
+        <v>6986687</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4253,15 +4250,44 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4278,10 +4304,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129908880</v>
+        <v>129910649</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>56922</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4289,16 +4315,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4306,12 +4332,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4325,10 +4355,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>516686</v>
+        <v>517134</v>
       </c>
       <c r="R37" t="n">
-        <v>6986687</v>
+        <v>6986204</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4363,11 +4393,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4376,31 +4401,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4611,61 +4611,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129908896</v>
+        <v>129910581</v>
       </c>
       <c r="B40" t="n">
-        <v>98831</v>
+        <v>80200</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>516925</v>
+        <v>517011</v>
       </c>
       <c r="R40" t="n">
-        <v>6986509</v>
+        <v>6986383</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4700,25 +4684,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4735,32 +4708,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129910646</v>
+        <v>129910589</v>
       </c>
       <c r="B41" t="n">
-        <v>80160</v>
+        <v>80200</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4770,10 +4743,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>517237</v>
+        <v>517055</v>
       </c>
       <c r="R41" t="n">
-        <v>6986059</v>
+        <v>6986272</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4832,7 +4805,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129910581</v>
+        <v>129910578</v>
       </c>
       <c r="B42" t="n">
         <v>80200</v>
@@ -4867,10 +4840,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>517011</v>
+        <v>517037</v>
       </c>
       <c r="R42" t="n">
-        <v>6986383</v>
+        <v>6986432</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4929,7 +4902,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129910589</v>
+        <v>129910629</v>
       </c>
       <c r="B43" t="n">
         <v>80200</v>
@@ -4964,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>517055</v>
+        <v>517270</v>
       </c>
       <c r="R43" t="n">
-        <v>6986272</v>
+        <v>6986036</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5026,45 +4999,61 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129910578</v>
+        <v>129908896</v>
       </c>
       <c r="B44" t="n">
-        <v>80200</v>
+        <v>98831</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>517037</v>
+        <v>516925</v>
       </c>
       <c r="R44" t="n">
-        <v>6986432</v>
+        <v>6986509</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5099,14 +5088,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5123,32 +5123,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129910629</v>
+        <v>129910646</v>
       </c>
       <c r="B45" t="n">
-        <v>80200</v>
+        <v>80160</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>517270</v>
+        <v>517237</v>
       </c>
       <c r="R45" t="n">
-        <v>6986036</v>
+        <v>6986059</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129910568</v>
+        <v>129910547</v>
       </c>
       <c r="B46" t="n">
-        <v>80201</v>
+        <v>97077</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5231,21 +5231,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>517230</v>
+        <v>517122</v>
       </c>
       <c r="R46" t="n">
-        <v>6986059</v>
+        <v>6986191</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5317,45 +5317,52 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129910750</v>
+        <v>129910660</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>92234</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>517017</v>
+        <v>517050</v>
       </c>
       <c r="R47" t="n">
-        <v>6986332</v>
+        <v>6986414</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5390,39 +5397,50 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129910547</v>
+        <v>129910568</v>
       </c>
       <c r="B48" t="n">
-        <v>97077</v>
+        <v>80201</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5430,21 +5448,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5454,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>517122</v>
+        <v>517230</v>
       </c>
       <c r="R48" t="n">
-        <v>6986191</v>
+        <v>6986059</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5516,52 +5534,61 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129910660</v>
+        <v>129910559</v>
       </c>
       <c r="B49" t="n">
-        <v>92234</v>
+        <v>57900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>760</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>517050</v>
+        <v>517266</v>
       </c>
       <c r="R49" t="n">
-        <v>6986414</v>
+        <v>6986055</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5602,24 +5629,8 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5636,10 +5647,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129910632</v>
+        <v>129910750</v>
       </c>
       <c r="B50" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5647,21 +5658,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5671,10 +5682,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>517285</v>
+        <v>517017</v>
       </c>
       <c r="R50" t="n">
-        <v>6986090</v>
+        <v>6986332</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5709,6 +5720,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5721,19 +5737,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129910591</v>
+        <v>129910632</v>
       </c>
       <c r="B51" t="n">
         <v>80200</v>
@@ -5768,10 +5784,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>517068</v>
+        <v>517285</v>
       </c>
       <c r="R51" t="n">
-        <v>6986257</v>
+        <v>6986090</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,10 +5846,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129910559</v>
+        <v>129910591</v>
       </c>
       <c r="B52" t="n">
-        <v>57900</v>
+        <v>80200</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5841,50 +5857,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>517266</v>
+        <v>517068</v>
       </c>
       <c r="R52" t="n">
-        <v>6986055</v>
+        <v>6986257</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129910604</v>
+        <v>129908901</v>
       </c>
       <c r="B61" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6801,34 +6801,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>517211</v>
+        <v>516936</v>
       </c>
       <c r="R61" t="n">
-        <v>6986077</v>
+        <v>6986463</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6869,8 +6872,34 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6887,7 +6916,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129908888</v>
+        <v>129910604</v>
       </c>
       <c r="B62" t="n">
         <v>80200</v>
@@ -6916,19 +6945,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>516854</v>
+        <v>517211</v>
       </c>
       <c r="R62" t="n">
-        <v>6986558</v>
+        <v>6986077</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6963,45 +6989,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7018,7 +7013,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129910746</v>
+        <v>129908888</v>
       </c>
       <c r="B63" t="n">
         <v>80200</v>
@@ -7047,16 +7042,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>516690</v>
+        <v>516854</v>
       </c>
       <c r="R63" t="n">
-        <v>6986709</v>
+        <v>6986558</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7093,7 +7091,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7102,25 +7100,51 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129910595</v>
+        <v>129910746</v>
       </c>
       <c r="B64" t="n">
         <v>80200</v>
@@ -7155,10 +7179,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>517169</v>
+        <v>516690</v>
       </c>
       <c r="R64" t="n">
-        <v>6986203</v>
+        <v>6986709</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7193,6 +7217,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7205,19 +7234,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129910617</v>
+        <v>129910595</v>
       </c>
       <c r="B65" t="n">
         <v>80200</v>
@@ -7252,10 +7281,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>517040</v>
+        <v>517169</v>
       </c>
       <c r="R65" t="n">
-        <v>6986263</v>
+        <v>6986203</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7314,7 +7343,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129910575</v>
+        <v>129910617</v>
       </c>
       <c r="B66" t="n">
         <v>80200</v>
@@ -7349,10 +7378,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>516969</v>
+        <v>517040</v>
       </c>
       <c r="R66" t="n">
-        <v>6986323</v>
+        <v>6986263</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7411,10 +7440,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129910641</v>
+        <v>129910575</v>
       </c>
       <c r="B67" t="n">
-        <v>78107</v>
+        <v>80200</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7422,21 +7451,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7475,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>517183</v>
+        <v>516969</v>
       </c>
       <c r="R67" t="n">
-        <v>6986150</v>
+        <v>6986323</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7508,10 +7537,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129908901</v>
+        <v>129910641</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>78107</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7519,37 +7548,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>516936</v>
+        <v>517183</v>
       </c>
       <c r="R68" t="n">
-        <v>6986463</v>
+        <v>6986150</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7590,34 +7616,8 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9052,35 +9052,51 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129910749</v>
+        <v>129908912</v>
       </c>
       <c r="B82" t="n">
-        <v>79095</v>
+        <v>98748</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
@@ -9090,7 +9106,7 @@
         <v>516929</v>
       </c>
       <c r="R82" t="n">
-        <v>6986288</v>
+        <v>6986305</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9125,69 +9141,96 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>1 vinterståndare.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129910740</v>
+        <v>129908894</v>
       </c>
       <c r="B83" t="n">
-        <v>80200</v>
+        <v>98831</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>517033</v>
+        <v>517028</v>
       </c>
       <c r="R83" t="n">
-        <v>6986309</v>
+        <v>6986324</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9224,7 +9267,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På torraka och låga av sälg</t>
+          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9233,28 +9276,34 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129910543</v>
+        <v>129910749</v>
       </c>
       <c r="B84" t="n">
-        <v>83073</v>
+        <v>79095</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9262,21 +9311,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9286,10 +9335,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>517077</v>
+        <v>516929</v>
       </c>
       <c r="R84" t="n">
-        <v>6986242</v>
+        <v>6986288</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9336,22 +9385,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129910546</v>
+        <v>129910740</v>
       </c>
       <c r="B85" t="n">
-        <v>83073</v>
+        <v>80200</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9359,21 +9408,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9383,10 +9432,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>517241</v>
+        <v>517033</v>
       </c>
       <c r="R85" t="n">
-        <v>6986104</v>
+        <v>6986309</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9421,6 +9470,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På torraka och låga av sälg</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9433,22 +9487,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129910602</v>
+        <v>129910543</v>
       </c>
       <c r="B86" t="n">
-        <v>80200</v>
+        <v>83073</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9456,21 +9510,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9480,10 +9534,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>517146</v>
+        <v>517077</v>
       </c>
       <c r="R86" t="n">
-        <v>6986161</v>
+        <v>6986242</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9542,10 +9596,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129910619</v>
+        <v>129910546</v>
       </c>
       <c r="B87" t="n">
-        <v>80200</v>
+        <v>83073</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9553,21 +9607,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9577,10 +9631,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>517108</v>
+        <v>517241</v>
       </c>
       <c r="R87" t="n">
-        <v>6986255</v>
+        <v>6986104</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9639,10 +9693,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129910647</v>
+        <v>129910602</v>
       </c>
       <c r="B88" t="n">
-        <v>78852</v>
+        <v>80200</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9650,21 +9704,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9674,10 +9728,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>517081</v>
+        <v>517146</v>
       </c>
       <c r="R88" t="n">
-        <v>6986186</v>
+        <v>6986161</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9736,32 +9790,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129910571</v>
+        <v>129910619</v>
       </c>
       <c r="B89" t="n">
-        <v>80104</v>
+        <v>80200</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9771,10 +9825,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>517109</v>
+        <v>517108</v>
       </c>
       <c r="R89" t="n">
-        <v>6986168</v>
+        <v>6986255</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9833,10 +9887,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129910636</v>
+        <v>129910647</v>
       </c>
       <c r="B90" t="n">
-        <v>80200</v>
+        <v>78852</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9844,21 +9898,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9868,10 +9922,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>517228</v>
+        <v>517081</v>
       </c>
       <c r="R90" t="n">
-        <v>6986059</v>
+        <v>6986186</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9930,32 +9984,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129910545</v>
+        <v>129910571</v>
       </c>
       <c r="B91" t="n">
-        <v>83073</v>
+        <v>80104</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9965,10 +10019,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>517251</v>
+        <v>517109</v>
       </c>
       <c r="R91" t="n">
-        <v>6986081</v>
+        <v>6986168</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10027,61 +10081,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129908912</v>
+        <v>129910636</v>
       </c>
       <c r="B92" t="n">
-        <v>98748</v>
+        <v>80200</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>516929</v>
+        <v>517228</v>
       </c>
       <c r="R92" t="n">
-        <v>6986305</v>
+        <v>6986059</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10116,25 +10154,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>1 vinterståndare.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10151,61 +10178,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129908894</v>
+        <v>129910545</v>
       </c>
       <c r="B93" t="n">
-        <v>98831</v>
+        <v>83073</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>517028</v>
+        <v>517251</v>
       </c>
       <c r="R93" t="n">
-        <v>6986324</v>
+        <v>6986081</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10240,25 +10251,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -13389,61 +13389,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129908895</v>
+        <v>129910753</v>
       </c>
       <c r="B123" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>516927</v>
+        <v>516914</v>
       </c>
       <c r="R123" t="n">
-        <v>6986523</v>
+        <v>6986518</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13480,7 +13464,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 3 vinterståndare inom ca 3 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+          <t>På granar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13489,34 +13473,28 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129910753</v>
+        <v>129910640</v>
       </c>
       <c r="B124" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13524,21 +13502,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13548,10 +13526,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>516914</v>
+        <v>517288</v>
       </c>
       <c r="R124" t="n">
-        <v>6986518</v>
+        <v>6986118</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13586,11 +13564,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>På granar</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -13603,19 +13576,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129910640</v>
+        <v>129910621</v>
       </c>
       <c r="B125" t="n">
         <v>80200</v>
@@ -13650,10 +13623,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>517288</v>
+        <v>517170</v>
       </c>
       <c r="R125" t="n">
-        <v>6986118</v>
+        <v>6986215</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13712,7 +13685,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129910621</v>
+        <v>129910635</v>
       </c>
       <c r="B126" t="n">
         <v>80200</v>
@@ -13747,10 +13720,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>517170</v>
+        <v>517229</v>
       </c>
       <c r="R126" t="n">
-        <v>6986215</v>
+        <v>6986063</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13809,7 +13782,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129910635</v>
+        <v>129910605</v>
       </c>
       <c r="B127" t="n">
         <v>80200</v>
@@ -13844,10 +13817,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>517229</v>
+        <v>517273</v>
       </c>
       <c r="R127" t="n">
-        <v>6986063</v>
+        <v>6986075</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13906,32 +13879,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129910605</v>
+        <v>129910566</v>
       </c>
       <c r="B128" t="n">
-        <v>80200</v>
+        <v>79181</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13941,10 +13914,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>517273</v>
+        <v>517128</v>
       </c>
       <c r="R128" t="n">
-        <v>6986075</v>
+        <v>6986180</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14003,32 +13976,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129910566</v>
+        <v>129910637</v>
       </c>
       <c r="B129" t="n">
-        <v>79181</v>
+        <v>80200</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14038,10 +14011,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>517128</v>
+        <v>517251</v>
       </c>
       <c r="R129" t="n">
-        <v>6986180</v>
+        <v>6986087</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14100,45 +14073,61 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129910637</v>
+        <v>129908895</v>
       </c>
       <c r="B130" t="n">
-        <v>80200</v>
+        <v>98831</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>517251</v>
+        <v>516927</v>
       </c>
       <c r="R130" t="n">
-        <v>6986087</v>
+        <v>6986523</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14173,14 +14162,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor och 3 vinterståndare inom ca 3 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -14197,10 +14197,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129910551</v>
+        <v>129910584</v>
       </c>
       <c r="B131" t="n">
-        <v>91639</v>
+        <v>80200</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14208,41 +14208,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>517014</v>
+        <v>517004</v>
       </c>
       <c r="R131" t="n">
-        <v>6986339</v>
+        <v>6986361</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14283,29 +14276,8 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
@@ -14322,52 +14294,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129910659</v>
+        <v>129910594</v>
       </c>
       <c r="B132" t="n">
-        <v>92921</v>
+        <v>80200</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>517328</v>
+        <v>517165</v>
       </c>
       <c r="R132" t="n">
-        <v>6986156</v>
+        <v>6986222</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14408,7 +14373,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14427,7 +14391,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129910584</v>
+        <v>129910624</v>
       </c>
       <c r="B133" t="n">
         <v>80200</v>
@@ -14462,10 +14426,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>517004</v>
+        <v>517195</v>
       </c>
       <c r="R133" t="n">
-        <v>6986361</v>
+        <v>6986175</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14524,7 +14488,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129910594</v>
+        <v>129910747</v>
       </c>
       <c r="B134" t="n">
         <v>80200</v>
@@ -14559,10 +14523,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>517165</v>
+        <v>516674</v>
       </c>
       <c r="R134" t="n">
-        <v>6986222</v>
+        <v>6986695</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14597,6 +14561,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på liggande men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14609,19 +14578,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129910624</v>
+        <v>129910634</v>
       </c>
       <c r="B135" t="n">
         <v>80200</v>
@@ -14656,10 +14625,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>517195</v>
+        <v>517233</v>
       </c>
       <c r="R135" t="n">
-        <v>6986175</v>
+        <v>6986069</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14718,32 +14687,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129910747</v>
+        <v>129910572</v>
       </c>
       <c r="B136" t="n">
-        <v>80200</v>
+        <v>80104</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14753,10 +14722,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>516674</v>
+        <v>517147</v>
       </c>
       <c r="R136" t="n">
-        <v>6986695</v>
+        <v>6986129</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14791,11 +14760,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på liggande men levande sälg.</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14808,57 +14772,73 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129910634</v>
+        <v>129910560</v>
       </c>
       <c r="B137" t="n">
-        <v>80200</v>
+        <v>58377</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>102125</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>517233</v>
+        <v>517237</v>
       </c>
       <c r="R137" t="n">
-        <v>6986069</v>
+        <v>6986082</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14917,45 +14897,52 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129910572</v>
+        <v>129910551</v>
       </c>
       <c r="B138" t="n">
-        <v>80104</v>
+        <v>91639</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>517147</v>
+        <v>517014</v>
       </c>
       <c r="R138" t="n">
-        <v>6986129</v>
+        <v>6986339</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14996,8 +14983,29 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -15014,61 +15022,52 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129910560</v>
+        <v>129910659</v>
       </c>
       <c r="B139" t="n">
-        <v>58377</v>
+        <v>92921</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>102125</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>517237</v>
+        <v>517328</v>
       </c>
       <c r="R139" t="n">
-        <v>6986082</v>
+        <v>6986156</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15109,6 +15108,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15468,48 +15468,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129910651</v>
+        <v>129910570</v>
       </c>
       <c r="B143" t="n">
-        <v>79095</v>
+        <v>80104</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>517137</v>
+        <v>517172</v>
       </c>
       <c r="R143" t="n">
-        <v>6986150</v>
+        <v>6986122</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15550,24 +15547,8 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
@@ -15584,45 +15565,52 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129910570</v>
+        <v>129910639</v>
       </c>
       <c r="B144" t="n">
-        <v>80104</v>
+        <v>80200</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>517172</v>
+        <v>517276</v>
       </c>
       <c r="R144" t="n">
-        <v>6986122</v>
+        <v>6986120</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15657,12 +15645,18 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apotechier.</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15681,7 +15675,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129910639</v>
+        <v>129910608</v>
       </c>
       <c r="B145" t="n">
         <v>80200</v>
@@ -15710,23 +15704,16 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>517276</v>
+        <v>517230</v>
       </c>
       <c r="R145" t="n">
-        <v>6986120</v>
+        <v>6986231</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15761,18 +15748,12 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apotechier.</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15791,7 +15772,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129910608</v>
+        <v>129910582</v>
       </c>
       <c r="B146" t="n">
         <v>80200</v>
@@ -15826,10 +15807,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>517230</v>
+        <v>517009</v>
       </c>
       <c r="R146" t="n">
-        <v>6986231</v>
+        <v>6986366</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15888,10 +15869,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129910582</v>
+        <v>129910651</v>
       </c>
       <c r="B147" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15899,34 +15880,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>517009</v>
+        <v>517137</v>
       </c>
       <c r="R147" t="n">
-        <v>6986366</v>
+        <v>6986150</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15967,8 +15951,24 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -16124,10 +16124,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129908900</v>
+        <v>129910662</v>
       </c>
       <c r="B149" t="n">
-        <v>79095</v>
+        <v>89038</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16135,37 +16135,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>516960</v>
+        <v>517336</v>
       </c>
       <c r="R149" t="n">
-        <v>6986352</v>
+        <v>6986195</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16200,45 +16197,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal gran.</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -16255,37 +16221,50 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129908909</v>
+        <v>129910648</v>
       </c>
       <c r="B150" t="n">
-        <v>79095</v>
+        <v>98831</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16293,10 +16272,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>516915</v>
+        <v>517224</v>
       </c>
       <c r="R150" t="n">
-        <v>6986509</v>
+        <v>6986227</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16331,6 +16310,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -16340,31 +16324,6 @@
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -16381,7 +16340,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129908903</v>
+        <v>129908900</v>
       </c>
       <c r="B151" t="n">
         <v>79095</v>
@@ -16419,10 +16378,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>516956</v>
+        <v>516960</v>
       </c>
       <c r="R151" t="n">
-        <v>6986419</v>
+        <v>6986352</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16459,7 +16418,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>På en grovbarkad gammal gran.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16479,22 +16438,22 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -16512,10 +16471,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129910662</v>
+        <v>129908909</v>
       </c>
       <c r="B152" t="n">
-        <v>89038</v>
+        <v>79095</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16523,34 +16482,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>517336</v>
+        <v>516915</v>
       </c>
       <c r="R152" t="n">
-        <v>6986195</v>
+        <v>6986509</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16591,8 +16553,34 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16609,10 +16597,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129910607</v>
+        <v>129908903</v>
       </c>
       <c r="B153" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16620,34 +16608,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>517246</v>
+        <v>516956</v>
       </c>
       <c r="R153" t="n">
-        <v>6986091</v>
+        <v>6986419</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16682,14 +16673,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>På bark av tall.</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
@@ -16706,7 +16728,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129910587</v>
+        <v>129910607</v>
       </c>
       <c r="B154" t="n">
         <v>80200</v>
@@ -16741,10 +16763,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>517018</v>
+        <v>517246</v>
       </c>
       <c r="R154" t="n">
-        <v>6986301</v>
+        <v>6986091</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16803,7 +16825,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129910609</v>
+        <v>129910587</v>
       </c>
       <c r="B155" t="n">
         <v>80200</v>
@@ -16838,10 +16860,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>517221</v>
+        <v>517018</v>
       </c>
       <c r="R155" t="n">
-        <v>6986213</v>
+        <v>6986301</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16900,7 +16922,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129910745</v>
+        <v>129910609</v>
       </c>
       <c r="B156" t="n">
         <v>80200</v>
@@ -16935,10 +16957,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>516739</v>
+        <v>517221</v>
       </c>
       <c r="R156" t="n">
-        <v>6986664</v>
+        <v>6986213</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16973,11 +16995,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>På stående död sälg</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -16990,22 +17007,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129908882</v>
+        <v>129910745</v>
       </c>
       <c r="B157" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17013,46 +17030,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>516646</v>
+        <v>516739</v>
       </c>
       <c r="R157" t="n">
-        <v>6986735</v>
+        <v>6986664</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17089,7 +17094,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
+          <t>På stående död sälg</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17100,102 +17105,73 @@
       </c>
       <c r="AG157" t="b">
         <v>0</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129910648</v>
+        <v>129908882</v>
       </c>
       <c r="B158" t="n">
-        <v>98831</v>
+        <v>57741</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>517224</v>
+        <v>516646</v>
       </c>
       <c r="R158" t="n">
-        <v>6986227</v>
+        <v>6986735</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17232,7 +17208,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid vägkanten.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17241,9 +17217,33 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910574</v>
+        <v>129910666</v>
       </c>
       <c r="B2" t="n">
-        <v>79119</v>
+        <v>81158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>229558</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517340</v>
+        <v>517120</v>
       </c>
       <c r="R2" t="n">
-        <v>6986164</v>
+        <v>6986257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910577</v>
+        <v>129910557</v>
       </c>
       <c r="B3" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517035</v>
+        <v>517175</v>
       </c>
       <c r="R3" t="n">
-        <v>6986429</v>
+        <v>6986155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129908891</v>
+        <v>129910556</v>
       </c>
       <c r="B4" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,28 +893,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -911,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516683</v>
+        <v>517169</v>
       </c>
       <c r="R4" t="n">
-        <v>6986718</v>
+        <v>6986201</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På asp i granskog.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -960,34 +974,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1004,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910667</v>
+        <v>129910574</v>
       </c>
       <c r="B5" t="n">
-        <v>79351</v>
+        <v>79119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1003,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6459</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517221</v>
+        <v>517340</v>
       </c>
       <c r="R5" t="n">
-        <v>6986209</v>
+        <v>6986164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910557</v>
+        <v>129910577</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,42 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517175</v>
+        <v>517035</v>
       </c>
       <c r="R6" t="n">
-        <v>6986155</v>
+        <v>6986429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,11 +1160,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910556</v>
+        <v>129910654</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,31 +1197,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1254,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517169</v>
+        <v>517262</v>
       </c>
       <c r="R7" t="n">
-        <v>6986201</v>
+        <v>6986119</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,7 +1272,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Rikligt!!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,8 +1281,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1321,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129910642</v>
+        <v>129910752</v>
       </c>
       <c r="B8" t="n">
-        <v>78107</v>
+        <v>79095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517251</v>
+        <v>516947</v>
       </c>
       <c r="R8" t="n">
-        <v>6986078</v>
+        <v>6986297</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,6 +1388,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1406,22 +1405,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129910666</v>
+        <v>129908891</v>
       </c>
       <c r="B9" t="n">
-        <v>81158</v>
+        <v>80200</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,34 +1428,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229558</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517120</v>
+        <v>516683</v>
       </c>
       <c r="R9" t="n">
-        <v>6986257</v>
+        <v>6986718</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,14 +1497,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På asp i granskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1515,56 +1552,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129910654</v>
+        <v>129910667</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517262</v>
+        <v>517221</v>
       </c>
       <c r="R10" t="n">
-        <v>6986119</v>
+        <v>6986209</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,35 +1625,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt!!</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1644,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129910752</v>
+        <v>129910642</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>78107</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516947</v>
+        <v>517251</v>
       </c>
       <c r="R11" t="n">
-        <v>6986297</v>
+        <v>6986078</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,11 +1722,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1734,12 +1734,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
         <v>129908878</v>
       </c>
       <c r="B13" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129910580</v>
+        <v>129910564</v>
       </c>
       <c r="B27" t="n">
-        <v>80200</v>
+        <v>80066</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,21 +3302,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517047</v>
+        <v>517170</v>
       </c>
       <c r="R27" t="n">
-        <v>6986415</v>
+        <v>6986124</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,6 +3370,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3388,10 +3389,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129910610</v>
+        <v>129910649</v>
       </c>
       <c r="B28" t="n">
-        <v>80200</v>
+        <v>56922</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,34 +3400,50 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517211</v>
+        <v>517134</v>
       </c>
       <c r="R28" t="n">
-        <v>6986211</v>
+        <v>6986204</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,7 +3502,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129910599</v>
+        <v>129910601</v>
       </c>
       <c r="B29" t="n">
         <v>80200</v>
@@ -3520,10 +3537,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517177</v>
+        <v>517170</v>
       </c>
       <c r="R29" t="n">
-        <v>6986167</v>
+        <v>6986161</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,10 +3599,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129910620</v>
+        <v>129908880</v>
       </c>
       <c r="B30" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3593,34 +3610,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>517112</v>
+        <v>516686</v>
       </c>
       <c r="R30" t="n">
-        <v>6986273</v>
+        <v>6986687</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3655,6 +3684,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3663,6 +3697,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3679,32 +3738,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129910668</v>
+        <v>129910580</v>
       </c>
       <c r="B31" t="n">
-        <v>79351</v>
+        <v>80200</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>517042</v>
+        <v>517047</v>
       </c>
       <c r="R31" t="n">
-        <v>6986262</v>
+        <v>6986415</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,7 +3835,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129910631</v>
+        <v>129910599</v>
       </c>
       <c r="B32" t="n">
         <v>80200</v>
@@ -3811,10 +3870,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517287</v>
+        <v>517177</v>
       </c>
       <c r="R32" t="n">
-        <v>6986080</v>
+        <v>6986167</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3873,32 +3932,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129910601</v>
+        <v>129910668</v>
       </c>
       <c r="B33" t="n">
-        <v>80200</v>
+        <v>79351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3908,10 +3967,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517170</v>
+        <v>517042</v>
       </c>
       <c r="R33" t="n">
-        <v>6986161</v>
+        <v>6986262</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3970,7 +4029,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129910592</v>
+        <v>129910631</v>
       </c>
       <c r="B34" t="n">
         <v>80200</v>
@@ -4005,10 +4064,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517119</v>
+        <v>517287</v>
       </c>
       <c r="R34" t="n">
-        <v>6986251</v>
+        <v>6986080</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,10 +4126,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129910564</v>
+        <v>129910592</v>
       </c>
       <c r="B35" t="n">
-        <v>80066</v>
+        <v>80200</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,21 +4137,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4161,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517170</v>
+        <v>517119</v>
       </c>
       <c r="R35" t="n">
-        <v>6986124</v>
+        <v>6986251</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4146,7 +4205,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4165,10 +4223,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129908880</v>
+        <v>129910610</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,46 +4234,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>516686</v>
+        <v>517211</v>
       </c>
       <c r="R36" t="n">
-        <v>6986687</v>
+        <v>6986211</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,11 +4296,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4263,31 +4304,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4304,10 +4320,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129910649</v>
+        <v>129910620</v>
       </c>
       <c r="B37" t="n">
-        <v>56922</v>
+        <v>80200</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4315,50 +4331,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>517134</v>
+        <v>517112</v>
       </c>
       <c r="R37" t="n">
-        <v>6986204</v>
+        <v>6986273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4999,61 +4999,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129908896</v>
+        <v>129910646</v>
       </c>
       <c r="B44" t="n">
-        <v>98831</v>
+        <v>80160</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>516925</v>
+        <v>517237</v>
       </c>
       <c r="R44" t="n">
-        <v>6986509</v>
+        <v>6986059</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5088,25 +5072,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5123,45 +5096,61 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129910646</v>
+        <v>129908896</v>
       </c>
       <c r="B45" t="n">
-        <v>80160</v>
+        <v>98833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>517237</v>
+        <v>516925</v>
       </c>
       <c r="R45" t="n">
-        <v>6986059</v>
+        <v>6986509</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5196,14 +5185,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5223,7 +5223,7 @@
         <v>129910547</v>
       </c>
       <c r="B46" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5317,52 +5317,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129910660</v>
+        <v>129910568</v>
       </c>
       <c r="B47" t="n">
-        <v>92234</v>
+        <v>80201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>517050</v>
+        <v>517230</v>
       </c>
       <c r="R47" t="n">
-        <v>6986414</v>
+        <v>6986059</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5403,24 +5396,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5437,45 +5414,52 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129910568</v>
+        <v>129910660</v>
       </c>
       <c r="B48" t="n">
-        <v>80201</v>
+        <v>92236</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>517230</v>
+        <v>517050</v>
       </c>
       <c r="R48" t="n">
-        <v>6986059</v>
+        <v>6986414</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5516,8 +5500,24 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129910559</v>
+        <v>129910632</v>
       </c>
       <c r="B49" t="n">
-        <v>57900</v>
+        <v>80200</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,50 +5545,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>517266</v>
+        <v>517285</v>
       </c>
       <c r="R49" t="n">
-        <v>6986055</v>
+        <v>6986090</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5647,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129910750</v>
+        <v>129910591</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5658,21 +5642,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5682,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>517017</v>
+        <v>517068</v>
       </c>
       <c r="R50" t="n">
-        <v>6986332</v>
+        <v>6986257</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,11 +5704,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5737,22 +5716,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129910632</v>
+        <v>129910750</v>
       </c>
       <c r="B51" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5760,21 +5739,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5784,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>517285</v>
+        <v>517017</v>
       </c>
       <c r="R51" t="n">
-        <v>6986090</v>
+        <v>6986332</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5822,6 +5801,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5834,22 +5818,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129910591</v>
+        <v>129910559</v>
       </c>
       <c r="B52" t="n">
-        <v>80200</v>
+        <v>57900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5857,34 +5841,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>517068</v>
+        <v>517266</v>
       </c>
       <c r="R52" t="n">
-        <v>6986257</v>
+        <v>6986055</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6040,10 +6040,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129908905</v>
+        <v>129910588</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6051,37 +6051,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>517020</v>
+        <v>517014</v>
       </c>
       <c r="R54" t="n">
-        <v>6986358</v>
+        <v>6986283</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6116,45 +6113,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6171,7 +6137,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129910653</v>
+        <v>129908905</v>
       </c>
       <c r="B55" t="n">
         <v>79095</v>
@@ -6209,10 +6175,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>516971</v>
+        <v>517020</v>
       </c>
       <c r="R55" t="n">
-        <v>6986287</v>
+        <v>6986358</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6249,7 +6215,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Långväxta bålar på flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6262,6 +6228,11 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ55" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6272,9 +6243,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6292,7 +6268,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129910588</v>
+        <v>129910630</v>
       </c>
       <c r="B56" t="n">
         <v>80200</v>
@@ -6327,10 +6303,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>517014</v>
+        <v>517275</v>
       </c>
       <c r="R56" t="n">
-        <v>6986283</v>
+        <v>6986074</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6389,7 +6365,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129910630</v>
+        <v>129910606</v>
       </c>
       <c r="B57" t="n">
         <v>80200</v>
@@ -6424,10 +6400,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>517275</v>
+        <v>517237</v>
       </c>
       <c r="R57" t="n">
-        <v>6986074</v>
+        <v>6986073</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6486,7 +6462,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129910606</v>
+        <v>129910741</v>
       </c>
       <c r="B58" t="n">
         <v>80200</v>
@@ -6521,10 +6497,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>517237</v>
+        <v>517046</v>
       </c>
       <c r="R58" t="n">
-        <v>6986073</v>
+        <v>6986289</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6559,6 +6535,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6571,22 +6552,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129910741</v>
+        <v>129910653</v>
       </c>
       <c r="B59" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6594,34 +6575,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>517046</v>
+        <v>516971</v>
       </c>
       <c r="R59" t="n">
-        <v>6986289</v>
+        <v>6986287</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6658,7 +6642,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6667,18 +6651,34 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129908901</v>
+        <v>129910746</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6801,37 +6801,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>516936</v>
+        <v>516690</v>
       </c>
       <c r="R61" t="n">
-        <v>6986463</v>
+        <v>6986709</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6866,57 +6863,36 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129910604</v>
+        <v>129910595</v>
       </c>
       <c r="B62" t="n">
         <v>80200</v>
@@ -6951,10 +6927,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>517211</v>
+        <v>517169</v>
       </c>
       <c r="R62" t="n">
-        <v>6986077</v>
+        <v>6986203</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7013,7 +6989,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129908888</v>
+        <v>129910575</v>
       </c>
       <c r="B63" t="n">
         <v>80200</v>
@@ -7042,19 +7018,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>516854</v>
+        <v>516969</v>
       </c>
       <c r="R63" t="n">
-        <v>6986558</v>
+        <v>6986323</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7089,45 +7062,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7144,10 +7086,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129910746</v>
+        <v>129908901</v>
       </c>
       <c r="B64" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7155,34 +7097,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>516690</v>
+        <v>516936</v>
       </c>
       <c r="R64" t="n">
-        <v>6986709</v>
+        <v>6986463</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7217,36 +7162,57 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129910595</v>
+        <v>129910604</v>
       </c>
       <c r="B65" t="n">
         <v>80200</v>
@@ -7281,10 +7247,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>517169</v>
+        <v>517211</v>
       </c>
       <c r="R65" t="n">
-        <v>6986203</v>
+        <v>6986077</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7343,7 +7309,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129910617</v>
+        <v>129908888</v>
       </c>
       <c r="B66" t="n">
         <v>80200</v>
@@ -7372,16 +7338,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>517040</v>
+        <v>516854</v>
       </c>
       <c r="R66" t="n">
-        <v>6986263</v>
+        <v>6986558</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7416,14 +7385,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7440,7 +7440,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129910575</v>
+        <v>129910617</v>
       </c>
       <c r="B67" t="n">
         <v>80200</v>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>516969</v>
+        <v>517040</v>
       </c>
       <c r="R67" t="n">
-        <v>6986323</v>
+        <v>6986263</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7834,10 +7834,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129908908</v>
+        <v>129908890</v>
       </c>
       <c r="B71" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7845,21 +7845,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>516927</v>
+        <v>516676</v>
       </c>
       <c r="R71" t="n">
-        <v>6986311</v>
+        <v>6986711</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7910,6 +7910,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På grovbarkad asp i granskog.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7927,22 +7932,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -7960,37 +7965,41 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129908890</v>
+        <v>129910664</v>
       </c>
       <c r="B72" t="n">
-        <v>80200</v>
+        <v>80235</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7998,10 +8007,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>516676</v>
+        <v>517231</v>
       </c>
       <c r="R72" t="n">
-        <v>6986711</v>
+        <v>6986060</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8036,11 +8045,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På grovbarkad asp i granskog.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8050,31 +8054,6 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8091,27 +8070,27 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129910664</v>
+        <v>129908908</v>
       </c>
       <c r="B73" t="n">
-        <v>80235</v>
+        <v>79095</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8121,11 +8100,7 @@
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8133,10 +8108,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>517231</v>
+        <v>516927</v>
       </c>
       <c r="R73" t="n">
-        <v>6986060</v>
+        <v>6986311</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8180,6 +8155,31 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8331,45 +8331,57 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129910565</v>
+        <v>129908881</v>
       </c>
       <c r="B75" t="n">
-        <v>79181</v>
+        <v>57741</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6450</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>517235</v>
+        <v>516659</v>
       </c>
       <c r="R75" t="n">
-        <v>6986250</v>
+        <v>6986705</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8404,6 +8416,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid vägkanten.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8412,6 +8429,31 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8428,10 +8470,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129910670</v>
+        <v>129910565</v>
       </c>
       <c r="B76" t="n">
-        <v>79351</v>
+        <v>79181</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8439,21 +8481,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6459</v>
+        <v>6450</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8463,10 +8505,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>517175</v>
+        <v>517235</v>
       </c>
       <c r="R76" t="n">
-        <v>6986169</v>
+        <v>6986250</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8913,57 +8955,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129908881</v>
+        <v>129910670</v>
       </c>
       <c r="B81" t="n">
-        <v>57741</v>
+        <v>79351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>516659</v>
+        <v>517175</v>
       </c>
       <c r="R81" t="n">
-        <v>6986705</v>
+        <v>6986169</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8998,11 +9028,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid vägkanten.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9011,31 +9036,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9052,61 +9052,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129908912</v>
+        <v>129910740</v>
       </c>
       <c r="B82" t="n">
-        <v>98748</v>
+        <v>80200</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>516929</v>
+        <v>517033</v>
       </c>
       <c r="R82" t="n">
-        <v>6986305</v>
+        <v>6986309</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9143,7 +9127,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>1 vinterståndare.</t>
+          <t>På torraka och låga av sälg</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9152,85 +9136,63 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129908894</v>
+        <v>129910749</v>
       </c>
       <c r="B83" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>517028</v>
+        <v>516929</v>
       </c>
       <c r="R83" t="n">
-        <v>6986324</v>
+        <v>6986288</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9265,45 +9227,34 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129910749</v>
+        <v>129910543</v>
       </c>
       <c r="B84" t="n">
-        <v>79095</v>
+        <v>83073</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9311,21 +9262,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9335,10 +9286,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>516929</v>
+        <v>517077</v>
       </c>
       <c r="R84" t="n">
-        <v>6986288</v>
+        <v>6986242</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9385,22 +9336,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129910740</v>
+        <v>129910546</v>
       </c>
       <c r="B85" t="n">
-        <v>80200</v>
+        <v>83073</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9408,21 +9359,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9432,10 +9383,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>517033</v>
+        <v>517241</v>
       </c>
       <c r="R85" t="n">
-        <v>6986309</v>
+        <v>6986104</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9470,11 +9421,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På torraka och låga av sälg</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9487,22 +9433,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129910543</v>
+        <v>129910602</v>
       </c>
       <c r="B86" t="n">
-        <v>83073</v>
+        <v>80200</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9510,21 +9456,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9534,10 +9480,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>517077</v>
+        <v>517146</v>
       </c>
       <c r="R86" t="n">
-        <v>6986242</v>
+        <v>6986161</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9596,10 +9542,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129910546</v>
+        <v>129910619</v>
       </c>
       <c r="B87" t="n">
-        <v>83073</v>
+        <v>80200</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9607,21 +9553,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9631,10 +9577,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>517241</v>
+        <v>517108</v>
       </c>
       <c r="R87" t="n">
-        <v>6986104</v>
+        <v>6986255</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9693,10 +9639,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129910602</v>
+        <v>129910647</v>
       </c>
       <c r="B88" t="n">
-        <v>80200</v>
+        <v>78852</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9704,21 +9650,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9728,10 +9674,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>517146</v>
+        <v>517081</v>
       </c>
       <c r="R88" t="n">
-        <v>6986161</v>
+        <v>6986186</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9790,32 +9736,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129910619</v>
+        <v>129910571</v>
       </c>
       <c r="B89" t="n">
-        <v>80200</v>
+        <v>80104</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9825,10 +9771,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>517108</v>
+        <v>517109</v>
       </c>
       <c r="R89" t="n">
-        <v>6986255</v>
+        <v>6986168</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9887,10 +9833,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129910647</v>
+        <v>129910636</v>
       </c>
       <c r="B90" t="n">
-        <v>78852</v>
+        <v>80200</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9898,21 +9844,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9922,10 +9868,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>517081</v>
+        <v>517228</v>
       </c>
       <c r="R90" t="n">
-        <v>6986186</v>
+        <v>6986059</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9984,32 +9930,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129910571</v>
+        <v>129910545</v>
       </c>
       <c r="B91" t="n">
-        <v>80104</v>
+        <v>83073</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10019,10 +9965,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>517109</v>
+        <v>517251</v>
       </c>
       <c r="R91" t="n">
-        <v>6986168</v>
+        <v>6986081</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10081,45 +10027,61 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129910636</v>
+        <v>129908912</v>
       </c>
       <c r="B92" t="n">
-        <v>80200</v>
+        <v>98750</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>517228</v>
+        <v>516929</v>
       </c>
       <c r="R92" t="n">
-        <v>6986059</v>
+        <v>6986305</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10154,14 +10116,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>1 vinterståndare.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10178,45 +10151,61 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129910545</v>
+        <v>129908894</v>
       </c>
       <c r="B93" t="n">
-        <v>83073</v>
+        <v>98833</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>517251</v>
+        <v>517028</v>
       </c>
       <c r="R93" t="n">
-        <v>6986081</v>
+        <v>6986324</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10251,14 +10240,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -10275,32 +10275,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129910665</v>
+        <v>129910748</v>
       </c>
       <c r="B94" t="n">
-        <v>83065</v>
+        <v>98833</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10310,10 +10310,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>517165</v>
+        <v>516692</v>
       </c>
       <c r="R94" t="n">
-        <v>6986212</v>
+        <v>6986711</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10348,6 +10348,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10360,12 +10365,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10765,45 +10770,53 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129910748</v>
+        <v>129910554</v>
       </c>
       <c r="B99" t="n">
-        <v>98831</v>
+        <v>57741</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>516692</v>
+        <v>516949</v>
       </c>
       <c r="R99" t="n">
-        <v>6986711</v>
+        <v>6986325</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10840,7 +10853,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Ca 50 st inom 1 kvm. En vinterståndare.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10855,22 +10868,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129910554</v>
+        <v>129910665</v>
       </c>
       <c r="B100" t="n">
-        <v>57741</v>
+        <v>83065</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10878,42 +10891,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>516949</v>
+        <v>517165</v>
       </c>
       <c r="R100" t="n">
-        <v>6986325</v>
+        <v>6986212</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10946,11 +10951,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10977,32 +10977,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129910645</v>
+        <v>129910622</v>
       </c>
       <c r="B101" t="n">
-        <v>80071</v>
+        <v>80200</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11012,10 +11012,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>517286</v>
+        <v>517142</v>
       </c>
       <c r="R101" t="n">
-        <v>6986091</v>
+        <v>6986177</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11074,10 +11074,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129908899</v>
+        <v>129908886</v>
       </c>
       <c r="B102" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11085,26 +11085,30 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -11112,10 +11116,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>516951</v>
+        <v>517038</v>
       </c>
       <c r="R102" t="n">
-        <v>6986304</v>
+        <v>6986289</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11150,6 +11154,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På levande sälg.</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11159,31 +11168,6 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11200,48 +11184,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129908902</v>
+        <v>129910645</v>
       </c>
       <c r="B103" t="n">
-        <v>79095</v>
+        <v>80071</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>516926</v>
+        <v>517286</v>
       </c>
       <c r="R103" t="n">
-        <v>6986445</v>
+        <v>6986091</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11276,45 +11257,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11622,10 +11572,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129910622</v>
+        <v>129908899</v>
       </c>
       <c r="B107" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11633,34 +11583,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>517142</v>
+        <v>516951</v>
       </c>
       <c r="R107" t="n">
-        <v>6986177</v>
+        <v>6986304</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11701,8 +11654,34 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11719,10 +11698,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129908886</v>
+        <v>129908902</v>
       </c>
       <c r="B108" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11730,30 +11709,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11761,10 +11736,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>517038</v>
+        <v>516926</v>
       </c>
       <c r="R108" t="n">
-        <v>6986289</v>
+        <v>6986445</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11801,7 +11776,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>På levande sälg.</t>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11813,6 +11788,31 @@
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -11832,7 +11832,7 @@
         <v>129910661</v>
       </c>
       <c r="B109" t="n">
-        <v>92234</v>
+        <v>92236</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12084,10 +12084,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129910652</v>
+        <v>129910743</v>
       </c>
       <c r="B111" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12095,37 +12095,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>517345</v>
+        <v>516874</v>
       </c>
       <c r="R111" t="n">
-        <v>6986186</v>
+        <v>6986542</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12160,47 +12157,36 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Liggande död sälg</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129910743</v>
+        <v>129910627</v>
       </c>
       <c r="B112" t="n">
         <v>80200</v>
@@ -12235,10 +12221,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>516874</v>
+        <v>517139</v>
       </c>
       <c r="R112" t="n">
-        <v>6986542</v>
+        <v>6986155</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12273,11 +12259,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Liggande död sälg</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12290,19 +12271,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129910627</v>
+        <v>129910603</v>
       </c>
       <c r="B113" t="n">
         <v>80200</v>
@@ -12337,10 +12318,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>517139</v>
+        <v>517199</v>
       </c>
       <c r="R113" t="n">
-        <v>6986155</v>
+        <v>6986098</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12399,10 +12380,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129910603</v>
+        <v>129910652</v>
       </c>
       <c r="B114" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12410,34 +12391,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>517199</v>
+        <v>517345</v>
       </c>
       <c r="R114" t="n">
-        <v>6986098</v>
+        <v>6986186</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12478,8 +12462,24 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13272,7 +13272,7 @@
         <v>129910562</v>
       </c>
       <c r="B122" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129910640</v>
+        <v>129910637</v>
       </c>
       <c r="B124" t="n">
         <v>80200</v>
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>517288</v>
+        <v>517251</v>
       </c>
       <c r="R124" t="n">
-        <v>6986118</v>
+        <v>6986087</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13588,7 +13588,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129910621</v>
+        <v>129910635</v>
       </c>
       <c r="B125" t="n">
         <v>80200</v>
@@ -13623,10 +13623,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>517170</v>
+        <v>517229</v>
       </c>
       <c r="R125" t="n">
-        <v>6986215</v>
+        <v>6986063</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13685,7 +13685,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129910635</v>
+        <v>129910640</v>
       </c>
       <c r="B126" t="n">
         <v>80200</v>
@@ -13720,10 +13720,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>517229</v>
+        <v>517288</v>
       </c>
       <c r="R126" t="n">
-        <v>6986063</v>
+        <v>6986118</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13782,7 +13782,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129910605</v>
+        <v>129910621</v>
       </c>
       <c r="B127" t="n">
         <v>80200</v>
@@ -13817,10 +13817,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>517273</v>
+        <v>517170</v>
       </c>
       <c r="R127" t="n">
-        <v>6986075</v>
+        <v>6986215</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13879,32 +13879,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129910566</v>
+        <v>129910605</v>
       </c>
       <c r="B128" t="n">
-        <v>79181</v>
+        <v>80200</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13914,10 +13914,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>517128</v>
+        <v>517273</v>
       </c>
       <c r="R128" t="n">
-        <v>6986180</v>
+        <v>6986075</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13976,32 +13976,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129910637</v>
+        <v>129910566</v>
       </c>
       <c r="B129" t="n">
-        <v>80200</v>
+        <v>79181</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14011,10 +14011,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>517251</v>
+        <v>517128</v>
       </c>
       <c r="R129" t="n">
-        <v>6986087</v>
+        <v>6986180</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14076,7 +14076,7 @@
         <v>129908895</v>
       </c>
       <c r="B130" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14197,10 +14197,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129910584</v>
+        <v>129910551</v>
       </c>
       <c r="B131" t="n">
-        <v>80200</v>
+        <v>91641</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14208,34 +14208,41 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>517004</v>
+        <v>517014</v>
       </c>
       <c r="R131" t="n">
-        <v>6986361</v>
+        <v>6986339</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14276,8 +14283,29 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
@@ -14294,45 +14322,52 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129910594</v>
+        <v>129910659</v>
       </c>
       <c r="B132" t="n">
-        <v>80200</v>
+        <v>92923</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>517165</v>
+        <v>517328</v>
       </c>
       <c r="R132" t="n">
-        <v>6986222</v>
+        <v>6986156</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14373,6 +14408,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14391,7 +14427,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129910624</v>
+        <v>129910747</v>
       </c>
       <c r="B133" t="n">
         <v>80200</v>
@@ -14426,10 +14462,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>517195</v>
+        <v>516674</v>
       </c>
       <c r="R133" t="n">
-        <v>6986175</v>
+        <v>6986695</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14464,6 +14500,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på liggande men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -14476,57 +14517,73 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129910747</v>
+        <v>129910560</v>
       </c>
       <c r="B134" t="n">
-        <v>80200</v>
+        <v>58377</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>102125</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>516674</v>
+        <v>517237</v>
       </c>
       <c r="R134" t="n">
-        <v>6986695</v>
+        <v>6986082</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14561,11 +14618,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på liggande men levande sälg.</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14578,19 +14630,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129910634</v>
+        <v>129910584</v>
       </c>
       <c r="B135" t="n">
         <v>80200</v>
@@ -14625,10 +14677,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>517233</v>
+        <v>517004</v>
       </c>
       <c r="R135" t="n">
-        <v>6986069</v>
+        <v>6986361</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14687,32 +14739,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129910572</v>
+        <v>129910594</v>
       </c>
       <c r="B136" t="n">
-        <v>80104</v>
+        <v>80200</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14722,10 +14774,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>517147</v>
+        <v>517165</v>
       </c>
       <c r="R136" t="n">
-        <v>6986129</v>
+        <v>6986222</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14784,61 +14836,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129910560</v>
+        <v>129910624</v>
       </c>
       <c r="B137" t="n">
-        <v>58377</v>
+        <v>80200</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>517237</v>
+        <v>517195</v>
       </c>
       <c r="R137" t="n">
-        <v>6986082</v>
+        <v>6986175</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14897,10 +14933,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129910551</v>
+        <v>129910634</v>
       </c>
       <c r="B138" t="n">
-        <v>91639</v>
+        <v>80200</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14908,41 +14944,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>517014</v>
+        <v>517233</v>
       </c>
       <c r="R138" t="n">
-        <v>6986339</v>
+        <v>6986069</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14983,29 +15012,8 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -15022,10 +15030,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129910659</v>
+        <v>129910572</v>
       </c>
       <c r="B139" t="n">
-        <v>92921</v>
+        <v>80104</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15033,41 +15041,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>517328</v>
+        <v>517147</v>
       </c>
       <c r="R139" t="n">
-        <v>6986156</v>
+        <v>6986129</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15108,7 +15109,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15130,7 +15130,7 @@
         <v>129908893</v>
       </c>
       <c r="B140" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>129908897</v>
       </c>
       <c r="B141" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15371,32 +15371,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129910656</v>
+        <v>129910570</v>
       </c>
       <c r="B142" t="n">
-        <v>82939</v>
+        <v>80104</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15406,10 +15406,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>517001</v>
+        <v>517172</v>
       </c>
       <c r="R142" t="n">
-        <v>6986292</v>
+        <v>6986122</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15468,45 +15468,48 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129910570</v>
+        <v>129910651</v>
       </c>
       <c r="B143" t="n">
-        <v>80104</v>
+        <v>79095</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>517172</v>
+        <v>517137</v>
       </c>
       <c r="R143" t="n">
-        <v>6986122</v>
+        <v>6986150</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15547,8 +15550,24 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
@@ -15869,10 +15888,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129910651</v>
+        <v>129910656</v>
       </c>
       <c r="B147" t="n">
-        <v>79095</v>
+        <v>82939</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15880,37 +15899,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>517137</v>
+        <v>517001</v>
       </c>
       <c r="R147" t="n">
-        <v>6986150</v>
+        <v>6986292</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15951,24 +15967,8 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -16124,10 +16124,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129910662</v>
+        <v>129908909</v>
       </c>
       <c r="B149" t="n">
-        <v>89038</v>
+        <v>79095</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16135,34 +16135,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>517336</v>
+        <v>516915</v>
       </c>
       <c r="R149" t="n">
-        <v>6986195</v>
+        <v>6986509</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16203,8 +16206,34 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -16221,50 +16250,37 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129910648</v>
+        <v>129908903</v>
       </c>
       <c r="B150" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16272,10 +16288,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>517224</v>
+        <v>516956</v>
       </c>
       <c r="R150" t="n">
-        <v>6986227</v>
+        <v>6986419</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16312,7 +16328,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16324,6 +16340,31 @@
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -16340,10 +16381,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129908900</v>
+        <v>129910587</v>
       </c>
       <c r="B151" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16351,37 +16392,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>516960</v>
+        <v>517018</v>
       </c>
       <c r="R151" t="n">
-        <v>6986352</v>
+        <v>6986301</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16416,45 +16454,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>På en grovbarkad gammal gran.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16471,10 +16478,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129908909</v>
+        <v>129910609</v>
       </c>
       <c r="B152" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16482,37 +16489,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>516915</v>
+        <v>517221</v>
       </c>
       <c r="R152" t="n">
-        <v>6986509</v>
+        <v>6986213</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16553,34 +16557,8 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16597,10 +16575,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129908903</v>
+        <v>129910745</v>
       </c>
       <c r="B153" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16608,37 +16586,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>516956</v>
+        <v>516739</v>
       </c>
       <c r="R153" t="n">
-        <v>6986419</v>
+        <v>6986664</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16675,7 +16650,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>På stående död sälg</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16684,54 +16659,28 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129910607</v>
+        <v>129910662</v>
       </c>
       <c r="B154" t="n">
-        <v>80200</v>
+        <v>89038</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16739,21 +16688,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16763,10 +16712,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>517246</v>
+        <v>517336</v>
       </c>
       <c r="R154" t="n">
-        <v>6986091</v>
+        <v>6986195</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16825,7 +16774,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129910587</v>
+        <v>129910607</v>
       </c>
       <c r="B155" t="n">
         <v>80200</v>
@@ -16860,10 +16809,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>517018</v>
+        <v>517246</v>
       </c>
       <c r="R155" t="n">
-        <v>6986301</v>
+        <v>6986091</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16922,10 +16871,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129910609</v>
+        <v>129908900</v>
       </c>
       <c r="B156" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16933,34 +16882,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>517221</v>
+        <v>516960</v>
       </c>
       <c r="R156" t="n">
-        <v>6986213</v>
+        <v>6986352</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16995,14 +16947,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På en grovbarkad gammal gran.</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
@@ -17019,45 +17002,61 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129910745</v>
+        <v>129910648</v>
       </c>
       <c r="B157" t="n">
-        <v>80200</v>
+        <v>98833</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>516739</v>
+        <v>517224</v>
       </c>
       <c r="R157" t="n">
-        <v>6986664</v>
+        <v>6986227</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17094,7 +17093,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>På stående död sälg</t>
+          <t>Minst 7 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17103,18 +17102,19 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -17260,10 +17260,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129908910</v>
+        <v>129910558</v>
       </c>
       <c r="B159" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17271,26 +17271,31 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -17298,10 +17303,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>516902</v>
+        <v>517356</v>
       </c>
       <c r="R159" t="n">
-        <v>6986521</v>
+        <v>6986190</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17336,40 +17341,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
@@ -17386,7 +17370,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129908904</v>
+        <v>129908910</v>
       </c>
       <c r="B160" t="n">
         <v>79095</v>
@@ -17424,10 +17408,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>516981</v>
+        <v>516902</v>
       </c>
       <c r="R160" t="n">
-        <v>6986356</v>
+        <v>6986521</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17474,7 +17458,7 @@
       </c>
       <c r="AH160" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ160" t="inlineStr">
@@ -17512,10 +17496,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129908907</v>
+        <v>129910744</v>
       </c>
       <c r="B161" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17523,37 +17507,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>517033</v>
+        <v>516858</v>
       </c>
       <c r="R161" t="n">
-        <v>6986307</v>
+        <v>6986573</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17590,7 +17571,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>På en gammal gran i granskog.</t>
+          <t>På både en lutande död sälg och en stående avbruten sälg.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17599,54 +17580,28 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129910558</v>
+        <v>129910611</v>
       </c>
       <c r="B162" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17654,42 +17609,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>517356</v>
+        <v>517216</v>
       </c>
       <c r="R162" t="n">
-        <v>6986190</v>
+        <v>6986197</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17722,11 +17669,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17753,10 +17695,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129910548</v>
+        <v>129910598</v>
       </c>
       <c r="B163" t="n">
-        <v>97077</v>
+        <v>80200</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17764,21 +17706,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17788,10 +17730,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>517167</v>
+        <v>517155</v>
       </c>
       <c r="R163" t="n">
-        <v>6986105</v>
+        <v>6986194</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17850,10 +17792,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129910550</v>
+        <v>129910628</v>
       </c>
       <c r="B164" t="n">
-        <v>90671</v>
+        <v>80200</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17861,21 +17803,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17885,10 +17827,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>517343</v>
+        <v>517207</v>
       </c>
       <c r="R164" t="n">
-        <v>6986165</v>
+        <v>6986088</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17947,10 +17889,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129910744</v>
+        <v>129908904</v>
       </c>
       <c r="B165" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17958,34 +17900,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>516858</v>
+        <v>516981</v>
       </c>
       <c r="R165" t="n">
-        <v>6986573</v>
+        <v>6986356</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18020,61 +17965,82 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>På både en lutande död sälg och en stående avbruten sälg.</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129910611</v>
+        <v>129910669</v>
       </c>
       <c r="B166" t="n">
-        <v>80200</v>
+        <v>79351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18084,10 +18050,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>517216</v>
+        <v>517113</v>
       </c>
       <c r="R166" t="n">
-        <v>6986197</v>
+        <v>6986244</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18146,7 +18112,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129910598</v>
+        <v>129910586</v>
       </c>
       <c r="B167" t="n">
         <v>80200</v>
@@ -18181,10 +18147,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>517155</v>
+        <v>517006</v>
       </c>
       <c r="R167" t="n">
-        <v>6986194</v>
+        <v>6986354</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18243,7 +18209,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129910628</v>
+        <v>129910616</v>
       </c>
       <c r="B168" t="n">
         <v>80200</v>
@@ -18278,10 +18244,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>517207</v>
+        <v>517030</v>
       </c>
       <c r="R168" t="n">
-        <v>6986088</v>
+        <v>6986400</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18340,32 +18306,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129910669</v>
+        <v>129910576</v>
       </c>
       <c r="B169" t="n">
-        <v>79351</v>
+        <v>80200</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18375,10 +18341,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>517113</v>
+        <v>516994</v>
       </c>
       <c r="R169" t="n">
-        <v>6986244</v>
+        <v>6986453</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18437,7 +18403,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129910586</v>
+        <v>129910623</v>
       </c>
       <c r="B170" t="n">
         <v>80200</v>
@@ -18472,10 +18438,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>517006</v>
+        <v>517174</v>
       </c>
       <c r="R170" t="n">
-        <v>6986354</v>
+        <v>6986187</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18534,10 +18500,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129910616</v>
+        <v>129908907</v>
       </c>
       <c r="B171" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18545,34 +18511,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>517030</v>
+        <v>517033</v>
       </c>
       <c r="R171" t="n">
-        <v>6986400</v>
+        <v>6986307</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18607,14 +18576,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>På en gammal gran i granskog.</t>
+        </is>
+      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
@@ -18631,10 +18631,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129910576</v>
+        <v>129910548</v>
       </c>
       <c r="B172" t="n">
-        <v>80200</v>
+        <v>97079</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18642,21 +18642,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18666,10 +18666,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>516994</v>
+        <v>517167</v>
       </c>
       <c r="R172" t="n">
-        <v>6986453</v>
+        <v>6986105</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18728,10 +18728,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129910623</v>
+        <v>129910550</v>
       </c>
       <c r="B173" t="n">
-        <v>80200</v>
+        <v>90673</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18739,21 +18739,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18763,10 +18763,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>517174</v>
+        <v>517343</v>
       </c>
       <c r="R173" t="n">
-        <v>6986187</v>
+        <v>6986165</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -5943,7 +5943,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129910588</v>
+        <v>129910741</v>
       </c>
       <c r="B53" t="n">
         <v>80285</v>
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>517014</v>
+        <v>517046</v>
       </c>
       <c r="R53" t="n">
-        <v>6986283</v>
+        <v>6986289</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6016,6 +6016,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6028,22 +6033,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129908905</v>
+        <v>129910588</v>
       </c>
       <c r="B54" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6051,37 +6056,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>517020</v>
+        <v>517014</v>
       </c>
       <c r="R54" t="n">
-        <v>6986358</v>
+        <v>6986283</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6116,45 +6118,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar i granskog.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6171,10 +6142,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129910630</v>
+        <v>129908905</v>
       </c>
       <c r="B55" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6182,34 +6153,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>517275</v>
+        <v>517020</v>
       </c>
       <c r="R55" t="n">
-        <v>6986074</v>
+        <v>6986358</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6244,14 +6218,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar i granskog.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6268,7 +6273,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129910606</v>
+        <v>129910630</v>
       </c>
       <c r="B56" t="n">
         <v>80285</v>
@@ -6303,10 +6308,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>517237</v>
+        <v>517275</v>
       </c>
       <c r="R56" t="n">
-        <v>6986073</v>
+        <v>6986074</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6365,10 +6370,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129910573</v>
+        <v>129910606</v>
       </c>
       <c r="B57" t="n">
-        <v>75270</v>
+        <v>80285</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6376,21 +6381,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6400,10 +6405,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>517112</v>
+        <v>517237</v>
       </c>
       <c r="R57" t="n">
-        <v>6986241</v>
+        <v>6986073</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6462,10 +6467,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129910653</v>
+        <v>129910573</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>75270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6473,37 +6478,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>516971</v>
+        <v>517112</v>
       </c>
       <c r="R58" t="n">
-        <v>6986287</v>
+        <v>6986241</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6538,35 +6540,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -6583,27 +6564,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129910663</v>
+        <v>129910653</v>
       </c>
       <c r="B59" t="n">
-        <v>80320</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6613,11 +6594,7 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6625,10 +6602,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>517007</v>
+        <v>516971</v>
       </c>
       <c r="R59" t="n">
-        <v>6986367</v>
+        <v>6986287</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6663,6 +6640,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6672,6 +6654,21 @@
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6688,45 +6685,52 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129910741</v>
+        <v>129910663</v>
       </c>
       <c r="B60" t="n">
-        <v>80285</v>
+        <v>80320</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>517046</v>
+        <v>517007</v>
       </c>
       <c r="R60" t="n">
-        <v>6986289</v>
+        <v>6986367</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6761,29 +6765,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -9052,10 +9052,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129910636</v>
+        <v>129910543</v>
       </c>
       <c r="B82" t="n">
-        <v>80285</v>
+        <v>83158</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9063,21 +9063,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9087,10 +9087,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>517228</v>
+        <v>517077</v>
       </c>
       <c r="R82" t="n">
-        <v>6986059</v>
+        <v>6986242</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9149,10 +9149,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129910740</v>
+        <v>129910546</v>
       </c>
       <c r="B83" t="n">
-        <v>80285</v>
+        <v>83158</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9160,21 +9160,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9184,10 +9184,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>517033</v>
+        <v>517241</v>
       </c>
       <c r="R83" t="n">
-        <v>6986309</v>
+        <v>6986104</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9222,11 +9222,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På torraka och låga av sälg</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9239,57 +9234,73 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129910749</v>
+        <v>129908894</v>
       </c>
       <c r="B84" t="n">
-        <v>79180</v>
+        <v>98920</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>516929</v>
+        <v>517028</v>
       </c>
       <c r="R84" t="n">
-        <v>6986288</v>
+        <v>6986324</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9324,34 +9335,45 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129910543</v>
+        <v>129910602</v>
       </c>
       <c r="B85" t="n">
-        <v>83158</v>
+        <v>80285</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9359,21 +9381,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9383,10 +9405,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>517077</v>
+        <v>517146</v>
       </c>
       <c r="R85" t="n">
-        <v>6986242</v>
+        <v>6986161</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9445,10 +9467,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129910546</v>
+        <v>129910619</v>
       </c>
       <c r="B86" t="n">
-        <v>83158</v>
+        <v>80285</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9456,21 +9478,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9480,10 +9502,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>517241</v>
+        <v>517108</v>
       </c>
       <c r="R86" t="n">
-        <v>6986104</v>
+        <v>6986255</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9542,61 +9564,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129908894</v>
+        <v>129910647</v>
       </c>
       <c r="B87" t="n">
-        <v>98920</v>
+        <v>78937</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>517028</v>
+        <v>517081</v>
       </c>
       <c r="R87" t="n">
-        <v>6986324</v>
+        <v>6986186</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9631,25 +9637,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor och 1 vinterståndare inom ca 0,5 m2 yta i granskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -9666,32 +9661,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129910602</v>
+        <v>129910571</v>
       </c>
       <c r="B88" t="n">
-        <v>80285</v>
+        <v>80189</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9701,10 +9696,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>517146</v>
+        <v>517109</v>
       </c>
       <c r="R88" t="n">
-        <v>6986161</v>
+        <v>6986168</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9763,10 +9758,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129910619</v>
+        <v>129910545</v>
       </c>
       <c r="B89" t="n">
-        <v>80285</v>
+        <v>83158</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9774,21 +9769,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9798,10 +9793,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>517108</v>
+        <v>517251</v>
       </c>
       <c r="R89" t="n">
-        <v>6986255</v>
+        <v>6986081</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9860,45 +9855,61 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129910647</v>
+        <v>129908912</v>
       </c>
       <c r="B90" t="n">
-        <v>78937</v>
+        <v>98837</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>517081</v>
+        <v>516929</v>
       </c>
       <c r="R90" t="n">
-        <v>6986186</v>
+        <v>6986305</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9933,14 +9944,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>1 vinterståndare.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -9957,32 +9979,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129910571</v>
+        <v>129910636</v>
       </c>
       <c r="B91" t="n">
-        <v>80189</v>
+        <v>80285</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9992,10 +10014,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>517109</v>
+        <v>517228</v>
       </c>
       <c r="R91" t="n">
-        <v>6986168</v>
+        <v>6986059</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10054,10 +10076,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129910545</v>
+        <v>129910740</v>
       </c>
       <c r="B92" t="n">
-        <v>83158</v>
+        <v>80285</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10065,21 +10087,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10089,10 +10111,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>517251</v>
+        <v>517033</v>
       </c>
       <c r="R92" t="n">
-        <v>6986081</v>
+        <v>6986309</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10127,6 +10149,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På torraka och låga av sälg</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10139,63 +10166,47 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129908912</v>
+        <v>129910749</v>
       </c>
       <c r="B93" t="n">
-        <v>98837</v>
+        <v>79180</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
@@ -10205,7 +10216,7 @@
         <v>516929</v>
       </c>
       <c r="R93" t="n">
-        <v>6986305</v>
+        <v>6986288</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10240,35 +10251,24 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>1 vinterståndare.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11829,10 +11829,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129910743</v>
+        <v>129908911</v>
       </c>
       <c r="B109" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11840,34 +11840,41 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>516874</v>
+        <v>516729</v>
       </c>
       <c r="R109" t="n">
-        <v>6986542</v>
+        <v>6986683</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11904,7 +11911,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Liggande död sälg</t>
+          <t>På gran med apothecier.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11913,57 +11920,83 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129908911</v>
+        <v>129910661</v>
       </c>
       <c r="B110" t="n">
-        <v>79180</v>
+        <v>92323</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -11973,10 +12006,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>516729</v>
+        <v>517220</v>
       </c>
       <c r="R110" t="n">
-        <v>6986683</v>
+        <v>6986131</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12011,11 +12044,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På gran med apothecier.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12026,29 +12054,19 @@
       <c r="AG110" t="b">
         <v>0</v>
       </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12066,10 +12084,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129910627</v>
+        <v>129910652</v>
       </c>
       <c r="B111" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12077,34 +12095,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>517139</v>
+        <v>517345</v>
       </c>
       <c r="R111" t="n">
-        <v>6986155</v>
+        <v>6986186</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12145,8 +12166,24 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -12163,52 +12200,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129910661</v>
+        <v>129910627</v>
       </c>
       <c r="B112" t="n">
-        <v>92323</v>
+        <v>80285</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>517220</v>
+        <v>517139</v>
       </c>
       <c r="R112" t="n">
-        <v>6986131</v>
+        <v>6986155</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12249,24 +12279,8 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -12283,10 +12297,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129910652</v>
+        <v>129910603</v>
       </c>
       <c r="B113" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12294,37 +12308,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>517345</v>
+        <v>517199</v>
       </c>
       <c r="R113" t="n">
-        <v>6986186</v>
+        <v>6986098</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12365,24 +12376,8 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -12399,7 +12394,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129910603</v>
+        <v>129910743</v>
       </c>
       <c r="B114" t="n">
         <v>80285</v>
@@ -12434,10 +12429,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>517199</v>
+        <v>516874</v>
       </c>
       <c r="R114" t="n">
-        <v>6986098</v>
+        <v>6986542</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12472,6 +12467,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Liggande död sälg</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -12484,12 +12484,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -14197,10 +14197,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129910551</v>
+        <v>129910747</v>
       </c>
       <c r="B131" t="n">
-        <v>91728</v>
+        <v>80285</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14208,41 +14208,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>517014</v>
+        <v>516674</v>
       </c>
       <c r="R131" t="n">
-        <v>6986339</v>
+        <v>6986695</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14277,55 +14270,39 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på liggande men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129910584</v>
+        <v>129910551</v>
       </c>
       <c r="B132" t="n">
-        <v>80285</v>
+        <v>91728</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14333,34 +14310,41 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>517004</v>
+        <v>517014</v>
       </c>
       <c r="R132" t="n">
-        <v>6986361</v>
+        <v>6986339</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14401,8 +14385,29 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
@@ -14419,57 +14424,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129908893</v>
+        <v>129910584</v>
       </c>
       <c r="B133" t="n">
-        <v>98920</v>
+        <v>80285</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>516958</v>
+        <v>517004</v>
       </c>
       <c r="R133" t="n">
-        <v>6986409</v>
+        <v>6986361</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14504,25 +14497,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i barrblandskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
@@ -14539,10 +14521,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129910560</v>
+        <v>129908893</v>
       </c>
       <c r="B134" t="n">
-        <v>58462</v>
+        <v>98920</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14550,50 +14532,46 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>102125</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>517237</v>
+        <v>516958</v>
       </c>
       <c r="R134" t="n">
-        <v>6986082</v>
+        <v>6986409</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14628,14 +14606,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 3 vinterståndare inom ca 1 m2 yta i barrblandskog. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
@@ -14652,10 +14641,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129908897</v>
+        <v>129910560</v>
       </c>
       <c r="B135" t="n">
-        <v>98920</v>
+        <v>58462</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14663,50 +14652,50 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>102125</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>516696</v>
+        <v>517237</v>
       </c>
       <c r="R135" t="n">
-        <v>6986696</v>
+        <v>6986082</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14741,25 +14730,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Minst 20 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
@@ -14776,45 +14754,61 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129910594</v>
+        <v>129908897</v>
       </c>
       <c r="B136" t="n">
-        <v>80285</v>
+        <v>98920</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>517165</v>
+        <v>516696</v>
       </c>
       <c r="R136" t="n">
-        <v>6986222</v>
+        <v>6986696</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14849,14 +14843,25 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Minst 20 plantor och 1 vinterståndare inom ca 0,5 m2 yta. Marken var snötäckt vid besöket på fyndplatsen. Fler plantor är sannolikt synliga under barmarkssäsongen.</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
@@ -14873,7 +14878,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129910624</v>
+        <v>129910594</v>
       </c>
       <c r="B137" t="n">
         <v>80285</v>
@@ -14908,10 +14913,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>517195</v>
+        <v>517165</v>
       </c>
       <c r="R137" t="n">
-        <v>6986175</v>
+        <v>6986222</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14970,7 +14975,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129910634</v>
+        <v>129910624</v>
       </c>
       <c r="B138" t="n">
         <v>80285</v>
@@ -15005,10 +15010,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>517233</v>
+        <v>517195</v>
       </c>
       <c r="R138" t="n">
-        <v>6986069</v>
+        <v>6986175</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15067,52 +15072,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129910659</v>
+        <v>129910634</v>
       </c>
       <c r="B139" t="n">
-        <v>93010</v>
+        <v>80285</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>517328</v>
+        <v>517233</v>
       </c>
       <c r="R139" t="n">
-        <v>6986156</v>
+        <v>6986069</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15153,7 +15151,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15172,10 +15169,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129910572</v>
+        <v>129910659</v>
       </c>
       <c r="B140" t="n">
-        <v>80189</v>
+        <v>93010</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15183,34 +15180,41 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Bergmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>517147</v>
+        <v>517328</v>
       </c>
       <c r="R140" t="n">
-        <v>6986129</v>
+        <v>6986156</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15251,6 +15255,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15269,32 +15274,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129910747</v>
+        <v>129910572</v>
       </c>
       <c r="B141" t="n">
-        <v>80285</v>
+        <v>80189</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15304,10 +15309,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>516674</v>
+        <v>517147</v>
       </c>
       <c r="R141" t="n">
-        <v>6986695</v>
+        <v>6986129</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15342,11 +15347,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på liggande men levande sälg.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15359,12 +15359,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>

--- a/artfynd/A 51969-2025 artfynd.xlsx
+++ b/artfynd/A 51969-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY188"/>
+  <dimension ref="A1:AZ188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910547</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910548</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910665</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910563</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1159,6 +1184,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910564</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1256,6 +1286,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910643</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1353,6 +1388,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910644</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1450,6 +1490,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910645</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1547,6 +1592,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910662</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910660</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910661</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1922,6 +1982,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908878</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2047,6 +2112,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910551</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2167,6 +2237,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910562</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2264,6 +2339,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910655</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2361,6 +2441,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910656</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2458,6 +2543,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910573</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2555,6 +2645,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910550</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2652,6 +2747,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910567</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2749,6 +2849,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910568</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2846,6 +2951,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910569</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2951,6 +3061,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910659</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3077,6 +3192,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908899</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3208,6 +3328,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908900</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3334,6 +3459,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908901</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3465,6 +3595,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908902</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3596,6 +3731,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908903</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3722,6 +3862,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908904</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3853,6 +3998,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908905</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3979,6 +4129,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908906</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4110,6 +4265,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908907</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4236,6 +4396,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908908</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4362,6 +4527,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908909</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4488,6 +4658,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908910</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4623,6 +4798,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908911</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4739,6 +4919,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910651</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4855,6 +5040,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910652</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4976,6 +5166,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910653</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5105,6 +5300,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910654</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5202,6 +5402,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910749</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5304,6 +5509,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910750</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5406,6 +5616,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910751</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5508,6 +5723,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910752</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5610,6 +5830,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910753</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5712,6 +5937,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910754</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5809,6 +6039,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921280</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5906,6 +6141,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910574</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6003,6 +6243,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910541</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6100,6 +6345,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910542</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6197,6 +6447,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910543</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6294,6 +6549,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910544</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6391,6 +6651,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910545</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6488,6 +6753,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910546</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6585,6 +6855,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910647</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6682,6 +6957,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910565</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6779,6 +7059,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910566</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6876,6 +7161,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910549</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6973,6 +7263,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910570</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7070,6 +7365,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910571</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7167,6 +7467,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910572</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7302,6 +7607,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908885</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7412,6 +7722,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908886</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7547,6 +7862,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908887</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7678,6 +7998,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908888</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7813,6 +8138,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908889</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7944,6 +8274,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908890</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8079,6 +8414,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908891</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8214,6 +8554,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908892</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8311,6 +8656,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910575</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8408,6 +8758,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910576</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8505,6 +8860,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910577</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8602,6 +8962,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910578</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8699,6 +9064,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910579</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8796,6 +9166,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910580</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8893,6 +9268,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910581</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8990,6 +9370,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910582</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9087,6 +9472,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910583</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9184,6 +9574,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910584</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9281,6 +9676,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910585</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9378,6 +9778,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910586</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9475,6 +9880,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910587</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9572,6 +9982,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910588</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9669,6 +10084,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910589</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9766,6 +10186,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910590</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9863,6 +10288,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910591</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9960,6 +10390,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910592</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10057,6 +10492,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910593</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10154,6 +10594,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910594</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10251,6 +10696,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910595</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10348,6 +10798,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910596</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10445,6 +10900,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910597</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10542,6 +11002,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910598</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10639,6 +11104,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910599</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10736,6 +11206,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910600</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10833,6 +11308,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910601</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10930,6 +11410,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910602</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11027,6 +11512,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910603</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11124,6 +11614,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910604</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11221,6 +11716,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910605</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11318,6 +11818,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910606</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11415,6 +11920,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910607</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11512,6 +12022,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910608</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11609,6 +12124,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910609</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11706,6 +12226,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910610</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11803,6 +12328,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910611</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11900,6 +12430,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910613</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11997,6 +12532,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910614</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12094,6 +12634,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910615</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12191,6 +12736,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910616</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12288,6 +12838,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910617</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12385,6 +12940,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910618</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12482,6 +13042,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910619</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12579,6 +13144,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910620</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12676,6 +13246,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910621</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12773,6 +13348,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910622</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12870,6 +13450,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910623</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12967,6 +13552,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910624</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13064,6 +13654,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910625</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13161,6 +13756,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910626</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13258,6 +13858,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910627</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13355,6 +13960,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910628</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13452,6 +14062,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910629</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13549,6 +14164,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910630</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13646,6 +14266,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910631</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13743,6 +14368,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910632</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13840,6 +14470,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910633</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13937,6 +14572,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910634</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14034,6 +14674,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910635</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14131,6 +14776,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910636</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14228,6 +14878,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910637</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14325,6 +14980,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910638</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14435,6 +15095,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910639</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14532,6 +15197,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910640</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14634,6 +15304,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910738</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14736,6 +15411,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910739</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14838,6 +15518,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910740</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14940,6 +15625,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910741</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15042,6 +15732,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910742</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15144,6 +15839,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910743</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15246,6 +15946,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910744</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15348,6 +16053,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910745</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15450,6 +16160,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910746</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15552,6 +16267,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910747</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15654,6 +16374,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921263</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15756,6 +16481,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921265</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15853,6 +16583,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921267</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15950,6 +16685,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921270</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16052,6 +16792,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921271</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16149,6 +16894,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921272</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16251,6 +17001,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921273</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16348,6 +17103,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921274</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16445,6 +17205,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921275</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16542,6 +17307,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921276</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16644,6 +17414,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921277</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16746,6 +17521,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921278</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16852,6 +17632,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129921279</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16949,6 +17734,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910667</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17046,6 +17836,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910668</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17143,6 +17938,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910669</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17240,6 +18040,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910670</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17345,6 +18150,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910663</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17450,6 +18260,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910664</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17589,6 +18404,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908879</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17728,6 +18548,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908880</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17867,6 +18692,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908881</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18006,6 +18836,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908882</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18116,6 +18951,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910553</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18226,6 +19066,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910554</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18336,6 +19181,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910555</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18446,6 +19296,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910556</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18556,6 +19411,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910557</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18666,6 +19526,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910558</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18779,6 +19644,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910560</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18892,6 +19762,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910649</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19005,6 +19880,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910559</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19129,6 +20009,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908912</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19249,6 +20134,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908893</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19373,6 +20263,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908894</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19497,6 +20392,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908895</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19621,6 +20521,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908896</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19745,6 +20650,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908897</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19864,6 +20774,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910648</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19966,6 +20881,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910748</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20063,6 +20983,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910641</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20160,6 +21085,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910642</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20257,6 +21187,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910646</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20354,8 +21289,202 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910666</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>